--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2650,6 +2650,5451 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124739661</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fagernäs, Fagernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>705952</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7086928</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124736627</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>706292</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7087225</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124749376</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>706224</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7087139</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124734903</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>706371</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7087353</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124749539</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>706157</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7087072</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124734139</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>706472</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7087356</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124732683</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>706597</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7087402</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124749657</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>705966</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7086987</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124732613</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>706654</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7087408</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124749013</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>706446</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7087375</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124749040</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>706431</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7087362</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124735830</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>706344</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7087202</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124749086</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>706447</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7087337</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124739580</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fagernäs, Fagernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>706048</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7086914</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124734081</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>706490</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7087362</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124749575</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>706133</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7087057</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124749500</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>706145</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7087098</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124739909</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fagernäs, Fagernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>706048</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7086914</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124733522</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>706523</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7087364</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124749111</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>706398</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7087345</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124749167</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>706354</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7087195</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124749460</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>706115</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7087088</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124733886</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>706495</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7087369</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124733393</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>706533</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7087362</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124749290</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>706276</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7087213</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124749246</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>706288</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7087206</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124734648</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>706405</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7087320</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124749070</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>706442</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7087349</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124749414</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>706126</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7087117</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124739585</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fagernäs, Fagernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>705944</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7086954</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124738318</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>706281</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7087219</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124734745</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>706401</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7087323</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124735169</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>706394</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7087340</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124749263</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>706282</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7087215</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124737518</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>706341</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7087207</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124749184</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>706340</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7087178</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124749392</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>706191</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7087129</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124739921</v>
+      </c>
+      <c r="B55" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fagernäs, Fagernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>706034</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7086918</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124737966</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>706281</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7087219</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124734381</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>706473</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7087334</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124734940</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>706418</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7087323</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124749350</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>706238</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7087154</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124749331</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>706228</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7087165</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124739096</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>706304</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7087194</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124744220</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>706411</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7087322</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124749686</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>705962</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7086855</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124732401</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>706665</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7087406</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124734417</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Brattfällan, Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>706465</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7087346</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124749133</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Brattfällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>706364</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7087314</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124739661</v>
+        <v>124749350</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2686,19 +2686,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705952</v>
+        <v>706238</v>
       </c>
       <c r="R18" t="n">
-        <v>7086928</v>
+        <v>7087154</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2725,19 +2729,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2746,28 +2745,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124736627</v>
+        <v>124734139</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,25 +2776,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706292</v>
+        <v>706472</v>
       </c>
       <c r="R19" t="n">
-        <v>7087225</v>
+        <v>7087356</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2837,9 +2837,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,19 +2869,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749376</v>
+        <v>124749086</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2910,10 +2925,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706224</v>
+        <v>706447</v>
       </c>
       <c r="R20" t="n">
-        <v>7087139</v>
+        <v>7087337</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2978,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124734903</v>
+        <v>124749167</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2990,41 +3005,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706371</v>
+        <v>706354</v>
       </c>
       <c r="R21" t="n">
-        <v>7087353</v>
+        <v>7087195</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3051,19 +3070,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,25 +3086,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749539</v>
+        <v>124749263</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3134,10 +3149,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706157</v>
+        <v>706282</v>
       </c>
       <c r="R22" t="n">
-        <v>7087072</v>
+        <v>7087215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3202,7 +3217,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124734139</v>
+        <v>124749040</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3236,19 +3251,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706472</v>
+        <v>706431</v>
       </c>
       <c r="R23" t="n">
-        <v>7087356</v>
+        <v>7087362</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3275,24 +3294,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,18 +3310,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3431,7 +3441,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749657</v>
+        <v>124749539</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3475,10 +3485,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705966</v>
+        <v>706157</v>
       </c>
       <c r="R25" t="n">
-        <v>7086987</v>
+        <v>7087072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3543,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124732613</v>
+        <v>124734648</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3555,25 +3565,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3583,10 +3593,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706654</v>
+        <v>706405</v>
       </c>
       <c r="R26" t="n">
-        <v>7087408</v>
+        <v>7087320</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3618,7 +3628,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3628,7 +3638,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,7 +3665,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749013</v>
+        <v>124749070</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3699,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706446</v>
+        <v>706442</v>
       </c>
       <c r="R27" t="n">
-        <v>7087375</v>
+        <v>7087349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,7 +3749,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3767,10 +3777,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749040</v>
+        <v>124738318</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3779,45 +3789,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706431</v>
+        <v>706281</v>
       </c>
       <c r="R28" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3849,40 +3855,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124735830</v>
+        <v>124733886</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,25 +3891,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706344</v>
+        <v>706495</v>
       </c>
       <c r="R29" t="n">
-        <v>7087202</v>
+        <v>7087369</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3964,7 +3964,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3991,10 +3996,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124749086</v>
+        <v>124732401</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,45 +4008,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706447</v>
+        <v>706665</v>
       </c>
       <c r="R30" t="n">
-        <v>7087337</v>
+        <v>7087406</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4068,14 +4069,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,29 +4090,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124739580</v>
+        <v>124749246</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4115,41 +4120,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706048</v>
+        <v>706288</v>
       </c>
       <c r="R31" t="n">
-        <v>7086914</v>
+        <v>7087206</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4181,31 +4190,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124734081</v>
+        <v>124749392</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4239,19 +4254,23 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706490</v>
+        <v>706191</v>
       </c>
       <c r="R32" t="n">
-        <v>7087362</v>
+        <v>7087129</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4278,19 +4297,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4299,25 +4313,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749575</v>
+        <v>124749460</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4361,10 +4376,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706133</v>
+        <v>706115</v>
       </c>
       <c r="R33" t="n">
-        <v>7087057</v>
+        <v>7087088</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4401,7 +4416,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,7 +4444,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749500</v>
+        <v>124734081</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4463,23 +4478,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706145</v>
+        <v>706490</v>
       </c>
       <c r="R34" t="n">
-        <v>7087098</v>
+        <v>7087362</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4506,14 +4517,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4522,29 +4538,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739909</v>
+        <v>124739580</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4553,37 +4568,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fagernäs, Fagernäs, Ång</t>
@@ -4652,10 +4658,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124733522</v>
+        <v>124734940</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4664,25 +4670,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4692,10 +4698,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706523</v>
+        <v>706418</v>
       </c>
       <c r="R36" t="n">
-        <v>7087364</v>
+        <v>7087323</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4725,19 +4731,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4752,19 +4748,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749111</v>
+        <v>124734745</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4798,23 +4794,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706398</v>
+        <v>706401</v>
       </c>
       <c r="R37" t="n">
-        <v>7087345</v>
+        <v>7087323</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4841,14 +4833,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4857,26 +4859,25 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749167</v>
+        <v>124735830</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4910,23 +4911,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706354</v>
+        <v>706344</v>
       </c>
       <c r="R38" t="n">
-        <v>7087195</v>
+        <v>7087202</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4953,14 +4950,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4969,29 +4971,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749460</v>
+        <v>124739921</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5000,45 +5001,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706115</v>
+        <v>706034</v>
       </c>
       <c r="R39" t="n">
-        <v>7087088</v>
+        <v>7086918</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5065,14 +5062,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5081,29 +5083,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124733886</v>
+        <v>124734381</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5112,25 +5113,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5140,10 +5141,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706495</v>
+        <v>706473</v>
       </c>
       <c r="R40" t="n">
-        <v>7087369</v>
+        <v>7087334</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5175,7 +5176,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5185,12 +5186,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5217,7 +5213,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124733393</v>
+        <v>124749414</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5251,19 +5247,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706533</v>
+        <v>706126</v>
       </c>
       <c r="R41" t="n">
-        <v>7087362</v>
+        <v>7087117</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5290,19 +5290,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,28 +5306,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749290</v>
+        <v>124733393</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5341,49 +5337,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706276</v>
+        <v>706533</v>
       </c>
       <c r="R42" t="n">
-        <v>7087213</v>
+        <v>7087362</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5410,9 +5398,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,19 +5425,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749246</v>
+        <v>124749111</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5483,10 +5481,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706288</v>
+        <v>706398</v>
       </c>
       <c r="R43" t="n">
-        <v>7087206</v>
+        <v>7087345</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5523,7 +5521,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5551,7 +5549,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124734648</v>
+        <v>124749500</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5585,19 +5583,23 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706405</v>
+        <v>706145</v>
       </c>
       <c r="R44" t="n">
-        <v>7087320</v>
+        <v>7087098</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5624,19 +5626,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5645,25 +5642,26 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749070</v>
+        <v>124737966</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5696,24 +5694,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706442</v>
+        <v>706281</v>
       </c>
       <c r="R45" t="n">
-        <v>7087349</v>
+        <v>7087219</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5745,37 +5748,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749414</v>
+        <v>124749575</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5819,10 +5816,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706126</v>
+        <v>706133</v>
       </c>
       <c r="R46" t="n">
-        <v>7087117</v>
+        <v>7087057</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5999,10 +5996,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124738318</v>
+        <v>124749657</v>
       </c>
       <c r="B48" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6011,41 +6008,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706281</v>
+        <v>705966</v>
       </c>
       <c r="R48" t="n">
-        <v>7087219</v>
+        <v>7086987</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6077,31 +6078,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124734745</v>
+        <v>124739096</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6141,10 +6148,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706401</v>
+        <v>706304</v>
       </c>
       <c r="R49" t="n">
-        <v>7087323</v>
+        <v>7087194</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6176,7 +6183,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6186,12 +6193,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,10 +6220,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124735169</v>
+        <v>124737518</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6230,25 +6232,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6258,10 +6260,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706394</v>
+        <v>706341</v>
       </c>
       <c r="R50" t="n">
-        <v>7087340</v>
+        <v>7087207</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6291,9 +6293,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6308,19 +6320,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749263</v>
+        <v>124749133</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6364,10 +6376,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706282</v>
+        <v>706364</v>
       </c>
       <c r="R51" t="n">
-        <v>7087215</v>
+        <v>7087314</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6400,11 +6412,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6432,10 +6439,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124737518</v>
+        <v>124749290</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,41 +6451,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706341</v>
+        <v>706276</v>
       </c>
       <c r="R52" t="n">
-        <v>7087207</v>
+        <v>7087213</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6505,19 +6520,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6532,12 +6537,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6656,7 +6661,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749392</v>
+        <v>124749376</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6700,10 +6705,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706191</v>
+        <v>706224</v>
       </c>
       <c r="R54" t="n">
-        <v>7087129</v>
+        <v>7087139</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6768,10 +6773,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124739921</v>
+        <v>124739909</v>
       </c>
       <c r="B55" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6780,38 +6785,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706034</v>
+        <v>706048</v>
       </c>
       <c r="R55" t="n">
-        <v>7086918</v>
+        <v>7086914</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6841,19 +6855,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6868,19 +6872,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124737966</v>
+        <v>124749331</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6913,29 +6917,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706281</v>
+        <v>706228</v>
       </c>
       <c r="R56" t="n">
-        <v>7087219</v>
+        <v>7087165</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6967,34 +6966,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124734381</v>
+        <v>124739661</v>
       </c>
       <c r="B57" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7003,38 +7008,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706473</v>
+        <v>705952</v>
       </c>
       <c r="R57" t="n">
-        <v>7087334</v>
+        <v>7086928</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7066,7 +7071,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7076,7 +7081,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7103,10 +7108,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124734940</v>
+        <v>124732613</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7115,25 +7120,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706418</v>
+        <v>706654</v>
       </c>
       <c r="R58" t="n">
-        <v>7087323</v>
+        <v>7087408</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7176,9 +7181,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7193,22 +7208,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749350</v>
+        <v>124744220</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7217,31 +7232,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7249,10 +7272,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706238</v>
+        <v>706411</v>
       </c>
       <c r="R59" t="n">
-        <v>7087154</v>
+        <v>7087322</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7287,18 +7310,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7317,10 +7334,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749331</v>
+        <v>124736627</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7329,45 +7346,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706228</v>
+        <v>706292</v>
       </c>
       <c r="R60" t="n">
-        <v>7087165</v>
+        <v>7087225</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7399,40 +7412,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124739096</v>
+        <v>124735169</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7441,25 +7448,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7469,10 +7476,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706304</v>
+        <v>706394</v>
       </c>
       <c r="R61" t="n">
-        <v>7087194</v>
+        <v>7087340</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7502,19 +7509,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7529,22 +7526,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124744220</v>
+        <v>124733522</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7553,53 +7550,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706411</v>
+        <v>706523</v>
       </c>
       <c r="R62" t="n">
-        <v>7087322</v>
+        <v>7087364</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7626,9 +7611,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7643,22 +7638,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749686</v>
+        <v>124734417</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7667,44 +7662,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>705962</v>
+        <v>706465</v>
       </c>
       <c r="R63" t="n">
-        <v>7086855</v>
+        <v>7087346</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7731,40 +7723,54 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124732401</v>
+        <v>124734903</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7773,25 +7779,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7801,10 +7807,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706665</v>
+        <v>706371</v>
       </c>
       <c r="R64" t="n">
-        <v>7087406</v>
+        <v>7087353</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7836,7 +7842,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7846,7 +7852,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7873,10 +7879,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124734417</v>
+        <v>124749686</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,41 +7891,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706465</v>
+        <v>705962</v>
       </c>
       <c r="R65" t="n">
-        <v>7087346</v>
+        <v>7086855</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7946,51 +7955,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749133</v>
+        <v>124749013</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8034,10 +8029,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706364</v>
+        <v>706446</v>
       </c>
       <c r="R66" t="n">
-        <v>7087314</v>
+        <v>7087375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8070,6 +8065,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749350</v>
+        <v>124749414</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706238</v>
+        <v>706126</v>
       </c>
       <c r="R18" t="n">
-        <v>7087154</v>
+        <v>7087117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,10 +2881,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749086</v>
+        <v>124739921</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,45 +2893,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706447</v>
+        <v>706034</v>
       </c>
       <c r="R20" t="n">
-        <v>7087337</v>
+        <v>7086918</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,14 +2954,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2974,26 +2975,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749167</v>
+        <v>124749657</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706354</v>
+        <v>705966</v>
       </c>
       <c r="R21" t="n">
-        <v>7087195</v>
+        <v>7086987</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3105,10 +3105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749263</v>
+        <v>124749290</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,31 +3117,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3149,10 +3153,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706282</v>
+        <v>706276</v>
       </c>
       <c r="R22" t="n">
-        <v>7087215</v>
+        <v>7087213</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3187,18 +3191,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3217,7 +3215,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749040</v>
+        <v>124737966</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3250,24 +3248,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706431</v>
+        <v>706281</v>
       </c>
       <c r="R23" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3299,40 +3302,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124732683</v>
+        <v>124734417</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3341,25 +3338,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3369,10 +3366,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706597</v>
+        <v>706465</v>
       </c>
       <c r="R24" t="n">
-        <v>7087402</v>
+        <v>7087346</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3404,7 +3401,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3414,7 +3411,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3441,7 +3443,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749539</v>
+        <v>124739661</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3475,23 +3477,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706157</v>
+        <v>705952</v>
       </c>
       <c r="R25" t="n">
-        <v>7087072</v>
+        <v>7086928</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3518,14 +3516,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,29 +3537,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124734648</v>
+        <v>124734903</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,25 +3567,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3593,10 +3595,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706405</v>
+        <v>706371</v>
       </c>
       <c r="R26" t="n">
-        <v>7087320</v>
+        <v>7087353</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3628,7 +3630,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3638,7 +3640,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,10 +3667,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749070</v>
+        <v>124736627</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3677,45 +3679,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706442</v>
+        <v>706292</v>
       </c>
       <c r="R27" t="n">
-        <v>7087349</v>
+        <v>7087225</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3747,40 +3745,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124738318</v>
+        <v>124749263</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3789,41 +3781,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706281</v>
+        <v>706282</v>
       </c>
       <c r="R28" t="n">
-        <v>7087219</v>
+        <v>7087215</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3855,34 +3851,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124733886</v>
+        <v>124734648</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,25 +3893,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3919,10 +3921,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706495</v>
+        <v>706405</v>
       </c>
       <c r="R29" t="n">
-        <v>7087369</v>
+        <v>7087320</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3954,7 +3956,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3964,12 +3966,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3996,10 +3993,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732401</v>
+        <v>124749575</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4008,41 +4005,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706665</v>
+        <v>706133</v>
       </c>
       <c r="R30" t="n">
-        <v>7087406</v>
+        <v>7087057</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,19 +4070,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,25 +4086,26 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749246</v>
+        <v>124749350</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4152,10 +4149,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706288</v>
+        <v>706238</v>
       </c>
       <c r="R31" t="n">
-        <v>7087206</v>
+        <v>7087154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,7 +4189,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4220,7 +4217,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749392</v>
+        <v>124749111</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4264,10 +4261,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706191</v>
+        <v>706398</v>
       </c>
       <c r="R32" t="n">
-        <v>7087129</v>
+        <v>7087345</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4332,7 +4329,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749460</v>
+        <v>124749331</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4376,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706115</v>
+        <v>706228</v>
       </c>
       <c r="R33" t="n">
-        <v>7087088</v>
+        <v>7087165</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4413,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4444,7 +4441,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124734081</v>
+        <v>124749460</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4478,19 +4475,23 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706490</v>
+        <v>706115</v>
       </c>
       <c r="R34" t="n">
-        <v>7087362</v>
+        <v>7087088</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4517,19 +4518,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4538,28 +4534,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739580</v>
+        <v>124749167</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4568,41 +4565,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706048</v>
+        <v>706354</v>
       </c>
       <c r="R35" t="n">
-        <v>7086914</v>
+        <v>7087195</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4634,34 +4635,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124734940</v>
+        <v>124732401</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4670,25 +4677,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4698,10 +4705,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706418</v>
+        <v>706665</v>
       </c>
       <c r="R36" t="n">
-        <v>7087323</v>
+        <v>7087406</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4731,9 +4738,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4748,19 +4765,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124734745</v>
+        <v>124739585</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4796,14 +4813,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706401</v>
+        <v>705944</v>
       </c>
       <c r="R37" t="n">
-        <v>7087323</v>
+        <v>7086954</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4835,7 +4852,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4845,12 +4862,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4877,7 +4889,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124735830</v>
+        <v>124749070</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4911,19 +4923,23 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706344</v>
+        <v>706442</v>
       </c>
       <c r="R38" t="n">
-        <v>7087202</v>
+        <v>7087349</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4950,19 +4966,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,28 +4982,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124739921</v>
+        <v>124739909</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5001,38 +5013,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706034</v>
+        <v>706048</v>
       </c>
       <c r="R39" t="n">
-        <v>7086918</v>
+        <v>7086914</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5062,19 +5083,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5089,22 +5100,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124734381</v>
+        <v>124744220</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5113,41 +5124,53 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706473</v>
+        <v>706411</v>
       </c>
       <c r="R40" t="n">
-        <v>7087334</v>
+        <v>7087322</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5174,19 +5197,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5201,19 +5214,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749414</v>
+        <v>124735830</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5247,23 +5260,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706126</v>
+        <v>706344</v>
       </c>
       <c r="R41" t="n">
-        <v>7087117</v>
+        <v>7087202</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5290,14 +5299,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5306,26 +5320,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124733393</v>
+        <v>124749086</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5359,19 +5372,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706533</v>
+        <v>706447</v>
       </c>
       <c r="R42" t="n">
-        <v>7087362</v>
+        <v>7087337</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5398,19 +5415,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5419,25 +5431,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749111</v>
+        <v>124734940</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5471,23 +5484,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706398</v>
+        <v>706418</v>
       </c>
       <c r="R43" t="n">
-        <v>7087345</v>
+        <v>7087323</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5519,37 +5528,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749500</v>
+        <v>124749392</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5593,10 +5596,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706145</v>
+        <v>706191</v>
       </c>
       <c r="R44" t="n">
-        <v>7087098</v>
+        <v>7087129</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5661,10 +5664,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124737966</v>
+        <v>124739580</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5673,47 +5676,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706281</v>
+        <v>706048</v>
       </c>
       <c r="R45" t="n">
-        <v>7087219</v>
+        <v>7086914</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5772,7 +5766,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749575</v>
+        <v>124749184</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5816,10 +5810,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706133</v>
+        <v>706340</v>
       </c>
       <c r="R46" t="n">
-        <v>7087057</v>
+        <v>7087178</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5884,7 +5878,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124739585</v>
+        <v>124749013</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5918,19 +5912,23 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705944</v>
+        <v>706446</v>
       </c>
       <c r="R47" t="n">
-        <v>7086954</v>
+        <v>7087375</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5957,19 +5955,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5978,25 +5971,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749657</v>
+        <v>124749040</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6040,10 +6034,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705966</v>
+        <v>706431</v>
       </c>
       <c r="R48" t="n">
-        <v>7086987</v>
+        <v>7087362</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6080,7 +6074,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6108,7 +6102,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124739096</v>
+        <v>124749500</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6142,19 +6136,23 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706304</v>
+        <v>706145</v>
       </c>
       <c r="R49" t="n">
-        <v>7087194</v>
+        <v>7087098</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6181,19 +6179,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6202,25 +6195,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124737518</v>
+        <v>124749376</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6254,19 +6248,23 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706341</v>
+        <v>706224</v>
       </c>
       <c r="R50" t="n">
-        <v>7087207</v>
+        <v>7087139</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6293,19 +6291,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,28 +6307,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749133</v>
+        <v>124732613</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,45 +6338,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706364</v>
+        <v>706654</v>
       </c>
       <c r="R51" t="n">
-        <v>7087314</v>
+        <v>7087408</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6409,40 +6399,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749290</v>
+        <v>124733393</v>
       </c>
       <c r="B52" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6451,49 +6450,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706276</v>
+        <v>706533</v>
       </c>
       <c r="R52" t="n">
-        <v>7087213</v>
+        <v>7087362</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6520,9 +6511,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6537,19 +6538,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749184</v>
+        <v>124739096</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6583,23 +6584,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706340</v>
+        <v>706304</v>
       </c>
       <c r="R53" t="n">
-        <v>7087178</v>
+        <v>7087194</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6626,14 +6623,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6642,29 +6644,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749376</v>
+        <v>124738318</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6673,45 +6674,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706224</v>
+        <v>706281</v>
       </c>
       <c r="R54" t="n">
-        <v>7087139</v>
+        <v>7087219</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6743,37 +6740,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124739909</v>
+        <v>124749246</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6806,29 +6797,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706048</v>
+        <v>706288</v>
       </c>
       <c r="R55" t="n">
-        <v>7086914</v>
+        <v>7087206</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6860,31 +6846,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749331</v>
+        <v>124749539</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6928,10 +6920,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706228</v>
+        <v>706157</v>
       </c>
       <c r="R56" t="n">
-        <v>7087165</v>
+        <v>7087072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6968,7 +6960,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6996,7 +6988,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124739661</v>
+        <v>124734745</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7032,14 +7024,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705952</v>
+        <v>706401</v>
       </c>
       <c r="R57" t="n">
-        <v>7086928</v>
+        <v>7087323</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7071,7 +7063,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7081,7 +7073,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7108,10 +7105,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124732613</v>
+        <v>124737518</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7120,25 +7117,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7148,10 +7145,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706654</v>
+        <v>706341</v>
       </c>
       <c r="R58" t="n">
-        <v>7087408</v>
+        <v>7087207</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7183,7 +7180,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7193,7 +7190,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7220,10 +7217,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124744220</v>
+        <v>124749133</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7232,39 +7229,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7272,10 +7261,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706411</v>
+        <v>706364</v>
       </c>
       <c r="R59" t="n">
-        <v>7087322</v>
+        <v>7087314</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7316,6 +7305,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7334,7 +7324,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124736627</v>
+        <v>124734381</v>
       </c>
       <c r="B60" t="n">
         <v>57529</v>
@@ -7374,10 +7364,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706292</v>
+        <v>706473</v>
       </c>
       <c r="R60" t="n">
-        <v>7087225</v>
+        <v>7087334</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7407,9 +7397,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7424,19 +7424,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124735169</v>
+        <v>124749686</v>
       </c>
       <c r="B61" t="n">
         <v>91012</v>
@@ -7470,19 +7470,22 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706394</v>
+        <v>705962</v>
       </c>
       <c r="R61" t="n">
-        <v>7087340</v>
+        <v>7086855</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7520,28 +7523,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124733522</v>
+        <v>124733886</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7550,25 +7554,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7578,10 +7582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706523</v>
+        <v>706495</v>
       </c>
       <c r="R62" t="n">
-        <v>7087364</v>
+        <v>7087369</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7613,7 +7617,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7623,7 +7627,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7650,7 +7659,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124734417</v>
+        <v>124734081</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7690,10 +7699,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706465</v>
+        <v>706490</v>
       </c>
       <c r="R63" t="n">
-        <v>7087346</v>
+        <v>7087362</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7725,7 +7734,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7735,12 +7744,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7767,10 +7771,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124734903</v>
+        <v>124735169</v>
       </c>
       <c r="B64" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7779,25 +7783,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7807,10 +7811,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706371</v>
+        <v>706394</v>
       </c>
       <c r="R64" t="n">
-        <v>7087353</v>
+        <v>7087340</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7840,19 +7844,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7867,19 +7861,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749686</v>
+        <v>124732683</v>
       </c>
       <c r="B65" t="n">
         <v>91012</v>
@@ -7913,22 +7907,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705962</v>
+        <v>706597</v>
       </c>
       <c r="R65" t="n">
-        <v>7086855</v>
+        <v>7087402</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7955,40 +7946,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749013</v>
+        <v>124733522</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,45 +7997,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706446</v>
+        <v>706523</v>
       </c>
       <c r="R66" t="n">
-        <v>7087375</v>
+        <v>7087364</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8062,14 +8058,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,19 +8079,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2993,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749657</v>
+        <v>124749290</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,31 +3005,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3037,10 +3041,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705966</v>
+        <v>706276</v>
       </c>
       <c r="R21" t="n">
-        <v>7086987</v>
+        <v>7087213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,18 +3079,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3105,10 +3103,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749290</v>
+        <v>124749657</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,35 +3115,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3153,10 +3147,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706276</v>
+        <v>705966</v>
       </c>
       <c r="R22" t="n">
-        <v>7087213</v>
+        <v>7086987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3191,12 +3185,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124737966</v>
+        <v>124734903</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3227,47 +3227,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706281</v>
+        <v>706371</v>
       </c>
       <c r="R23" t="n">
-        <v>7087219</v>
+        <v>7087353</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3297,9 +3288,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3314,19 +3315,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124734417</v>
+        <v>124737966</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3359,17 +3360,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706465</v>
+        <v>706281</v>
       </c>
       <c r="R24" t="n">
-        <v>7087346</v>
+        <v>7087219</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3399,24 +3409,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3431,19 +3426,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124739661</v>
+        <v>124734417</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3479,14 +3474,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705952</v>
+        <v>706465</v>
       </c>
       <c r="R25" t="n">
-        <v>7086928</v>
+        <v>7087346</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3518,7 +3513,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3528,7 +3523,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124734903</v>
+        <v>124739661</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3567,38 +3567,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706371</v>
+        <v>705952</v>
       </c>
       <c r="R26" t="n">
-        <v>7087353</v>
+        <v>7086928</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3667,10 +3667,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124736627</v>
+        <v>124749263</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3679,41 +3679,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706292</v>
+        <v>706282</v>
       </c>
       <c r="R27" t="n">
-        <v>7087225</v>
+        <v>7087215</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3745,34 +3749,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749263</v>
+        <v>124736627</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3781,45 +3791,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706282</v>
+        <v>706292</v>
       </c>
       <c r="R28" t="n">
-        <v>7087215</v>
+        <v>7087225</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3851,30 +3857,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124744220</v>
+        <v>124735830</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5124,53 +5124,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706411</v>
+        <v>706344</v>
       </c>
       <c r="R40" t="n">
-        <v>7087322</v>
+        <v>7087202</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5197,9 +5185,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5214,19 +5212,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124735830</v>
+        <v>124749086</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5260,19 +5258,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706344</v>
+        <v>706447</v>
       </c>
       <c r="R41" t="n">
-        <v>7087202</v>
+        <v>7087337</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5299,19 +5301,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5320,28 +5317,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749086</v>
+        <v>124744220</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5350,31 +5348,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5382,10 +5388,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706447</v>
+        <v>706411</v>
       </c>
       <c r="R42" t="n">
-        <v>7087337</v>
+        <v>7087322</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5420,18 +5426,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124734081</v>
+        <v>124735169</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7671,25 +7671,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706490</v>
+        <v>706394</v>
       </c>
       <c r="R63" t="n">
-        <v>7087362</v>
+        <v>7087340</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7732,19 +7732,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7759,19 +7749,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124735169</v>
+        <v>124732683</v>
       </c>
       <c r="B64" t="n">
         <v>91012</v>
@@ -7811,10 +7801,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706394</v>
+        <v>706597</v>
       </c>
       <c r="R64" t="n">
-        <v>7087340</v>
+        <v>7087402</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7844,9 +7834,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7861,22 +7861,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124732683</v>
+        <v>124733522</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7889,21 +7889,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706597</v>
+        <v>706523</v>
       </c>
       <c r="R65" t="n">
-        <v>7087402</v>
+        <v>7087364</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7985,10 +7985,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124733522</v>
+        <v>124734081</v>
       </c>
       <c r="B66" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,25 +7997,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706523</v>
+        <v>706490</v>
       </c>
       <c r="R66" t="n">
-        <v>7087364</v>
+        <v>7087362</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749414</v>
+        <v>124749350</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706126</v>
+        <v>706238</v>
       </c>
       <c r="R18" t="n">
-        <v>7087117</v>
+        <v>7087154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,7 +2764,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124734139</v>
+        <v>124739661</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2800,14 +2800,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706472</v>
+        <v>705952</v>
       </c>
       <c r="R19" t="n">
-        <v>7087356</v>
+        <v>7086928</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2849,12 +2849,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,10 +2876,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124739921</v>
+        <v>124739096</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,38 +2888,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706034</v>
+        <v>706304</v>
       </c>
       <c r="R20" t="n">
-        <v>7086918</v>
+        <v>7087194</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2956,7 +2951,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2966,7 +2961,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2993,10 +2988,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749290</v>
+        <v>124749460</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,35 +3000,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3041,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706276</v>
+        <v>706115</v>
       </c>
       <c r="R21" t="n">
-        <v>7087213</v>
+        <v>7087088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3079,12 +3070,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3103,7 +3100,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749657</v>
+        <v>124749013</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3147,10 +3144,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705966</v>
+        <v>706446</v>
       </c>
       <c r="R22" t="n">
-        <v>7086987</v>
+        <v>7087375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3187,7 +3184,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3215,10 +3212,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124734903</v>
+        <v>124737518</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3227,25 +3224,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3255,10 +3252,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706371</v>
+        <v>706341</v>
       </c>
       <c r="R23" t="n">
-        <v>7087353</v>
+        <v>7087207</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3290,7 +3287,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3300,7 +3297,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3327,10 +3324,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124737966</v>
+        <v>124739921</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3339,47 +3336,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706281</v>
+        <v>706034</v>
       </c>
       <c r="R24" t="n">
-        <v>7087219</v>
+        <v>7086918</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3409,9 +3397,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3426,19 +3424,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734417</v>
+        <v>124749133</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3472,19 +3470,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706465</v>
+        <v>706364</v>
       </c>
       <c r="R25" t="n">
-        <v>7087346</v>
+        <v>7087314</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3511,54 +3513,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124739661</v>
+        <v>124749290</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3567,41 +3555,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705952</v>
+        <v>706276</v>
       </c>
       <c r="R26" t="n">
-        <v>7086928</v>
+        <v>7087213</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3628,19 +3624,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,22 +3641,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749263</v>
+        <v>124732613</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3679,45 +3665,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706282</v>
+        <v>706654</v>
       </c>
       <c r="R27" t="n">
-        <v>7087215</v>
+        <v>7087408</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3744,14 +3726,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,29 +3747,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124736627</v>
+        <v>124749263</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,41 +3777,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706292</v>
+        <v>706282</v>
       </c>
       <c r="R28" t="n">
-        <v>7087225</v>
+        <v>7087215</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3857,31 +3847,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124734648</v>
+        <v>124735830</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706405</v>
+        <v>706344</v>
       </c>
       <c r="R29" t="n">
-        <v>7087320</v>
+        <v>7087202</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3956,7 +3952,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3966,7 +3962,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3993,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124749575</v>
+        <v>124736627</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,45 +4001,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706133</v>
+        <v>706292</v>
       </c>
       <c r="R30" t="n">
-        <v>7087057</v>
+        <v>7087225</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4075,40 +4067,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749350</v>
+        <v>124732401</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4117,45 +4103,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706238</v>
+        <v>706665</v>
       </c>
       <c r="R31" t="n">
-        <v>7087154</v>
+        <v>7087406</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4182,14 +4164,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4198,29 +4185,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749111</v>
+        <v>124744220</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4229,31 +4215,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4261,10 +4255,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706398</v>
+        <v>706411</v>
       </c>
       <c r="R32" t="n">
-        <v>7087345</v>
+        <v>7087322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4299,18 +4293,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4329,7 +4317,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749331</v>
+        <v>124749376</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4373,10 +4361,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706228</v>
+        <v>706224</v>
       </c>
       <c r="R33" t="n">
-        <v>7087165</v>
+        <v>7087139</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4413,7 +4401,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4441,7 +4429,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749460</v>
+        <v>124734648</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4475,23 +4463,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706115</v>
+        <v>706405</v>
       </c>
       <c r="R34" t="n">
-        <v>7087088</v>
+        <v>7087320</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4518,14 +4502,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4534,26 +4523,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124749167</v>
+        <v>124739585</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4587,23 +4575,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706354</v>
+        <v>705944</v>
       </c>
       <c r="R35" t="n">
-        <v>7087195</v>
+        <v>7086954</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4630,14 +4614,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4646,29 +4635,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124732401</v>
+        <v>124734745</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4677,25 +4665,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4705,10 +4693,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706665</v>
+        <v>706401</v>
       </c>
       <c r="R36" t="n">
-        <v>7087406</v>
+        <v>7087323</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4740,7 +4728,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4750,7 +4738,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4777,7 +4770,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124739585</v>
+        <v>124749111</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4811,19 +4804,23 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705944</v>
+        <v>706398</v>
       </c>
       <c r="R37" t="n">
-        <v>7086954</v>
+        <v>7087345</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4850,19 +4847,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4871,28 +4863,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749070</v>
+        <v>124749686</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4901,31 +4894,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4933,10 +4925,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706442</v>
+        <v>705962</v>
       </c>
       <c r="R38" t="n">
-        <v>7087349</v>
+        <v>7086855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4969,11 +4961,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5001,10 +4988,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124739909</v>
+        <v>124733522</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5013,47 +5000,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706048</v>
+        <v>706523</v>
       </c>
       <c r="R39" t="n">
-        <v>7086914</v>
+        <v>7087364</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5083,9 +5061,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5100,19 +5088,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124735830</v>
+        <v>124734940</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5152,10 +5140,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706344</v>
+        <v>706418</v>
       </c>
       <c r="R40" t="n">
-        <v>7087202</v>
+        <v>7087323</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5185,19 +5173,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,19 +5190,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749086</v>
+        <v>124733393</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5258,23 +5236,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706447</v>
+        <v>706533</v>
       </c>
       <c r="R41" t="n">
-        <v>7087337</v>
+        <v>7087362</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5301,14 +5275,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5317,29 +5296,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124744220</v>
+        <v>124749246</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5348,39 +5326,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5388,10 +5358,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706411</v>
+        <v>706288</v>
       </c>
       <c r="R42" t="n">
-        <v>7087322</v>
+        <v>7087206</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5426,12 +5396,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5450,7 +5426,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124734940</v>
+        <v>124749331</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5484,19 +5460,23 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706418</v>
+        <v>706228</v>
       </c>
       <c r="R43" t="n">
-        <v>7087323</v>
+        <v>7087165</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5528,31 +5508,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749392</v>
+        <v>124749657</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5596,10 +5582,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706191</v>
+        <v>705966</v>
       </c>
       <c r="R44" t="n">
-        <v>7087129</v>
+        <v>7086987</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5664,10 +5650,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124739580</v>
+        <v>124737966</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5676,38 +5662,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706048</v>
+        <v>706281</v>
       </c>
       <c r="R45" t="n">
-        <v>7086914</v>
+        <v>7087219</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5766,7 +5761,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749184</v>
+        <v>124749167</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5810,10 +5805,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706340</v>
+        <v>706354</v>
       </c>
       <c r="R46" t="n">
-        <v>7087178</v>
+        <v>7087195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5878,7 +5873,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749013</v>
+        <v>124734081</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5912,23 +5907,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706446</v>
+        <v>706490</v>
       </c>
       <c r="R47" t="n">
-        <v>7087375</v>
+        <v>7087362</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5955,14 +5946,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5971,26 +5967,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749040</v>
+        <v>124749070</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6034,10 +6029,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706431</v>
+        <v>706442</v>
       </c>
       <c r="R48" t="n">
-        <v>7087362</v>
+        <v>7087349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6074,7 +6069,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6102,7 +6097,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749500</v>
+        <v>124749392</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6146,10 +6141,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706145</v>
+        <v>706191</v>
       </c>
       <c r="R49" t="n">
-        <v>7087098</v>
+        <v>7087129</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6214,10 +6209,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749376</v>
+        <v>124739580</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6226,45 +6221,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706224</v>
+        <v>706048</v>
       </c>
       <c r="R50" t="n">
-        <v>7087139</v>
+        <v>7086914</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6296,40 +6287,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124732613</v>
+        <v>124739909</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6338,38 +6323,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706654</v>
+        <v>706048</v>
       </c>
       <c r="R51" t="n">
-        <v>7087408</v>
+        <v>7086914</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6399,19 +6393,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6426,19 +6410,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124733393</v>
+        <v>124749500</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6472,19 +6456,23 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706533</v>
+        <v>706145</v>
       </c>
       <c r="R52" t="n">
-        <v>7087362</v>
+        <v>7087098</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6511,19 +6499,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6532,28 +6515,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124739096</v>
+        <v>124734381</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6562,25 +6546,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6590,10 +6574,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706304</v>
+        <v>706473</v>
       </c>
       <c r="R53" t="n">
-        <v>7087194</v>
+        <v>7087334</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6625,7 +6609,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6635,7 +6619,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6662,10 +6646,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124738318</v>
+        <v>124732683</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6674,25 +6658,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6702,10 +6686,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706281</v>
+        <v>706597</v>
       </c>
       <c r="R54" t="n">
-        <v>7087219</v>
+        <v>7087402</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6735,9 +6719,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6752,22 +6746,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749246</v>
+        <v>124734903</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6776,45 +6770,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706288</v>
+        <v>706371</v>
       </c>
       <c r="R55" t="n">
-        <v>7087206</v>
+        <v>7087353</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6841,14 +6831,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6857,29 +6852,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749539</v>
+        <v>124733886</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6888,45 +6882,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706157</v>
+        <v>706495</v>
       </c>
       <c r="R56" t="n">
-        <v>7087072</v>
+        <v>7087369</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6953,14 +6943,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6969,26 +6969,25 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124734745</v>
+        <v>124749184</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7022,19 +7021,23 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706401</v>
+        <v>706340</v>
       </c>
       <c r="R57" t="n">
-        <v>7087323</v>
+        <v>7087178</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7061,24 +7064,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7087,25 +7080,26 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124737518</v>
+        <v>124749575</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -7139,19 +7133,23 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706341</v>
+        <v>706133</v>
       </c>
       <c r="R58" t="n">
-        <v>7087207</v>
+        <v>7087057</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7178,19 +7176,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7199,25 +7192,26 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749133</v>
+        <v>124749040</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7261,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706364</v>
+        <v>706431</v>
       </c>
       <c r="R59" t="n">
-        <v>7087314</v>
+        <v>7087362</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7297,6 +7291,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7324,10 +7323,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124734381</v>
+        <v>124749414</v>
       </c>
       <c r="B60" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7336,41 +7335,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706473</v>
+        <v>706126</v>
       </c>
       <c r="R60" t="n">
-        <v>7087334</v>
+        <v>7087117</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7397,19 +7400,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,28 +7416,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749686</v>
+        <v>124734139</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7448,44 +7447,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705962</v>
+        <v>706472</v>
       </c>
       <c r="R61" t="n">
-        <v>7086855</v>
+        <v>7087356</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7512,40 +7508,54 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124733886</v>
+        <v>124749086</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7554,41 +7564,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706495</v>
+        <v>706447</v>
       </c>
       <c r="R62" t="n">
-        <v>7087369</v>
+        <v>7087337</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7615,24 +7629,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7641,18 +7645,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7761,10 +7766,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124732683</v>
+        <v>124738318</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7773,25 +7778,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7801,10 +7806,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706597</v>
+        <v>706281</v>
       </c>
       <c r="R64" t="n">
-        <v>7087402</v>
+        <v>7087219</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7834,19 +7839,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7861,22 +7856,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124733522</v>
+        <v>124749539</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,41 +7880,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706523</v>
+        <v>706157</v>
       </c>
       <c r="R65" t="n">
-        <v>7087364</v>
+        <v>7087072</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7946,19 +7945,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7967,25 +7961,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124734081</v>
+        <v>124734417</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8025,10 +8020,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706490</v>
+        <v>706465</v>
       </c>
       <c r="R66" t="n">
-        <v>7087362</v>
+        <v>7087346</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8060,7 +8055,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8070,7 +8065,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -3989,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124736627</v>
+        <v>124732401</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,21 +4005,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706292</v>
+        <v>706665</v>
       </c>
       <c r="R30" t="n">
-        <v>7087225</v>
+        <v>7087406</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4062,9 +4062,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,22 +4089,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124732401</v>
+        <v>124736627</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4107,21 +4117,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4131,10 +4141,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706665</v>
+        <v>706292</v>
       </c>
       <c r="R31" t="n">
-        <v>7087406</v>
+        <v>7087225</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4164,19 +4174,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,12 +4191,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124734139</v>
+        <v>124738318</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7447,25 +7447,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706472</v>
+        <v>706281</v>
       </c>
       <c r="R61" t="n">
-        <v>7087356</v>
+        <v>7087219</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7508,24 +7508,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7540,12 +7525,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7766,10 +7751,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124738318</v>
+        <v>124734139</v>
       </c>
       <c r="B64" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7778,25 +7763,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7806,10 +7791,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706281</v>
+        <v>706472</v>
       </c>
       <c r="R64" t="n">
-        <v>7087219</v>
+        <v>7087356</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7839,9 +7824,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7856,12 +7856,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -6646,10 +6646,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124732683</v>
+        <v>124749184</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6658,41 +6658,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706597</v>
+        <v>706340</v>
       </c>
       <c r="R54" t="n">
-        <v>7087402</v>
+        <v>7087178</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6719,19 +6723,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6740,28 +6739,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124734903</v>
+        <v>124749575</v>
       </c>
       <c r="B55" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6770,41 +6770,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706371</v>
+        <v>706133</v>
       </c>
       <c r="R55" t="n">
-        <v>7087353</v>
+        <v>7087057</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6831,19 +6835,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6852,18 +6851,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749184</v>
+        <v>124732683</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,45 +6999,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706340</v>
+        <v>706597</v>
       </c>
       <c r="R57" t="n">
-        <v>7087178</v>
+        <v>7087402</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7064,14 +7060,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7080,29 +7081,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749575</v>
+        <v>124734903</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7111,45 +7111,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706133</v>
+        <v>706371</v>
       </c>
       <c r="R58" t="n">
-        <v>7087057</v>
+        <v>7087353</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7176,14 +7172,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7192,19 +7193,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749350</v>
+        <v>124744220</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,31 +2664,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2704,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706238</v>
+        <v>706411</v>
       </c>
       <c r="R18" t="n">
-        <v>7087154</v>
+        <v>7087322</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,18 +2742,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2764,7 +2766,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124739661</v>
+        <v>124736752</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2797,17 +2799,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705952</v>
+        <v>706281</v>
       </c>
       <c r="R19" t="n">
-        <v>7086928</v>
+        <v>7087219</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2837,19 +2848,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2864,19 +2865,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124739096</v>
+        <v>124749263</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2910,19 +2911,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706304</v>
+        <v>706282</v>
       </c>
       <c r="R20" t="n">
-        <v>7087194</v>
+        <v>7087215</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2949,19 +2954,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2970,28 +2970,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749460</v>
+        <v>124732613</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,45 +3001,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706115</v>
+        <v>706654</v>
       </c>
       <c r="R21" t="n">
-        <v>7087088</v>
+        <v>7087408</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3065,14 +3062,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,26 +3083,25 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749013</v>
+        <v>124749414</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3144,10 +3145,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706446</v>
+        <v>706126</v>
       </c>
       <c r="R22" t="n">
-        <v>7087375</v>
+        <v>7087117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3184,7 +3185,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3212,7 +3213,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124737518</v>
+        <v>124749376</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3246,19 +3247,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706341</v>
+        <v>706224</v>
       </c>
       <c r="R23" t="n">
-        <v>7087207</v>
+        <v>7087139</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3285,19 +3290,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,28 +3306,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124739921</v>
+        <v>124734417</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3336,38 +3337,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706034</v>
+        <v>706465</v>
       </c>
       <c r="R24" t="n">
-        <v>7086918</v>
+        <v>7087346</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3399,7 +3400,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3409,7 +3410,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,7 +3442,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749133</v>
+        <v>124734745</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3470,23 +3476,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706364</v>
+        <v>706401</v>
       </c>
       <c r="R25" t="n">
-        <v>7087314</v>
+        <v>7087323</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3513,40 +3515,54 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124749290</v>
+        <v>124739661</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3555,49 +3571,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706276</v>
+        <v>705952</v>
       </c>
       <c r="R26" t="n">
-        <v>7087213</v>
+        <v>7086928</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3624,9 +3632,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,22 +3659,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124732613</v>
+        <v>124737518</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3665,25 +3683,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3693,10 +3711,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706654</v>
+        <v>706341</v>
       </c>
       <c r="R27" t="n">
-        <v>7087408</v>
+        <v>7087207</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3728,7 +3746,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3738,7 +3756,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,10 +3783,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749263</v>
+        <v>124738318</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3777,45 +3795,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706282</v>
+        <v>706281</v>
       </c>
       <c r="R28" t="n">
-        <v>7087215</v>
+        <v>7087219</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,40 +3861,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124735830</v>
+        <v>124736627</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,25 +3897,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3917,10 +3925,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706344</v>
+        <v>706292</v>
       </c>
       <c r="R29" t="n">
-        <v>7087202</v>
+        <v>7087225</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3950,19 +3958,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,12 +3975,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4101,10 +4099,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124736627</v>
+        <v>124739585</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4113,38 +4111,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706292</v>
+        <v>705944</v>
       </c>
       <c r="R31" t="n">
-        <v>7087225</v>
+        <v>7086954</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4174,9 +4172,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,22 +4199,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124744220</v>
+        <v>124734139</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4215,53 +4223,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706411</v>
+        <v>706472</v>
       </c>
       <c r="R32" t="n">
-        <v>7087322</v>
+        <v>7087356</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4288,9 +4284,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4305,19 +4316,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749376</v>
+        <v>124749133</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4361,10 +4372,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706224</v>
+        <v>706364</v>
       </c>
       <c r="R33" t="n">
-        <v>7087139</v>
+        <v>7087314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4397,11 +4408,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,7 +4435,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124734648</v>
+        <v>124749184</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4463,19 +4469,23 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706405</v>
+        <v>706340</v>
       </c>
       <c r="R34" t="n">
-        <v>7087320</v>
+        <v>7087178</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4502,19 +4512,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,25 +4528,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739585</v>
+        <v>124734648</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4577,14 +4583,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>705944</v>
+        <v>706405</v>
       </c>
       <c r="R35" t="n">
-        <v>7086954</v>
+        <v>7087320</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4616,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4626,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4653,7 +4659,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124734745</v>
+        <v>124749331</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4687,19 +4693,23 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706401</v>
+        <v>706228</v>
       </c>
       <c r="R36" t="n">
-        <v>7087323</v>
+        <v>7087165</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4726,24 +4736,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4752,25 +4752,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749111</v>
+        <v>124749657</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4814,10 +4815,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706398</v>
+        <v>705966</v>
       </c>
       <c r="R37" t="n">
-        <v>7087345</v>
+        <v>7086987</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,10 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749686</v>
+        <v>124749013</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4894,30 +4895,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4925,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705962</v>
+        <v>706446</v>
       </c>
       <c r="R38" t="n">
-        <v>7086855</v>
+        <v>7087375</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4961,6 +4963,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4988,10 +4995,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124733522</v>
+        <v>124749290</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5000,41 +5007,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706523</v>
+        <v>706276</v>
       </c>
       <c r="R39" t="n">
-        <v>7087364</v>
+        <v>7087213</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5061,19 +5076,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,22 +5093,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124734940</v>
+        <v>124734381</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5112,25 +5117,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5140,10 +5145,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706418</v>
+        <v>706473</v>
       </c>
       <c r="R40" t="n">
-        <v>7087323</v>
+        <v>7087334</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5173,9 +5178,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,12 +5205,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5314,7 +5329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749246</v>
+        <v>124749500</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5358,10 +5373,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706288</v>
+        <v>706145</v>
       </c>
       <c r="R42" t="n">
-        <v>7087206</v>
+        <v>7087098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5398,7 +5413,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,7 +5441,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749331</v>
+        <v>124749460</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5470,10 +5485,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706228</v>
+        <v>706115</v>
       </c>
       <c r="R43" t="n">
-        <v>7087165</v>
+        <v>7087088</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5510,7 +5525,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5538,7 +5553,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749657</v>
+        <v>124734940</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5572,23 +5587,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>705966</v>
+        <v>706418</v>
       </c>
       <c r="R44" t="n">
-        <v>7086987</v>
+        <v>7087323</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5620,37 +5631,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124737966</v>
+        <v>124749539</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5683,29 +5688,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706281</v>
+        <v>706157</v>
       </c>
       <c r="R45" t="n">
-        <v>7087219</v>
+        <v>7087072</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5737,34 +5737,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749167</v>
+        <v>124733886</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5773,45 +5779,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706354</v>
+        <v>706495</v>
       </c>
       <c r="R46" t="n">
-        <v>7087195</v>
+        <v>7087369</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5838,14 +5840,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5854,26 +5866,25 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124734081</v>
+        <v>124749392</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5907,19 +5918,23 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706490</v>
+        <v>706191</v>
       </c>
       <c r="R47" t="n">
-        <v>7087362</v>
+        <v>7087129</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5946,19 +5961,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5967,25 +5977,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749070</v>
+        <v>124749111</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6029,10 +6040,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706442</v>
+        <v>706398</v>
       </c>
       <c r="R48" t="n">
-        <v>7087349</v>
+        <v>7087345</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6097,7 +6108,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749392</v>
+        <v>124749086</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6141,10 +6152,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706191</v>
+        <v>706447</v>
       </c>
       <c r="R49" t="n">
-        <v>7087129</v>
+        <v>7087337</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6209,10 +6220,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124739580</v>
+        <v>124735169</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6225,34 +6236,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706048</v>
+        <v>706394</v>
       </c>
       <c r="R50" t="n">
-        <v>7086914</v>
+        <v>7087340</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6311,10 +6322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124739909</v>
+        <v>124749686</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6323,50 +6334,44 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706048</v>
+        <v>705962</v>
       </c>
       <c r="R51" t="n">
-        <v>7086914</v>
+        <v>7086855</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6404,25 +6409,26 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749500</v>
+        <v>124735830</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6456,23 +6462,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706145</v>
+        <v>706344</v>
       </c>
       <c r="R52" t="n">
-        <v>7087098</v>
+        <v>7087202</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6499,14 +6501,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6515,29 +6522,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124734381</v>
+        <v>124749070</v>
       </c>
       <c r="B53" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6546,41 +6552,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706473</v>
+        <v>706442</v>
       </c>
       <c r="R53" t="n">
-        <v>7087334</v>
+        <v>7087349</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6607,19 +6617,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6628,25 +6633,26 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749184</v>
+        <v>124749575</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6690,10 +6696,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706340</v>
+        <v>706133</v>
       </c>
       <c r="R54" t="n">
-        <v>7087178</v>
+        <v>7087057</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6758,7 +6764,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749575</v>
+        <v>124749167</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6802,10 +6808,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706133</v>
+        <v>706354</v>
       </c>
       <c r="R55" t="n">
-        <v>7087057</v>
+        <v>7087195</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6870,10 +6876,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124733886</v>
+        <v>124749350</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6882,41 +6888,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706495</v>
+        <v>706238</v>
       </c>
       <c r="R56" t="n">
-        <v>7087369</v>
+        <v>7087154</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6943,24 +6953,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6969,28 +6969,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124732683</v>
+        <v>124733522</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7003,21 +7004,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7027,10 +7028,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706597</v>
+        <v>706523</v>
       </c>
       <c r="R57" t="n">
-        <v>7087402</v>
+        <v>7087364</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7062,7 +7063,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7072,7 +7073,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7099,10 +7100,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124734903</v>
+        <v>124739580</v>
       </c>
       <c r="B58" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7111,38 +7112,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706371</v>
+        <v>706048</v>
       </c>
       <c r="R58" t="n">
-        <v>7087353</v>
+        <v>7086914</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7172,19 +7173,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7199,19 +7190,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749040</v>
+        <v>124749246</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7255,10 +7246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706431</v>
+        <v>706288</v>
       </c>
       <c r="R59" t="n">
-        <v>7087362</v>
+        <v>7087206</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7295,7 +7286,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7323,10 +7314,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749414</v>
+        <v>124734903</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7335,45 +7326,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706126</v>
+        <v>706371</v>
       </c>
       <c r="R60" t="n">
-        <v>7087117</v>
+        <v>7087353</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,14 +7387,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7416,29 +7408,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124738318</v>
+        <v>124749040</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7447,41 +7438,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706281</v>
+        <v>706431</v>
       </c>
       <c r="R61" t="n">
-        <v>7087219</v>
+        <v>7087362</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7513,31 +7508,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749086</v>
+        <v>124734081</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7571,23 +7572,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706447</v>
+        <v>706490</v>
       </c>
       <c r="R62" t="n">
-        <v>7087337</v>
+        <v>7087362</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7614,14 +7611,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7630,29 +7632,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124735169</v>
+        <v>124739909</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7661,38 +7662,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706394</v>
+        <v>706048</v>
       </c>
       <c r="R63" t="n">
-        <v>7087340</v>
+        <v>7086914</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7751,10 +7761,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124734139</v>
+        <v>124739921</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7763,38 +7773,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706472</v>
+        <v>706034</v>
       </c>
       <c r="R64" t="n">
-        <v>7087356</v>
+        <v>7086918</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7826,7 +7836,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7836,12 +7846,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7868,10 +7873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749539</v>
+        <v>124732683</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7880,45 +7885,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706157</v>
+        <v>706597</v>
       </c>
       <c r="R65" t="n">
-        <v>7087072</v>
+        <v>7087402</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7945,14 +7946,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7961,26 +7967,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124734417</v>
+        <v>124739096</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8020,10 +8025,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706465</v>
+        <v>706304</v>
       </c>
       <c r="R66" t="n">
-        <v>7087346</v>
+        <v>7087194</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8055,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8065,12 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124744220</v>
+        <v>124749133</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,39 +2664,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2704,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706411</v>
+        <v>706364</v>
       </c>
       <c r="R18" t="n">
-        <v>7087322</v>
+        <v>7087314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2748,6 +2740,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2766,7 +2759,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124736752</v>
+        <v>124734940</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2799,26 +2792,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706281</v>
+        <v>706418</v>
       </c>
       <c r="R19" t="n">
-        <v>7087219</v>
+        <v>7087323</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2877,7 +2861,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749263</v>
+        <v>124749040</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2921,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706282</v>
+        <v>706431</v>
       </c>
       <c r="R20" t="n">
-        <v>7087215</v>
+        <v>7087362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2961,7 +2945,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2989,10 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124732613</v>
+        <v>124749500</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3001,41 +2985,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706654</v>
+        <v>706145</v>
       </c>
       <c r="R21" t="n">
-        <v>7087408</v>
+        <v>7087098</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3062,19 +3050,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3083,25 +3066,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749414</v>
+        <v>124734081</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3135,23 +3119,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706126</v>
+        <v>706490</v>
       </c>
       <c r="R22" t="n">
-        <v>7087117</v>
+        <v>7087362</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3178,14 +3158,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3194,26 +3179,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749376</v>
+        <v>124737966</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3246,24 +3230,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706224</v>
+        <v>706281</v>
       </c>
       <c r="R23" t="n">
-        <v>7087139</v>
+        <v>7087219</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3295,37 +3284,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124734417</v>
+        <v>124734648</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3365,10 +3348,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706465</v>
+        <v>706405</v>
       </c>
       <c r="R24" t="n">
-        <v>7087346</v>
+        <v>7087320</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3400,7 +3383,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3410,12 +3393,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3442,7 +3420,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734745</v>
+        <v>124734417</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3482,10 +3460,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706401</v>
+        <v>706465</v>
       </c>
       <c r="R25" t="n">
-        <v>7087323</v>
+        <v>7087346</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3517,7 +3495,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3527,7 +3505,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3559,10 +3537,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124739661</v>
+        <v>124734903</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3571,38 +3549,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705952</v>
+        <v>706371</v>
       </c>
       <c r="R26" t="n">
-        <v>7086928</v>
+        <v>7087353</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3634,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3644,7 +3622,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3671,10 +3649,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124737518</v>
+        <v>124732613</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3683,25 +3661,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3711,10 +3689,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706341</v>
+        <v>706654</v>
       </c>
       <c r="R27" t="n">
-        <v>7087207</v>
+        <v>7087408</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3746,7 +3724,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3756,7 +3734,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3783,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124738318</v>
+        <v>124749657</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3795,41 +3773,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706281</v>
+        <v>705966</v>
       </c>
       <c r="R28" t="n">
-        <v>7087219</v>
+        <v>7086987</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3861,34 +3843,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124736627</v>
+        <v>124749111</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,41 +3885,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706292</v>
+        <v>706398</v>
       </c>
       <c r="R29" t="n">
-        <v>7087225</v>
+        <v>7087345</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3963,31 +3955,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732401</v>
+        <v>124732683</v>
       </c>
       <c r="B30" t="n">
         <v>91012</v>
@@ -4027,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706665</v>
+        <v>706597</v>
       </c>
       <c r="R30" t="n">
-        <v>7087406</v>
+        <v>7087402</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4062,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4072,7 +4070,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4099,7 +4097,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124739585</v>
+        <v>124739909</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4132,17 +4130,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705944</v>
+        <v>706048</v>
       </c>
       <c r="R31" t="n">
-        <v>7086954</v>
+        <v>7086914</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4172,19 +4179,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4199,19 +4196,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124734139</v>
+        <v>124749184</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4245,19 +4242,23 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706472</v>
+        <v>706340</v>
       </c>
       <c r="R32" t="n">
-        <v>7087356</v>
+        <v>7087178</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4284,24 +4285,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4310,25 +4301,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749133</v>
+        <v>124749575</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4372,10 +4364,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706364</v>
+        <v>706133</v>
       </c>
       <c r="R33" t="n">
-        <v>7087314</v>
+        <v>7087057</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,6 +4400,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4435,7 +4432,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749184</v>
+        <v>124749414</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4479,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706340</v>
+        <v>706126</v>
       </c>
       <c r="R34" t="n">
-        <v>7087178</v>
+        <v>7087117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4547,10 +4544,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124734648</v>
+        <v>124735169</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4559,25 +4556,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4584,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706405</v>
+        <v>706394</v>
       </c>
       <c r="R35" t="n">
-        <v>7087320</v>
+        <v>7087340</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4620,19 +4617,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4647,22 +4634,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124749331</v>
+        <v>124749686</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,31 +4658,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4703,10 +4689,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706228</v>
+        <v>705962</v>
       </c>
       <c r="R36" t="n">
-        <v>7087165</v>
+        <v>7086855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4739,11 +4725,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,7 +4752,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749657</v>
+        <v>124739585</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4805,23 +4786,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705966</v>
+        <v>705944</v>
       </c>
       <c r="R37" t="n">
-        <v>7086987</v>
+        <v>7086954</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4848,14 +4825,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4864,29 +4846,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749013</v>
+        <v>124733522</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4895,45 +4876,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706446</v>
+        <v>706523</v>
       </c>
       <c r="R38" t="n">
-        <v>7087375</v>
+        <v>7087364</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4960,14 +4937,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4976,29 +4958,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749290</v>
+        <v>124733393</v>
       </c>
       <c r="B39" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5007,49 +4988,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706276</v>
+        <v>706533</v>
       </c>
       <c r="R39" t="n">
-        <v>7087213</v>
+        <v>7087362</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5076,9 +5049,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5093,22 +5076,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124734381</v>
+        <v>124749263</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5117,41 +5100,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706473</v>
+        <v>706282</v>
       </c>
       <c r="R40" t="n">
-        <v>7087334</v>
+        <v>7087215</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5178,19 +5165,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,25 +5181,26 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124733393</v>
+        <v>124749167</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5251,19 +5234,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706533</v>
+        <v>706354</v>
       </c>
       <c r="R41" t="n">
-        <v>7087362</v>
+        <v>7087195</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5290,19 +5277,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,25 +5293,26 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749500</v>
+        <v>124734139</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5363,23 +5346,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706145</v>
+        <v>706472</v>
       </c>
       <c r="R42" t="n">
-        <v>7087098</v>
+        <v>7087356</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5406,14 +5385,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5422,29 +5411,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749460</v>
+        <v>124733886</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5453,45 +5441,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706115</v>
+        <v>706495</v>
       </c>
       <c r="R43" t="n">
-        <v>7087088</v>
+        <v>7087369</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5518,14 +5502,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5534,26 +5528,25 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124734940</v>
+        <v>124749376</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5587,19 +5580,23 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706418</v>
+        <v>706224</v>
       </c>
       <c r="R44" t="n">
-        <v>7087323</v>
+        <v>7087139</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5631,31 +5628,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749539</v>
+        <v>124749460</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5699,10 +5702,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706157</v>
+        <v>706115</v>
       </c>
       <c r="R45" t="n">
-        <v>7087072</v>
+        <v>7087088</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5739,7 +5742,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5767,10 +5770,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124733886</v>
+        <v>124735830</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5779,25 +5782,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5807,10 +5810,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706495</v>
+        <v>706344</v>
       </c>
       <c r="R46" t="n">
-        <v>7087369</v>
+        <v>7087202</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5842,7 +5845,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5852,12 +5855,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5884,7 +5882,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749392</v>
+        <v>124749350</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5928,10 +5926,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706191</v>
+        <v>706238</v>
       </c>
       <c r="R47" t="n">
-        <v>7087129</v>
+        <v>7087154</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5968,7 +5966,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5996,7 +5994,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749111</v>
+        <v>124749013</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6040,10 +6038,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706398</v>
+        <v>706446</v>
       </c>
       <c r="R48" t="n">
-        <v>7087345</v>
+        <v>7087375</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6080,7 +6078,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6108,7 +6106,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749086</v>
+        <v>124749246</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6152,10 +6150,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706447</v>
+        <v>706288</v>
       </c>
       <c r="R49" t="n">
-        <v>7087337</v>
+        <v>7087206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6192,7 +6190,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6220,10 +6218,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124735169</v>
+        <v>124738318</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,25 +6230,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6260,10 +6258,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706394</v>
+        <v>706281</v>
       </c>
       <c r="R50" t="n">
-        <v>7087340</v>
+        <v>7087219</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6322,7 +6320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749686</v>
+        <v>124732401</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -6356,22 +6354,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>705962</v>
+        <v>706665</v>
       </c>
       <c r="R51" t="n">
-        <v>7086855</v>
+        <v>7087406</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6398,40 +6393,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124735830</v>
+        <v>124736627</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6440,25 +6444,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6472,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706344</v>
+        <v>706292</v>
       </c>
       <c r="R52" t="n">
-        <v>7087202</v>
+        <v>7087225</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6501,19 +6505,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6528,19 +6522,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749070</v>
+        <v>124739661</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6574,23 +6568,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706442</v>
+        <v>705952</v>
       </c>
       <c r="R53" t="n">
-        <v>7087349</v>
+        <v>7086928</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6617,14 +6607,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6633,26 +6628,25 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749575</v>
+        <v>124739096</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6686,23 +6680,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706133</v>
+        <v>706304</v>
       </c>
       <c r="R54" t="n">
-        <v>7087057</v>
+        <v>7087194</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6729,14 +6719,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6745,26 +6740,25 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749167</v>
+        <v>124749331</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6808,10 +6802,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706354</v>
+        <v>706228</v>
       </c>
       <c r="R55" t="n">
-        <v>7087195</v>
+        <v>7087165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6848,7 +6842,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6876,7 +6870,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749350</v>
+        <v>124737518</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6910,23 +6904,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706238</v>
+        <v>706341</v>
       </c>
       <c r="R56" t="n">
-        <v>7087154</v>
+        <v>7087207</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6953,14 +6943,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6969,26 +6964,25 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124733522</v>
+        <v>124734381</v>
       </c>
       <c r="B57" t="n">
         <v>57529</v>
@@ -7028,10 +7022,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706523</v>
+        <v>706473</v>
       </c>
       <c r="R57" t="n">
-        <v>7087364</v>
+        <v>7087334</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7063,7 +7057,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7073,7 +7067,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7100,10 +7094,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124739580</v>
+        <v>124749392</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7112,41 +7106,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706048</v>
+        <v>706191</v>
       </c>
       <c r="R58" t="n">
-        <v>7086914</v>
+        <v>7087129</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7178,31 +7176,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749246</v>
+        <v>124749070</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7246,10 +7250,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706288</v>
+        <v>706442</v>
       </c>
       <c r="R59" t="n">
-        <v>7087206</v>
+        <v>7087349</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7286,7 +7290,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7314,10 +7318,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124734903</v>
+        <v>124744220</v>
       </c>
       <c r="B60" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7330,37 +7334,49 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706371</v>
+        <v>706411</v>
       </c>
       <c r="R60" t="n">
-        <v>7087353</v>
+        <v>7087322</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7387,19 +7403,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7414,19 +7420,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749040</v>
+        <v>124734745</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7460,23 +7466,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706431</v>
+        <v>706401</v>
       </c>
       <c r="R61" t="n">
-        <v>7087362</v>
+        <v>7087323</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7503,14 +7505,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7519,26 +7531,25 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124734081</v>
+        <v>124749086</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7572,19 +7583,23 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706490</v>
+        <v>706447</v>
       </c>
       <c r="R62" t="n">
-        <v>7087362</v>
+        <v>7087337</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7611,19 +7626,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7632,25 +7642,26 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124739909</v>
+        <v>124749539</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7683,29 +7694,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706048</v>
+        <v>706157</v>
       </c>
       <c r="R63" t="n">
-        <v>7086914</v>
+        <v>7087072</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7737,34 +7743,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124739921</v>
+        <v>124749290</v>
       </c>
       <c r="B64" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7777,37 +7789,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706034</v>
+        <v>706276</v>
       </c>
       <c r="R64" t="n">
-        <v>7086918</v>
+        <v>7087213</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7834,19 +7854,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7861,22 +7871,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124732683</v>
+        <v>124739580</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7889,34 +7899,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706597</v>
+        <v>706048</v>
       </c>
       <c r="R65" t="n">
-        <v>7087402</v>
+        <v>7086914</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7946,19 +7956,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7973,22 +7973,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124739096</v>
+        <v>124739921</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,38 +7997,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706304</v>
+        <v>706034</v>
       </c>
       <c r="R66" t="n">
-        <v>7087194</v>
+        <v>7086918</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -3197,7 +3197,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124737966</v>
+        <v>124734648</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3230,26 +3230,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706281</v>
+        <v>706405</v>
       </c>
       <c r="R23" t="n">
-        <v>7087219</v>
+        <v>7087320</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3279,9 +3270,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,19 +3297,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124734648</v>
+        <v>124734417</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3348,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706405</v>
+        <v>706465</v>
       </c>
       <c r="R24" t="n">
-        <v>7087320</v>
+        <v>7087346</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3383,7 +3384,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3393,7 +3394,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3420,7 +3426,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734417</v>
+        <v>124737966</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3453,17 +3459,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706465</v>
+        <v>706281</v>
       </c>
       <c r="R25" t="n">
-        <v>7087346</v>
+        <v>7087219</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3493,24 +3508,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3525,12 +3525,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124735169</v>
+        <v>124749686</v>
       </c>
       <c r="B35" t="n">
         <v>91012</v>
@@ -4578,19 +4578,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706394</v>
+        <v>705962</v>
       </c>
       <c r="R35" t="n">
-        <v>7087340</v>
+        <v>7086855</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4628,25 +4631,26 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124749686</v>
+        <v>124735169</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4680,22 +4684,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705962</v>
+        <v>706394</v>
       </c>
       <c r="R36" t="n">
-        <v>7086855</v>
+        <v>7087340</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4733,19 +4734,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749263</v>
+        <v>124749167</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706282</v>
+        <v>706354</v>
       </c>
       <c r="R40" t="n">
-        <v>7087215</v>
+        <v>7087195</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749167</v>
+        <v>124734139</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5234,23 +5234,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706354</v>
+        <v>706472</v>
       </c>
       <c r="R41" t="n">
-        <v>7087195</v>
+        <v>7087356</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5277,14 +5273,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,26 +5299,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124734139</v>
+        <v>124749263</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5346,19 +5351,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706472</v>
+        <v>706282</v>
       </c>
       <c r="R42" t="n">
-        <v>7087356</v>
+        <v>7087215</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5385,24 +5394,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5411,18 +5410,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124738318</v>
+        <v>124736627</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6230,25 +6230,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706281</v>
+        <v>706292</v>
       </c>
       <c r="R50" t="n">
-        <v>7087219</v>
+        <v>7087225</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124732401</v>
+        <v>124738318</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6332,25 +6332,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706665</v>
+        <v>706281</v>
       </c>
       <c r="R51" t="n">
-        <v>7087406</v>
+        <v>7087219</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6393,19 +6393,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6420,22 +6410,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124736627</v>
+        <v>124732401</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,21 +6438,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6462,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706292</v>
+        <v>706665</v>
       </c>
       <c r="R52" t="n">
-        <v>7087225</v>
+        <v>7087406</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6505,9 +6495,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6522,12 +6522,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124734381</v>
+        <v>124749392</v>
       </c>
       <c r="B57" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6994,41 +6994,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706473</v>
+        <v>706191</v>
       </c>
       <c r="R57" t="n">
-        <v>7087334</v>
+        <v>7087129</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7055,19 +7059,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7076,25 +7075,26 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749392</v>
+        <v>124749070</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706191</v>
+        <v>706442</v>
       </c>
       <c r="R58" t="n">
-        <v>7087129</v>
+        <v>7087349</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7206,10 +7206,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749070</v>
+        <v>124734381</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7218,45 +7218,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706442</v>
+        <v>706473</v>
       </c>
       <c r="R59" t="n">
-        <v>7087349</v>
+        <v>7087334</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7283,14 +7279,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7299,26 +7300,25 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124744220</v>
+        <v>124749290</v>
       </c>
       <c r="B60" t="n">
         <v>56722</v>
@@ -7351,18 +7351,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7370,10 +7366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706411</v>
+        <v>706276</v>
       </c>
       <c r="R60" t="n">
-        <v>7087322</v>
+        <v>7087213</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7432,10 +7428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124734745</v>
+        <v>124744220</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7444,41 +7440,53 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706401</v>
+        <v>706411</v>
       </c>
       <c r="R61" t="n">
-        <v>7087323</v>
+        <v>7087322</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7505,24 +7513,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7537,19 +7530,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749086</v>
+        <v>124734745</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7583,23 +7576,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706447</v>
+        <v>706401</v>
       </c>
       <c r="R62" t="n">
-        <v>7087337</v>
+        <v>7087323</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7626,14 +7615,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7642,26 +7641,25 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749539</v>
+        <v>124749086</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7705,10 +7703,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706157</v>
+        <v>706447</v>
       </c>
       <c r="R63" t="n">
-        <v>7087072</v>
+        <v>7087337</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7773,10 +7771,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124749290</v>
+        <v>124749539</v>
       </c>
       <c r="B64" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7785,35 +7783,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7821,10 +7815,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706276</v>
+        <v>706157</v>
       </c>
       <c r="R64" t="n">
-        <v>7087213</v>
+        <v>7087072</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7859,12 +7853,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124739580</v>
+        <v>124739921</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7895,25 +7895,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706048</v>
+        <v>706034</v>
       </c>
       <c r="R65" t="n">
-        <v>7086914</v>
+        <v>7086918</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7956,9 +7956,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7973,22 +7983,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124739921</v>
+        <v>124739580</v>
       </c>
       <c r="B66" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,25 +8007,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8025,10 +8035,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706034</v>
+        <v>706048</v>
       </c>
       <c r="R66" t="n">
-        <v>7086918</v>
+        <v>7086914</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8058,19 +8068,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8085,12 +8085,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749133</v>
+        <v>124749686</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,31 +2664,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2696,10 +2695,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706364</v>
+        <v>705962</v>
       </c>
       <c r="R18" t="n">
-        <v>7087314</v>
+        <v>7086855</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2759,10 +2758,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124734940</v>
+        <v>124732683</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,25 +2770,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2799,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706418</v>
+        <v>706597</v>
       </c>
       <c r="R19" t="n">
-        <v>7087323</v>
+        <v>7087402</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2832,9 +2831,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2849,19 +2858,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749040</v>
+        <v>124736752</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2894,24 +2903,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706431</v>
+        <v>706281</v>
       </c>
       <c r="R20" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2943,37 +2957,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749500</v>
+        <v>124734745</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3007,23 +3015,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706145</v>
+        <v>706401</v>
       </c>
       <c r="R21" t="n">
-        <v>7087098</v>
+        <v>7087323</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3050,14 +3054,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,19 +3080,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3197,7 +3210,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124734648</v>
+        <v>124749070</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3231,19 +3244,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706405</v>
+        <v>706442</v>
       </c>
       <c r="R23" t="n">
-        <v>7087320</v>
+        <v>7087349</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3270,19 +3287,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3291,25 +3303,26 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124734417</v>
+        <v>124749539</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3343,19 +3356,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706465</v>
+        <v>706157</v>
       </c>
       <c r="R24" t="n">
-        <v>7087346</v>
+        <v>7087072</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3382,24 +3399,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,28 +3415,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124737966</v>
+        <v>124733522</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3438,47 +3446,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706281</v>
+        <v>706523</v>
       </c>
       <c r="R25" t="n">
-        <v>7087219</v>
+        <v>7087364</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3508,9 +3507,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3525,22 +3534,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124734903</v>
+        <v>124736627</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,25 +3558,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3577,10 +3586,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706371</v>
+        <v>706292</v>
       </c>
       <c r="R26" t="n">
-        <v>7087353</v>
+        <v>7087225</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3610,19 +3619,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3637,22 +3636,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124732613</v>
+        <v>124749246</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3661,41 +3660,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706654</v>
+        <v>706288</v>
       </c>
       <c r="R27" t="n">
-        <v>7087408</v>
+        <v>7087206</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3722,19 +3725,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3743,25 +3741,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749657</v>
+        <v>124749350</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3805,10 +3804,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>705966</v>
+        <v>706238</v>
       </c>
       <c r="R28" t="n">
-        <v>7086987</v>
+        <v>7087154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3845,7 +3844,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,7 +3872,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749111</v>
+        <v>124734940</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3907,23 +3906,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706398</v>
+        <v>706418</v>
       </c>
       <c r="R29" t="n">
-        <v>7087345</v>
+        <v>7087323</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3955,40 +3950,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732683</v>
+        <v>124749414</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3997,41 +3986,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706597</v>
+        <v>706126</v>
       </c>
       <c r="R30" t="n">
-        <v>7087402</v>
+        <v>7087117</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4058,19 +4051,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,25 +4067,26 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124739909</v>
+        <v>124749167</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4130,29 +4119,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706048</v>
+        <v>706354</v>
       </c>
       <c r="R31" t="n">
-        <v>7086914</v>
+        <v>7087195</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4184,34 +4168,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749184</v>
+        <v>124732613</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4220,45 +4210,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706340</v>
+        <v>706654</v>
       </c>
       <c r="R32" t="n">
-        <v>7087178</v>
+        <v>7087408</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4285,14 +4271,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4301,19 +4292,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4432,10 +4422,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749414</v>
+        <v>124733886</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,45 +4434,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706126</v>
+        <v>706495</v>
       </c>
       <c r="R34" t="n">
-        <v>7087117</v>
+        <v>7087369</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4509,14 +4495,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4525,29 +4521,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124749686</v>
+        <v>124749376</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4556,30 +4551,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4587,10 +4583,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>705962</v>
+        <v>706224</v>
       </c>
       <c r="R35" t="n">
-        <v>7086855</v>
+        <v>7087139</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4623,6 +4619,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,10 +4651,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124735169</v>
+        <v>124739909</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4662,38 +4663,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706394</v>
+        <v>706048</v>
       </c>
       <c r="R36" t="n">
-        <v>7087340</v>
+        <v>7086914</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4752,7 +4762,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124739585</v>
+        <v>124749460</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4786,19 +4796,23 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705944</v>
+        <v>706115</v>
       </c>
       <c r="R37" t="n">
-        <v>7086954</v>
+        <v>7087088</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4825,19 +4839,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4846,28 +4855,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124733522</v>
+        <v>124739661</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4876,38 +4886,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706523</v>
+        <v>705952</v>
       </c>
       <c r="R38" t="n">
-        <v>7087364</v>
+        <v>7086928</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4939,7 +4949,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4949,7 +4959,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4976,7 +4986,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124733393</v>
+        <v>124749184</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5010,19 +5020,23 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706533</v>
+        <v>706340</v>
       </c>
       <c r="R39" t="n">
-        <v>7087362</v>
+        <v>7087178</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5049,19 +5063,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5070,25 +5079,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749167</v>
+        <v>124739096</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5122,23 +5132,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706354</v>
+        <v>706304</v>
       </c>
       <c r="R40" t="n">
-        <v>7087195</v>
+        <v>7087194</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5165,14 +5171,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,26 +5192,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124734139</v>
+        <v>124749263</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5234,19 +5244,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706472</v>
+        <v>706282</v>
       </c>
       <c r="R41" t="n">
-        <v>7087356</v>
+        <v>7087215</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5273,24 +5287,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5299,28 +5303,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749263</v>
+        <v>124749290</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5329,31 +5334,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5361,10 +5370,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706282</v>
+        <v>706276</v>
       </c>
       <c r="R42" t="n">
-        <v>7087215</v>
+        <v>7087213</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,18 +5408,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5429,10 +5432,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124733886</v>
+        <v>124734381</v>
       </c>
       <c r="B43" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5441,25 +5444,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5469,10 +5472,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706495</v>
+        <v>706473</v>
       </c>
       <c r="R43" t="n">
-        <v>7087369</v>
+        <v>7087334</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5504,7 +5507,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5514,12 +5517,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5546,7 +5544,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749376</v>
+        <v>124739585</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5580,23 +5578,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706224</v>
+        <v>705944</v>
       </c>
       <c r="R44" t="n">
-        <v>7087139</v>
+        <v>7086954</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5623,14 +5617,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5639,26 +5638,25 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749460</v>
+        <v>124749111</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5702,10 +5700,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706115</v>
+        <v>706398</v>
       </c>
       <c r="R45" t="n">
-        <v>7087088</v>
+        <v>7087345</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5742,7 +5740,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5770,7 +5768,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124735830</v>
+        <v>124749657</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5804,19 +5802,23 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706344</v>
+        <v>705966</v>
       </c>
       <c r="R46" t="n">
-        <v>7087202</v>
+        <v>7086987</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5843,19 +5845,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5864,28 +5861,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749350</v>
+        <v>124738318</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5894,45 +5892,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706238</v>
+        <v>706281</v>
       </c>
       <c r="R47" t="n">
-        <v>7087154</v>
+        <v>7087219</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5964,40 +5958,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749013</v>
+        <v>124734903</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6006,45 +5994,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706446</v>
+        <v>706371</v>
       </c>
       <c r="R48" t="n">
-        <v>7087375</v>
+        <v>7087353</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6071,14 +6055,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,26 +6076,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749246</v>
+        <v>124734139</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6140,23 +6128,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706288</v>
+        <v>706472</v>
       </c>
       <c r="R49" t="n">
-        <v>7087206</v>
+        <v>7087356</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6183,14 +6167,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6199,29 +6193,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124736627</v>
+        <v>124749013</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6230,41 +6223,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706292</v>
+        <v>706446</v>
       </c>
       <c r="R50" t="n">
-        <v>7087225</v>
+        <v>7087375</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6296,34 +6293,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124738318</v>
+        <v>124739921</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6336,34 +6339,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706281</v>
+        <v>706034</v>
       </c>
       <c r="R51" t="n">
-        <v>7087219</v>
+        <v>7086918</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6393,9 +6396,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6410,22 +6423,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124732401</v>
+        <v>124749086</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6434,41 +6447,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706665</v>
+        <v>706447</v>
       </c>
       <c r="R52" t="n">
-        <v>7087406</v>
+        <v>7087337</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6495,19 +6512,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6516,25 +6528,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124739661</v>
+        <v>124737518</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6570,14 +6583,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705952</v>
+        <v>706341</v>
       </c>
       <c r="R53" t="n">
-        <v>7086928</v>
+        <v>7087207</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6609,7 +6622,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6619,7 +6632,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6646,7 +6659,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124739096</v>
+        <v>124749040</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6680,19 +6693,23 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706304</v>
+        <v>706431</v>
       </c>
       <c r="R54" t="n">
-        <v>7087194</v>
+        <v>7087362</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6719,19 +6736,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6740,25 +6752,26 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749331</v>
+        <v>124749133</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6802,10 +6815,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706228</v>
+        <v>706364</v>
       </c>
       <c r="R55" t="n">
-        <v>7087165</v>
+        <v>7087314</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6838,11 +6851,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6870,10 +6878,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124737518</v>
+        <v>124744220</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6882,41 +6890,53 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706341</v>
+        <v>706411</v>
       </c>
       <c r="R56" t="n">
-        <v>7087207</v>
+        <v>7087322</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6943,19 +6963,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6970,19 +6980,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749392</v>
+        <v>124749331</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7026,10 +7036,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706191</v>
+        <v>706228</v>
       </c>
       <c r="R57" t="n">
-        <v>7087129</v>
+        <v>7087165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7066,7 +7076,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7094,7 +7104,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749070</v>
+        <v>124734648</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -7128,23 +7138,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706442</v>
+        <v>706405</v>
       </c>
       <c r="R58" t="n">
-        <v>7087349</v>
+        <v>7087320</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7171,14 +7177,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7187,29 +7198,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124734381</v>
+        <v>124733393</v>
       </c>
       <c r="B59" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7218,25 +7228,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7246,10 +7256,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706473</v>
+        <v>706533</v>
       </c>
       <c r="R59" t="n">
-        <v>7087334</v>
+        <v>7087362</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7281,7 +7291,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7291,7 +7301,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7318,10 +7328,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749290</v>
+        <v>124749392</v>
       </c>
       <c r="B60" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7330,35 +7340,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7366,10 +7372,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706276</v>
+        <v>706191</v>
       </c>
       <c r="R60" t="n">
-        <v>7087213</v>
+        <v>7087129</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7404,12 +7410,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7428,10 +7440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124744220</v>
+        <v>124734417</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7440,53 +7452,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706411</v>
+        <v>706465</v>
       </c>
       <c r="R61" t="n">
-        <v>7087322</v>
+        <v>7087346</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7513,9 +7513,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7530,19 +7545,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124734745</v>
+        <v>124749500</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7576,19 +7591,23 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706401</v>
+        <v>706145</v>
       </c>
       <c r="R62" t="n">
-        <v>7087323</v>
+        <v>7087098</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7615,24 +7634,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7641,25 +7650,26 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749086</v>
+        <v>124735830</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7693,23 +7703,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706447</v>
+        <v>706344</v>
       </c>
       <c r="R63" t="n">
-        <v>7087337</v>
+        <v>7087202</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7736,14 +7742,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7752,29 +7763,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124749539</v>
+        <v>124732401</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7783,45 +7793,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706157</v>
+        <v>706665</v>
       </c>
       <c r="R64" t="n">
-        <v>7087072</v>
+        <v>7087406</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7848,14 +7854,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7864,29 +7875,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124739921</v>
+        <v>124735169</v>
       </c>
       <c r="B65" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7895,38 +7905,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706034</v>
+        <v>706394</v>
       </c>
       <c r="R65" t="n">
-        <v>7086918</v>
+        <v>7087340</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7956,19 +7966,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7983,12 +7983,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -3546,10 +3546,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124736627</v>
+        <v>124749246</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3558,41 +3558,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706292</v>
+        <v>706288</v>
       </c>
       <c r="R26" t="n">
-        <v>7087225</v>
+        <v>7087206</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3624,31 +3628,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749246</v>
+        <v>124749350</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3692,10 +3702,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706288</v>
+        <v>706238</v>
       </c>
       <c r="R27" t="n">
-        <v>7087206</v>
+        <v>7087154</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3732,7 +3742,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,10 +3770,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749350</v>
+        <v>124736627</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3772,45 +3782,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706238</v>
+        <v>706292</v>
       </c>
       <c r="R28" t="n">
-        <v>7087154</v>
+        <v>7087225</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3842,30 +3848,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749686</v>
+        <v>124734139</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,44 +2664,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705962</v>
+        <v>706472</v>
       </c>
       <c r="R18" t="n">
-        <v>7086855</v>
+        <v>7087356</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2728,40 +2725,54 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124732683</v>
+        <v>124749070</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2770,41 +2781,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706597</v>
+        <v>706442</v>
       </c>
       <c r="R19" t="n">
-        <v>7087402</v>
+        <v>7087349</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2831,19 +2846,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,28 +2862,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124736752</v>
+        <v>124732401</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2882,47 +2893,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706281</v>
+        <v>706665</v>
       </c>
       <c r="R20" t="n">
-        <v>7087219</v>
+        <v>7087406</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2952,9 +2954,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,19 +2981,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124734745</v>
+        <v>124734940</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3021,7 +3033,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706401</v>
+        <v>706418</v>
       </c>
       <c r="R21" t="n">
         <v>7087323</v>
@@ -3054,24 +3066,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,19 +3083,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124734081</v>
+        <v>124749246</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3132,19 +3129,23 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706490</v>
+        <v>706288</v>
       </c>
       <c r="R22" t="n">
-        <v>7087362</v>
+        <v>7087206</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3171,19 +3172,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3192,25 +3188,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749070</v>
+        <v>124736752</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3243,24 +3240,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706442</v>
+        <v>706281</v>
       </c>
       <c r="R23" t="n">
-        <v>7087349</v>
+        <v>7087219</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3292,37 +3294,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124749539</v>
+        <v>124749392</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3366,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706157</v>
+        <v>706191</v>
       </c>
       <c r="R24" t="n">
-        <v>7087072</v>
+        <v>7087129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3434,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124733522</v>
+        <v>124749133</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3446,41 +3442,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706523</v>
+        <v>706364</v>
       </c>
       <c r="R25" t="n">
-        <v>7087364</v>
+        <v>7087314</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3507,49 +3507,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124749246</v>
+        <v>124734903</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3558,45 +3549,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706288</v>
+        <v>706371</v>
       </c>
       <c r="R26" t="n">
-        <v>7087206</v>
+        <v>7087353</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3623,14 +3610,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3639,29 +3631,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749350</v>
+        <v>124749686</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3670,31 +3661,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3702,10 +3692,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706238</v>
+        <v>705962</v>
       </c>
       <c r="R27" t="n">
-        <v>7087154</v>
+        <v>7086855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3738,11 +3728,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3770,10 +3755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124736627</v>
+        <v>124749414</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3782,41 +3767,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706292</v>
+        <v>706126</v>
       </c>
       <c r="R28" t="n">
-        <v>7087225</v>
+        <v>7087117</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3848,31 +3837,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124734940</v>
+        <v>124734648</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706418</v>
+        <v>706405</v>
       </c>
       <c r="R29" t="n">
-        <v>7087323</v>
+        <v>7087320</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3945,9 +3940,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,22 +3967,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124749414</v>
+        <v>124732683</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3986,45 +3991,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706126</v>
+        <v>706597</v>
       </c>
       <c r="R30" t="n">
-        <v>7087117</v>
+        <v>7087402</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4051,14 +4052,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,29 +4073,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749167</v>
+        <v>124749290</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4098,31 +4103,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4130,10 +4139,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706354</v>
+        <v>706276</v>
       </c>
       <c r="R31" t="n">
-        <v>7087195</v>
+        <v>7087213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4168,18 +4177,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4198,10 +4201,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124732613</v>
+        <v>124744220</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4210,41 +4213,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706654</v>
+        <v>706411</v>
       </c>
       <c r="R32" t="n">
-        <v>7087408</v>
+        <v>7087322</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4271,19 +4286,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,19 +4303,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749575</v>
+        <v>124749539</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4354,10 +4359,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706133</v>
+        <v>706157</v>
       </c>
       <c r="R33" t="n">
-        <v>7087057</v>
+        <v>7087072</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4422,10 +4427,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124733886</v>
+        <v>124749111</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4434,41 +4439,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706495</v>
+        <v>706398</v>
       </c>
       <c r="R34" t="n">
-        <v>7087369</v>
+        <v>7087345</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4495,24 +4504,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4521,25 +4520,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124749376</v>
+        <v>124739661</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4573,23 +4573,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706224</v>
+        <v>705952</v>
       </c>
       <c r="R35" t="n">
-        <v>7087139</v>
+        <v>7086928</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4616,14 +4612,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,29 +4633,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124739909</v>
+        <v>124739921</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4663,47 +4663,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706048</v>
+        <v>706034</v>
       </c>
       <c r="R36" t="n">
-        <v>7086914</v>
+        <v>7086918</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4733,9 +4724,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4750,19 +4751,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749460</v>
+        <v>124749331</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4806,10 +4807,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706115</v>
+        <v>706228</v>
       </c>
       <c r="R37" t="n">
-        <v>7087088</v>
+        <v>7087165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4846,7 +4847,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,7 +4875,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124739661</v>
+        <v>124737518</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4910,14 +4911,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705952</v>
+        <v>706341</v>
       </c>
       <c r="R38" t="n">
-        <v>7086928</v>
+        <v>7087207</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4949,7 +4950,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4959,7 +4960,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,7 +4987,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749184</v>
+        <v>124739585</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5020,23 +5021,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706340</v>
+        <v>705944</v>
       </c>
       <c r="R39" t="n">
-        <v>7087178</v>
+        <v>7086954</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5063,14 +5060,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5079,26 +5081,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124739096</v>
+        <v>124749460</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5132,19 +5133,23 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706304</v>
+        <v>706115</v>
       </c>
       <c r="R40" t="n">
-        <v>7087194</v>
+        <v>7087088</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5171,19 +5176,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,25 +5192,26 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749263</v>
+        <v>124734081</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5244,23 +5245,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706282</v>
+        <v>706490</v>
       </c>
       <c r="R41" t="n">
-        <v>7087215</v>
+        <v>7087362</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5287,14 +5284,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5303,29 +5305,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749290</v>
+        <v>124749184</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5334,35 +5335,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5370,10 +5367,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706276</v>
+        <v>706340</v>
       </c>
       <c r="R42" t="n">
-        <v>7087213</v>
+        <v>7087178</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5408,12 +5405,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5432,10 +5435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124734381</v>
+        <v>124749167</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5444,41 +5447,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706473</v>
+        <v>706354</v>
       </c>
       <c r="R43" t="n">
-        <v>7087334</v>
+        <v>7087195</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5505,19 +5512,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5526,28 +5528,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124739585</v>
+        <v>124733886</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5556,38 +5559,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>705944</v>
+        <v>706495</v>
       </c>
       <c r="R44" t="n">
-        <v>7086954</v>
+        <v>7087369</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5619,7 +5622,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5629,7 +5632,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5656,7 +5664,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749111</v>
+        <v>124739096</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5690,23 +5698,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706398</v>
+        <v>706304</v>
       </c>
       <c r="R45" t="n">
-        <v>7087345</v>
+        <v>7087194</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5733,14 +5737,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5749,19 +5758,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5880,10 +5888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124738318</v>
+        <v>124734417</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5892,25 +5900,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5920,10 +5928,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706281</v>
+        <v>706465</v>
       </c>
       <c r="R47" t="n">
-        <v>7087219</v>
+        <v>7087346</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5953,9 +5961,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5970,22 +5993,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124734903</v>
+        <v>124749500</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5994,41 +6017,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706371</v>
+        <v>706145</v>
       </c>
       <c r="R48" t="n">
-        <v>7087353</v>
+        <v>7087098</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6055,19 +6082,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6076,28 +6098,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124734139</v>
+        <v>124736627</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6106,25 +6129,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6134,10 +6157,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706472</v>
+        <v>706292</v>
       </c>
       <c r="R49" t="n">
-        <v>7087356</v>
+        <v>7087225</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6167,24 +6190,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6199,19 +6207,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749013</v>
+        <v>124734745</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6245,23 +6253,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706446</v>
+        <v>706401</v>
       </c>
       <c r="R50" t="n">
-        <v>7087375</v>
+        <v>7087323</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6288,14 +6292,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,29 +6318,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124739921</v>
+        <v>124733393</v>
       </c>
       <c r="B51" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6335,38 +6348,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706034</v>
+        <v>706533</v>
       </c>
       <c r="R51" t="n">
-        <v>7086918</v>
+        <v>7087362</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6398,7 +6411,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6408,7 +6421,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6435,7 +6448,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749086</v>
+        <v>124735830</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6469,23 +6482,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706447</v>
+        <v>706344</v>
       </c>
       <c r="R52" t="n">
-        <v>7087337</v>
+        <v>7087202</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6512,14 +6521,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6528,29 +6542,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124737518</v>
+        <v>124734381</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6559,25 +6572,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6587,10 +6600,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706341</v>
+        <v>706473</v>
       </c>
       <c r="R53" t="n">
-        <v>7087207</v>
+        <v>7087334</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6622,7 +6635,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6632,7 +6645,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6659,7 +6672,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749040</v>
+        <v>124749376</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6703,10 +6716,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706431</v>
+        <v>706224</v>
       </c>
       <c r="R54" t="n">
-        <v>7087362</v>
+        <v>7087139</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6743,7 +6756,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6771,7 +6784,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749133</v>
+        <v>124749013</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6815,10 +6828,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706364</v>
+        <v>706446</v>
       </c>
       <c r="R55" t="n">
-        <v>7087314</v>
+        <v>7087375</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6851,6 +6864,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6878,10 +6896,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124744220</v>
+        <v>124739909</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6890,53 +6908,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706411</v>
+        <v>706048</v>
       </c>
       <c r="R56" t="n">
-        <v>7087322</v>
+        <v>7086914</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6980,22 +6995,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749331</v>
+        <v>124735169</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7004,45 +7019,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706228</v>
+        <v>706394</v>
       </c>
       <c r="R57" t="n">
-        <v>7087165</v>
+        <v>7087340</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7074,40 +7085,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124734648</v>
+        <v>124738318</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7116,25 +7121,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7144,10 +7149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706405</v>
+        <v>706281</v>
       </c>
       <c r="R58" t="n">
-        <v>7087320</v>
+        <v>7087219</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7177,19 +7182,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7204,22 +7199,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124733393</v>
+        <v>124733522</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7228,25 +7223,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7256,10 +7251,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706533</v>
+        <v>706523</v>
       </c>
       <c r="R59" t="n">
-        <v>7087362</v>
+        <v>7087364</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7291,7 +7286,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7301,7 +7296,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7328,7 +7323,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749392</v>
+        <v>124749350</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706191</v>
+        <v>706238</v>
       </c>
       <c r="R60" t="n">
-        <v>7087129</v>
+        <v>7087154</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7412,7 +7407,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7440,7 +7435,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124734417</v>
+        <v>124749040</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7474,19 +7469,23 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706465</v>
+        <v>706431</v>
       </c>
       <c r="R61" t="n">
-        <v>7087346</v>
+        <v>7087362</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7513,24 +7512,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7539,25 +7528,26 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749500</v>
+        <v>124749263</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7601,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706145</v>
+        <v>706282</v>
       </c>
       <c r="R62" t="n">
-        <v>7087098</v>
+        <v>7087215</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7669,10 +7659,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124735830</v>
+        <v>124739580</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7681,38 +7671,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706344</v>
+        <v>706048</v>
       </c>
       <c r="R63" t="n">
-        <v>7087202</v>
+        <v>7086914</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7742,19 +7732,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7769,19 +7749,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124732401</v>
+        <v>124732613</v>
       </c>
       <c r="B64" t="n">
         <v>91012</v>
@@ -7821,10 +7801,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706665</v>
+        <v>706654</v>
       </c>
       <c r="R64" t="n">
-        <v>7087406</v>
+        <v>7087408</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7856,7 +7836,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7866,7 +7846,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7893,10 +7873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124735169</v>
+        <v>124749575</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7905,41 +7885,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706394</v>
+        <v>706133</v>
       </c>
       <c r="R65" t="n">
-        <v>7087340</v>
+        <v>7087057</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7971,34 +7955,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124739580</v>
+        <v>124749086</v>
       </c>
       <c r="B66" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8007,41 +7997,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706048</v>
+        <v>706447</v>
       </c>
       <c r="R66" t="n">
-        <v>7086914</v>
+        <v>7087337</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8073,24 +8067,30 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124734139</v>
+        <v>124735169</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,25 +2664,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706472</v>
+        <v>706394</v>
       </c>
       <c r="R18" t="n">
-        <v>7087356</v>
+        <v>7087340</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2725,24 +2725,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2757,19 +2742,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124749070</v>
+        <v>124749040</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2813,10 +2798,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706442</v>
+        <v>706431</v>
       </c>
       <c r="R19" t="n">
-        <v>7087349</v>
+        <v>7087362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2853,7 +2838,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,7 +2866,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124732401</v>
+        <v>124732613</v>
       </c>
       <c r="B20" t="n">
         <v>91012</v>
@@ -2921,10 +2906,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706665</v>
+        <v>706654</v>
       </c>
       <c r="R20" t="n">
-        <v>7087406</v>
+        <v>7087408</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2956,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2966,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2993,7 +2978,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124734940</v>
+        <v>124749331</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3027,19 +3012,23 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706418</v>
+        <v>706228</v>
       </c>
       <c r="R21" t="n">
-        <v>7087323</v>
+        <v>7087165</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3071,31 +3060,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749246</v>
+        <v>124734139</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3129,23 +3124,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706288</v>
+        <v>706472</v>
       </c>
       <c r="R22" t="n">
-        <v>7087206</v>
+        <v>7087356</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3172,14 +3163,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3188,26 +3189,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124736752</v>
+        <v>124749167</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3240,29 +3240,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706281</v>
+        <v>706354</v>
       </c>
       <c r="R23" t="n">
-        <v>7087219</v>
+        <v>7087195</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3294,31 +3289,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124749392</v>
+        <v>124749500</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3362,10 +3363,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706191</v>
+        <v>706145</v>
       </c>
       <c r="R24" t="n">
-        <v>7087129</v>
+        <v>7087098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3430,7 +3431,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749133</v>
+        <v>124734940</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3464,23 +3465,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706364</v>
+        <v>706418</v>
       </c>
       <c r="R25" t="n">
-        <v>7087314</v>
+        <v>7087323</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3518,29 +3515,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124734903</v>
+        <v>124736752</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,38 +3545,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706371</v>
+        <v>706281</v>
       </c>
       <c r="R26" t="n">
-        <v>7087353</v>
+        <v>7087219</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3610,19 +3615,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3637,22 +3632,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749686</v>
+        <v>124749133</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3661,30 +3656,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3692,10 +3688,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705962</v>
+        <v>706364</v>
       </c>
       <c r="R27" t="n">
-        <v>7086855</v>
+        <v>7087314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3755,10 +3751,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749414</v>
+        <v>124734381</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3767,45 +3763,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706126</v>
+        <v>706473</v>
       </c>
       <c r="R28" t="n">
-        <v>7087117</v>
+        <v>7087334</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3832,14 +3824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3848,29 +3845,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124734648</v>
+        <v>124739580</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3879,38 +3875,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706405</v>
+        <v>706048</v>
       </c>
       <c r="R29" t="n">
-        <v>7087320</v>
+        <v>7086914</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3940,19 +3936,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3967,22 +3953,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732683</v>
+        <v>124736627</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,21 +3981,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +4005,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706597</v>
+        <v>706292</v>
       </c>
       <c r="R30" t="n">
-        <v>7087402</v>
+        <v>7087225</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4052,19 +4038,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,22 +4055,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749290</v>
+        <v>124749414</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4103,35 +4079,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4139,10 +4111,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706276</v>
+        <v>706126</v>
       </c>
       <c r="R31" t="n">
-        <v>7087213</v>
+        <v>7087117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,12 +4149,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4201,10 +4179,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124744220</v>
+        <v>124739585</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4213,53 +4191,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706411</v>
+        <v>705944</v>
       </c>
       <c r="R32" t="n">
-        <v>7087322</v>
+        <v>7086954</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4286,9 +4252,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4303,19 +4279,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749539</v>
+        <v>124739661</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4349,23 +4325,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706157</v>
+        <v>705952</v>
       </c>
       <c r="R33" t="n">
-        <v>7087072</v>
+        <v>7086928</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4392,14 +4364,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,26 +4385,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749111</v>
+        <v>124739096</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4461,23 +4437,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706398</v>
+        <v>706304</v>
       </c>
       <c r="R34" t="n">
-        <v>7087345</v>
+        <v>7087194</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4504,14 +4476,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4520,26 +4497,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739661</v>
+        <v>124749086</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4573,19 +4549,23 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>705952</v>
+        <v>706447</v>
       </c>
       <c r="R35" t="n">
-        <v>7086928</v>
+        <v>7087337</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4612,19 +4592,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4633,28 +4608,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124739921</v>
+        <v>124738318</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4667,34 +4643,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706034</v>
+        <v>706281</v>
       </c>
       <c r="R36" t="n">
-        <v>7086918</v>
+        <v>7087219</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4724,19 +4700,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,19 +4717,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749331</v>
+        <v>124734417</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4797,23 +4763,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706228</v>
+        <v>706465</v>
       </c>
       <c r="R37" t="n">
-        <v>7087165</v>
+        <v>7087346</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4840,14 +4802,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,26 +4828,25 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124737518</v>
+        <v>124749111</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4909,19 +4880,23 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706341</v>
+        <v>706398</v>
       </c>
       <c r="R38" t="n">
-        <v>7087207</v>
+        <v>7087345</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4948,19 +4923,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4969,25 +4939,26 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124739585</v>
+        <v>124737518</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5023,14 +4994,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705944</v>
+        <v>706341</v>
       </c>
       <c r="R39" t="n">
-        <v>7086954</v>
+        <v>7087207</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5062,7 +5033,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5072,7 +5043,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5099,10 +5070,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749460</v>
+        <v>124739921</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5111,45 +5082,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706115</v>
+        <v>706034</v>
       </c>
       <c r="R40" t="n">
-        <v>7087088</v>
+        <v>7086918</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5176,14 +5143,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,26 +5164,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124734081</v>
+        <v>124749575</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5245,19 +5216,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706490</v>
+        <v>706133</v>
       </c>
       <c r="R41" t="n">
-        <v>7087362</v>
+        <v>7087057</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5284,19 +5259,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5305,25 +5275,26 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749184</v>
+        <v>124749539</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5367,10 +5338,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706340</v>
+        <v>706157</v>
       </c>
       <c r="R42" t="n">
-        <v>7087178</v>
+        <v>7087072</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5435,7 +5406,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749167</v>
+        <v>124734648</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5469,23 +5440,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706354</v>
+        <v>706405</v>
       </c>
       <c r="R43" t="n">
-        <v>7087195</v>
+        <v>7087320</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5512,14 +5479,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,29 +5500,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124733886</v>
+        <v>124733393</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5559,25 +5530,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5587,10 +5558,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706495</v>
+        <v>706533</v>
       </c>
       <c r="R44" t="n">
-        <v>7087369</v>
+        <v>7087362</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5622,7 +5593,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5632,12 +5603,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5664,10 +5630,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124739096</v>
+        <v>124734903</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5676,25 +5642,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5704,10 +5670,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706304</v>
+        <v>706371</v>
       </c>
       <c r="R45" t="n">
-        <v>7087194</v>
+        <v>7087353</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5739,7 +5705,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5749,7 +5715,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5776,7 +5742,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749657</v>
+        <v>124734745</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5810,23 +5776,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705966</v>
+        <v>706401</v>
       </c>
       <c r="R46" t="n">
-        <v>7086987</v>
+        <v>7087323</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5853,14 +5815,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5869,26 +5841,25 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124734417</v>
+        <v>124749657</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5922,19 +5893,23 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706465</v>
+        <v>705966</v>
       </c>
       <c r="R47" t="n">
-        <v>7087346</v>
+        <v>7086987</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5961,24 +5936,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5987,28 +5952,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749500</v>
+        <v>124732401</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6017,45 +5983,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706145</v>
+        <v>706665</v>
       </c>
       <c r="R48" t="n">
-        <v>7087098</v>
+        <v>7087406</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6082,14 +6044,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6098,29 +6065,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124736627</v>
+        <v>124749376</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6129,41 +6095,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706292</v>
+        <v>706224</v>
       </c>
       <c r="R49" t="n">
-        <v>7087225</v>
+        <v>7087139</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6195,31 +6165,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124734745</v>
+        <v>124749460</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6253,19 +6229,23 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706401</v>
+        <v>706115</v>
       </c>
       <c r="R50" t="n">
-        <v>7087323</v>
+        <v>7087088</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6292,24 +6272,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6318,25 +6288,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124733393</v>
+        <v>124749392</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6370,19 +6341,23 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706533</v>
+        <v>706191</v>
       </c>
       <c r="R51" t="n">
-        <v>7087362</v>
+        <v>7087129</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6409,19 +6384,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6430,28 +6400,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124735830</v>
+        <v>124749686</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6460,41 +6431,44 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706344</v>
+        <v>705962</v>
       </c>
       <c r="R52" t="n">
-        <v>7087202</v>
+        <v>7086855</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6521,49 +6495,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124734381</v>
+        <v>124749290</v>
       </c>
       <c r="B53" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6572,41 +6537,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706473</v>
+        <v>706276</v>
       </c>
       <c r="R53" t="n">
-        <v>7087334</v>
+        <v>7087213</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6633,19 +6606,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6660,19 +6623,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749376</v>
+        <v>124749184</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6716,10 +6679,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706224</v>
+        <v>706340</v>
       </c>
       <c r="R54" t="n">
-        <v>7087139</v>
+        <v>7087178</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6784,7 +6747,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749013</v>
+        <v>124749263</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6828,10 +6791,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706446</v>
+        <v>706282</v>
       </c>
       <c r="R55" t="n">
-        <v>7087375</v>
+        <v>7087215</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6868,7 +6831,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6896,7 +6859,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124739909</v>
+        <v>124734081</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6929,26 +6892,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706048</v>
+        <v>706490</v>
       </c>
       <c r="R56" t="n">
-        <v>7086914</v>
+        <v>7087362</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6978,9 +6932,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6995,22 +6959,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124735169</v>
+        <v>124749246</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7019,41 +6983,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706394</v>
+        <v>706288</v>
       </c>
       <c r="R57" t="n">
-        <v>7087340</v>
+        <v>7087206</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7085,34 +7053,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124738318</v>
+        <v>124739909</v>
       </c>
       <c r="B58" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7121,38 +7095,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706281</v>
+        <v>706048</v>
       </c>
       <c r="R58" t="n">
-        <v>7087219</v>
+        <v>7086914</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7211,10 +7194,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124733522</v>
+        <v>124732683</v>
       </c>
       <c r="B59" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7227,21 +7210,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7251,10 +7234,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706523</v>
+        <v>706597</v>
       </c>
       <c r="R59" t="n">
-        <v>7087364</v>
+        <v>7087402</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7286,7 +7269,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7296,7 +7279,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7323,7 +7306,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749350</v>
+        <v>124735830</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7357,23 +7340,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706238</v>
+        <v>706344</v>
       </c>
       <c r="R60" t="n">
-        <v>7087154</v>
+        <v>7087202</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,14 +7379,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7416,29 +7400,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749040</v>
+        <v>124744220</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7447,31 +7430,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7479,10 +7470,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706431</v>
+        <v>706411</v>
       </c>
       <c r="R61" t="n">
-        <v>7087362</v>
+        <v>7087322</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7517,18 +7508,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7547,10 +7532,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749263</v>
+        <v>124733886</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7559,45 +7544,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706282</v>
+        <v>706495</v>
       </c>
       <c r="R62" t="n">
-        <v>7087215</v>
+        <v>7087369</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7624,14 +7605,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7640,29 +7631,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124739580</v>
+        <v>124749013</v>
       </c>
       <c r="B63" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7671,41 +7661,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706048</v>
+        <v>706446</v>
       </c>
       <c r="R63" t="n">
-        <v>7086914</v>
+        <v>7087375</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7737,34 +7731,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124732613</v>
+        <v>124749350</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7773,41 +7773,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706654</v>
+        <v>706238</v>
       </c>
       <c r="R64" t="n">
-        <v>7087408</v>
+        <v>7087154</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7834,19 +7838,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,28 +7854,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749575</v>
+        <v>124733522</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,45 +7885,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706133</v>
+        <v>706523</v>
       </c>
       <c r="R65" t="n">
-        <v>7087057</v>
+        <v>7087364</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7950,14 +7946,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,26 +7967,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749086</v>
+        <v>124749070</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706447</v>
+        <v>706442</v>
       </c>
       <c r="R66" t="n">
-        <v>7087337</v>
+        <v>7087349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -4515,10 +4515,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124749086</v>
+        <v>124738318</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4527,45 +4527,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706447</v>
+        <v>706281</v>
       </c>
       <c r="R35" t="n">
-        <v>7087337</v>
+        <v>7087219</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4597,40 +4593,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124738318</v>
+        <v>124734417</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4639,25 +4629,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4667,10 +4657,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706281</v>
+        <v>706465</v>
       </c>
       <c r="R36" t="n">
-        <v>7087219</v>
+        <v>7087346</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4700,9 +4690,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4717,19 +4722,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124734417</v>
+        <v>124749111</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4763,19 +4768,23 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706465</v>
+        <v>706398</v>
       </c>
       <c r="R37" t="n">
-        <v>7087346</v>
+        <v>7087345</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4802,24 +4811,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4828,25 +4827,26 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749111</v>
+        <v>124749086</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706398</v>
+        <v>706447</v>
       </c>
       <c r="R38" t="n">
-        <v>7087345</v>
+        <v>7087337</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -6307,10 +6307,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749392</v>
+        <v>124749686</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6319,31 +6319,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6351,10 +6350,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706191</v>
+        <v>705962</v>
       </c>
       <c r="R51" t="n">
-        <v>7087129</v>
+        <v>7086855</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6387,11 +6386,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6419,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749686</v>
+        <v>124749392</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6431,30 +6425,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6462,10 +6457,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705962</v>
+        <v>706191</v>
       </c>
       <c r="R52" t="n">
-        <v>7086855</v>
+        <v>7087129</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6498,6 +6493,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6525,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749290</v>
+        <v>124749184</v>
       </c>
       <c r="B53" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6537,35 +6537,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6573,10 +6569,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706276</v>
+        <v>706340</v>
       </c>
       <c r="R53" t="n">
-        <v>7087213</v>
+        <v>7087178</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6611,12 +6607,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6635,7 +6637,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749184</v>
+        <v>124749263</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6679,10 +6681,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706340</v>
+        <v>706282</v>
       </c>
       <c r="R54" t="n">
-        <v>7087178</v>
+        <v>7087215</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6747,7 +6749,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749263</v>
+        <v>124734081</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6781,23 +6783,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706282</v>
+        <v>706490</v>
       </c>
       <c r="R55" t="n">
-        <v>7087215</v>
+        <v>7087362</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6824,14 +6822,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6840,29 +6843,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124734081</v>
+        <v>124749290</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6871,41 +6873,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706490</v>
+        <v>706276</v>
       </c>
       <c r="R56" t="n">
-        <v>7087362</v>
+        <v>7087213</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6932,19 +6942,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6959,12 +6959,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124735169</v>
+        <v>124749040</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,41 +2664,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706394</v>
+        <v>706431</v>
       </c>
       <c r="R18" t="n">
-        <v>7087340</v>
+        <v>7087362</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2730,34 +2734,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124749040</v>
+        <v>124735169</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2766,45 +2776,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706431</v>
+        <v>706394</v>
       </c>
       <c r="R19" t="n">
-        <v>7087362</v>
+        <v>7087340</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2836,30 +2842,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124739580</v>
+        <v>124749414</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3875,41 +3875,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706048</v>
+        <v>706126</v>
       </c>
       <c r="R29" t="n">
-        <v>7086914</v>
+        <v>7087117</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3941,34 +3945,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124736627</v>
+        <v>124739585</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3977,38 +3987,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706292</v>
+        <v>705944</v>
       </c>
       <c r="R30" t="n">
-        <v>7087225</v>
+        <v>7086954</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4038,9 +4048,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4055,19 +4075,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749414</v>
+        <v>124739661</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4101,23 +4121,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706126</v>
+        <v>705952</v>
       </c>
       <c r="R31" t="n">
-        <v>7087117</v>
+        <v>7086928</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4144,14 +4160,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,26 +4181,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124739585</v>
+        <v>124739096</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4215,14 +4235,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705944</v>
+        <v>706304</v>
       </c>
       <c r="R32" t="n">
-        <v>7086954</v>
+        <v>7087194</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4254,7 +4274,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4264,7 +4284,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,10 +4311,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124739661</v>
+        <v>124739580</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4303,25 +4323,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4331,10 +4351,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705952</v>
+        <v>706048</v>
       </c>
       <c r="R33" t="n">
-        <v>7086928</v>
+        <v>7086914</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4364,19 +4384,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4391,22 +4401,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124739096</v>
+        <v>124736627</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4415,25 +4425,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706304</v>
+        <v>706292</v>
       </c>
       <c r="R34" t="n">
-        <v>7087194</v>
+        <v>7087225</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4476,19 +4486,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4503,12 +4503,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6307,10 +6307,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749686</v>
+        <v>124749392</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6319,30 +6319,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6350,10 +6351,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>705962</v>
+        <v>706191</v>
       </c>
       <c r="R51" t="n">
-        <v>7086855</v>
+        <v>7087129</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6386,6 +6387,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6413,10 +6419,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749392</v>
+        <v>124749686</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6425,31 +6431,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6457,10 +6462,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706191</v>
+        <v>705962</v>
       </c>
       <c r="R52" t="n">
-        <v>7087129</v>
+        <v>7086855</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6493,11 +6498,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749040</v>
+        <v>124749414</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706431</v>
+        <v>706126</v>
       </c>
       <c r="R18" t="n">
-        <v>7087362</v>
+        <v>7087117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124735169</v>
+        <v>124749331</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,41 +2776,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706394</v>
+        <v>706228</v>
       </c>
       <c r="R19" t="n">
-        <v>7087340</v>
+        <v>7087165</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2842,34 +2846,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124732613</v>
+        <v>124749460</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2878,41 +2888,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706654</v>
+        <v>706115</v>
       </c>
       <c r="R20" t="n">
-        <v>7087408</v>
+        <v>7087088</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2939,19 +2953,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2960,28 +2969,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749331</v>
+        <v>124735169</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2990,45 +3000,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706228</v>
+        <v>706394</v>
       </c>
       <c r="R21" t="n">
-        <v>7087165</v>
+        <v>7087340</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3060,37 +3066,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124734139</v>
+        <v>124749111</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3124,19 +3124,23 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706472</v>
+        <v>706398</v>
       </c>
       <c r="R22" t="n">
-        <v>7087356</v>
+        <v>7087345</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3163,24 +3167,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,25 +3183,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749167</v>
+        <v>124749263</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3251,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706354</v>
+        <v>706282</v>
       </c>
       <c r="R23" t="n">
-        <v>7087195</v>
+        <v>7087215</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3319,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124749500</v>
+        <v>124744220</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3331,31 +3326,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3363,10 +3366,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706145</v>
+        <v>706411</v>
       </c>
       <c r="R24" t="n">
-        <v>7087098</v>
+        <v>7087322</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3401,18 +3404,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3431,10 +3428,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734940</v>
+        <v>124734381</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3443,25 +3440,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3471,10 +3468,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706418</v>
+        <v>706473</v>
       </c>
       <c r="R25" t="n">
-        <v>7087323</v>
+        <v>7087334</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3504,9 +3501,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,22 +3528,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124736752</v>
+        <v>124739580</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3545,47 +3552,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706281</v>
+        <v>706048</v>
       </c>
       <c r="R26" t="n">
-        <v>7087219</v>
+        <v>7086914</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3644,10 +3642,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749133</v>
+        <v>124738318</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3656,45 +3654,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706364</v>
+        <v>706281</v>
       </c>
       <c r="R27" t="n">
-        <v>7087314</v>
+        <v>7087219</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3732,29 +3726,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124734381</v>
+        <v>124749376</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3763,41 +3756,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706473</v>
+        <v>706224</v>
       </c>
       <c r="R28" t="n">
-        <v>7087334</v>
+        <v>7087139</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,19 +3821,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3845,25 +3837,26 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749414</v>
+        <v>124739096</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3897,23 +3890,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706126</v>
+        <v>706304</v>
       </c>
       <c r="R29" t="n">
-        <v>7087117</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3940,14 +3929,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,26 +3950,25 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124739585</v>
+        <v>124734940</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4011,14 +4004,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705944</v>
+        <v>706418</v>
       </c>
       <c r="R30" t="n">
-        <v>7086954</v>
+        <v>7087323</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4048,19 +4041,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,19 +4058,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124739661</v>
+        <v>124749392</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4121,19 +4104,23 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705952</v>
+        <v>706191</v>
       </c>
       <c r="R31" t="n">
-        <v>7086928</v>
+        <v>7087129</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4160,19 +4147,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4181,25 +4163,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124739096</v>
+        <v>124749013</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4233,19 +4216,23 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706304</v>
+        <v>706446</v>
       </c>
       <c r="R32" t="n">
-        <v>7087194</v>
+        <v>7087375</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4272,19 +4259,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4293,28 +4275,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124739580</v>
+        <v>124735830</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4323,38 +4306,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706048</v>
+        <v>706344</v>
       </c>
       <c r="R33" t="n">
-        <v>7086914</v>
+        <v>7087202</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4384,9 +4367,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4401,22 +4394,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124736627</v>
+        <v>124749575</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4425,41 +4418,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706292</v>
+        <v>706133</v>
       </c>
       <c r="R34" t="n">
-        <v>7087225</v>
+        <v>7087057</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4491,34 +4488,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124738318</v>
+        <v>124739585</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4527,38 +4530,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706281</v>
+        <v>705944</v>
       </c>
       <c r="R35" t="n">
-        <v>7087219</v>
+        <v>7086954</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4588,9 +4591,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,19 +4618,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124734417</v>
+        <v>124736752</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4650,17 +4663,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706465</v>
+        <v>706281</v>
       </c>
       <c r="R36" t="n">
-        <v>7087346</v>
+        <v>7087219</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4690,24 +4712,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4722,19 +4729,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749111</v>
+        <v>124733393</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4768,23 +4775,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706398</v>
+        <v>706533</v>
       </c>
       <c r="R37" t="n">
-        <v>7087345</v>
+        <v>7087362</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,14 +4814,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4827,26 +4835,25 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749086</v>
+        <v>124734417</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4880,23 +4887,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706447</v>
+        <v>706465</v>
       </c>
       <c r="R38" t="n">
-        <v>7087337</v>
+        <v>7087346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4923,14 +4926,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4939,26 +4952,25 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124737518</v>
+        <v>124734081</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4998,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706341</v>
+        <v>706490</v>
       </c>
       <c r="R39" t="n">
-        <v>7087207</v>
+        <v>7087362</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5033,7 +5045,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5043,7 +5055,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5182,10 +5194,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749575</v>
+        <v>124732613</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5194,45 +5206,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706133</v>
+        <v>706654</v>
       </c>
       <c r="R41" t="n">
-        <v>7087057</v>
+        <v>7087408</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5259,14 +5267,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5275,26 +5288,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749539</v>
+        <v>124734648</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5328,23 +5340,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706157</v>
+        <v>706405</v>
       </c>
       <c r="R42" t="n">
-        <v>7087072</v>
+        <v>7087320</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5371,14 +5379,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5387,26 +5400,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124734648</v>
+        <v>124749246</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5440,19 +5452,23 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706405</v>
+        <v>706288</v>
       </c>
       <c r="R43" t="n">
-        <v>7087320</v>
+        <v>7087206</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5479,19 +5495,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5500,25 +5511,26 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124733393</v>
+        <v>124749350</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5552,19 +5564,23 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706533</v>
+        <v>706238</v>
       </c>
       <c r="R44" t="n">
-        <v>7087362</v>
+        <v>7087154</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5591,19 +5607,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5612,28 +5623,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124734903</v>
+        <v>124734745</v>
       </c>
       <c r="B45" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5642,25 +5654,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5670,10 +5682,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706371</v>
+        <v>706401</v>
       </c>
       <c r="R45" t="n">
-        <v>7087353</v>
+        <v>7087323</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5705,7 +5717,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5715,7 +5727,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5742,7 +5759,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124734745</v>
+        <v>124749133</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5776,19 +5793,23 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706401</v>
+        <v>706364</v>
       </c>
       <c r="R46" t="n">
-        <v>7087323</v>
+        <v>7087314</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5815,51 +5836,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749657</v>
+        <v>124739661</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5893,23 +5900,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705966</v>
+        <v>705952</v>
       </c>
       <c r="R47" t="n">
-        <v>7086987</v>
+        <v>7086928</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5936,14 +5939,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5952,29 +5960,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124732401</v>
+        <v>124733886</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5983,25 +5990,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6011,10 +6018,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706665</v>
+        <v>706495</v>
       </c>
       <c r="R48" t="n">
-        <v>7087406</v>
+        <v>7087369</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6046,7 +6053,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6056,7 +6063,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6083,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749376</v>
+        <v>124736627</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6095,45 +6107,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706224</v>
+        <v>706292</v>
       </c>
       <c r="R49" t="n">
-        <v>7087139</v>
+        <v>7087225</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6165,40 +6173,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749460</v>
+        <v>124749686</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6207,31 +6209,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6239,10 +6240,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706115</v>
+        <v>705962</v>
       </c>
       <c r="R50" t="n">
-        <v>7087088</v>
+        <v>7086855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6275,11 +6276,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6307,7 +6303,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749392</v>
+        <v>124749184</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6351,10 +6347,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706191</v>
+        <v>706340</v>
       </c>
       <c r="R51" t="n">
-        <v>7087129</v>
+        <v>7087178</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6419,10 +6415,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749686</v>
+        <v>124734903</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6431,44 +6427,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705962</v>
+        <v>706371</v>
       </c>
       <c r="R52" t="n">
-        <v>7086855</v>
+        <v>7087353</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6495,40 +6488,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749184</v>
+        <v>124732683</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6537,45 +6539,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706340</v>
+        <v>706597</v>
       </c>
       <c r="R53" t="n">
-        <v>7087178</v>
+        <v>7087402</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6602,14 +6600,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6618,26 +6621,25 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749263</v>
+        <v>124749070</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6681,10 +6683,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706282</v>
+        <v>706442</v>
       </c>
       <c r="R54" t="n">
-        <v>7087215</v>
+        <v>7087349</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6749,7 +6751,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124734081</v>
+        <v>124749539</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6783,19 +6785,23 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706490</v>
+        <v>706157</v>
       </c>
       <c r="R55" t="n">
-        <v>7087362</v>
+        <v>7087072</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6822,19 +6828,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6843,28 +6844,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749290</v>
+        <v>124749086</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6873,35 +6875,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6909,10 +6907,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706276</v>
+        <v>706447</v>
       </c>
       <c r="R56" t="n">
-        <v>7087213</v>
+        <v>7087337</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6947,12 +6945,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6971,7 +6975,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749246</v>
+        <v>124749040</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7015,10 +7019,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706288</v>
+        <v>706431</v>
       </c>
       <c r="R57" t="n">
-        <v>7087206</v>
+        <v>7087362</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7083,10 +7087,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124739909</v>
+        <v>124733522</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7095,47 +7099,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706048</v>
+        <v>706523</v>
       </c>
       <c r="R58" t="n">
-        <v>7086914</v>
+        <v>7087364</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7165,9 +7160,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7182,22 +7187,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124732683</v>
+        <v>124749290</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7206,41 +7211,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706597</v>
+        <v>706276</v>
       </c>
       <c r="R59" t="n">
-        <v>7087402</v>
+        <v>7087213</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7267,19 +7280,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7294,19 +7297,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124735830</v>
+        <v>124734139</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7346,10 +7349,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706344</v>
+        <v>706472</v>
       </c>
       <c r="R60" t="n">
-        <v>7087202</v>
+        <v>7087356</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7381,7 +7384,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7391,7 +7394,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,10 +7426,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124744220</v>
+        <v>124737518</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7430,53 +7438,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706411</v>
+        <v>706341</v>
       </c>
       <c r="R61" t="n">
-        <v>7087322</v>
+        <v>7087207</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7503,9 +7499,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7520,22 +7526,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124733886</v>
+        <v>124732401</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7544,25 +7550,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7572,10 +7578,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706495</v>
+        <v>706665</v>
       </c>
       <c r="R62" t="n">
-        <v>7087369</v>
+        <v>7087406</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7607,7 +7613,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7617,12 +7623,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7649,7 +7650,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749013</v>
+        <v>124749167</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7693,10 +7694,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706446</v>
+        <v>706354</v>
       </c>
       <c r="R63" t="n">
-        <v>7087375</v>
+        <v>7087195</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7733,7 +7734,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,7 +7762,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124749350</v>
+        <v>124739909</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7794,24 +7795,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706238</v>
+        <v>706048</v>
       </c>
       <c r="R64" t="n">
-        <v>7087154</v>
+        <v>7086914</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7843,40 +7849,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124733522</v>
+        <v>124749657</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,41 +7885,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706523</v>
+        <v>705966</v>
       </c>
       <c r="R65" t="n">
-        <v>7087364</v>
+        <v>7086987</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7946,19 +7950,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7967,25 +7966,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749070</v>
+        <v>124749500</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706442</v>
+        <v>706145</v>
       </c>
       <c r="R66" t="n">
-        <v>7087349</v>
+        <v>7087098</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749414</v>
+        <v>124739921</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,45 +2664,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706126</v>
+        <v>706034</v>
       </c>
       <c r="R18" t="n">
-        <v>7087117</v>
+        <v>7086918</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2729,14 +2725,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2745,29 +2746,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124749331</v>
+        <v>124735169</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,45 +2776,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706228</v>
+        <v>706394</v>
       </c>
       <c r="R19" t="n">
-        <v>7087165</v>
+        <v>7087340</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,37 +2842,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749460</v>
+        <v>124734745</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2910,23 +2900,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706115</v>
+        <v>706401</v>
       </c>
       <c r="R20" t="n">
-        <v>7087088</v>
+        <v>7087323</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,14 +2939,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,29 +2965,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124735169</v>
+        <v>124749111</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,41 +2995,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706394</v>
+        <v>706398</v>
       </c>
       <c r="R21" t="n">
-        <v>7087340</v>
+        <v>7087345</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3066,31 +3065,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749111</v>
+        <v>124734139</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3124,23 +3129,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706398</v>
+        <v>706472</v>
       </c>
       <c r="R22" t="n">
-        <v>7087345</v>
+        <v>7087356</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3167,14 +3168,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3183,29 +3194,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749263</v>
+        <v>124732401</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3214,45 +3224,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706282</v>
+        <v>706665</v>
       </c>
       <c r="R23" t="n">
-        <v>7087215</v>
+        <v>7087406</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3279,14 +3285,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,29 +3306,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124744220</v>
+        <v>124734940</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3326,53 +3336,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706411</v>
+        <v>706418</v>
       </c>
       <c r="R24" t="n">
-        <v>7087322</v>
+        <v>7087323</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3416,22 +3414,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734381</v>
+        <v>124739585</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3440,38 +3438,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706473</v>
+        <v>705944</v>
       </c>
       <c r="R25" t="n">
-        <v>7087334</v>
+        <v>7086954</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3503,7 +3501,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3513,7 +3511,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3540,7 +3538,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124739580</v>
+        <v>124733522</v>
       </c>
       <c r="B26" t="n">
         <v>57529</v>
@@ -3576,14 +3574,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706048</v>
+        <v>706523</v>
       </c>
       <c r="R26" t="n">
-        <v>7086914</v>
+        <v>7087364</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3613,9 +3611,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3630,19 +3638,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124738318</v>
+        <v>124733886</v>
       </c>
       <c r="B27" t="n">
         <v>56722</v>
@@ -3682,10 +3690,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706281</v>
+        <v>706495</v>
       </c>
       <c r="R27" t="n">
-        <v>7087219</v>
+        <v>7087369</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3715,9 +3723,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3732,19 +3755,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749376</v>
+        <v>124749350</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3788,10 +3811,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706224</v>
+        <v>706238</v>
       </c>
       <c r="R28" t="n">
-        <v>7087139</v>
+        <v>7087154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,7 +3851,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,7 +3879,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124739096</v>
+        <v>124749500</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3890,19 +3913,23 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706304</v>
+        <v>706145</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087098</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3929,19 +3956,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3950,25 +3972,26 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124734940</v>
+        <v>124749246</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4002,19 +4025,23 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706418</v>
+        <v>706288</v>
       </c>
       <c r="R30" t="n">
-        <v>7087323</v>
+        <v>7087206</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,31 +4073,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749392</v>
+        <v>124735830</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4104,23 +4137,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706191</v>
+        <v>706344</v>
       </c>
       <c r="R31" t="n">
-        <v>7087129</v>
+        <v>7087202</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4147,14 +4176,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4163,29 +4197,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749013</v>
+        <v>124749686</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4194,31 +4227,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4226,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706446</v>
+        <v>705962</v>
       </c>
       <c r="R32" t="n">
-        <v>7087375</v>
+        <v>7086855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4262,11 +4294,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,10 +4321,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124735830</v>
+        <v>124744220</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4306,41 +4333,53 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706344</v>
+        <v>706411</v>
       </c>
       <c r="R33" t="n">
-        <v>7087202</v>
+        <v>7087322</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4367,19 +4406,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4394,19 +4423,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749575</v>
+        <v>124749414</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4450,10 +4479,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706133</v>
+        <v>706126</v>
       </c>
       <c r="R34" t="n">
-        <v>7087057</v>
+        <v>7087117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4518,7 +4547,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739585</v>
+        <v>124739661</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4558,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>705944</v>
+        <v>705952</v>
       </c>
       <c r="R35" t="n">
-        <v>7086954</v>
+        <v>7086928</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4593,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4603,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,7 +4659,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124736752</v>
+        <v>124749133</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4663,29 +4692,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706281</v>
+        <v>706364</v>
       </c>
       <c r="R36" t="n">
-        <v>7087219</v>
+        <v>7087314</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4723,25 +4747,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124733393</v>
+        <v>124736752</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4774,17 +4799,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706533</v>
+        <v>706281</v>
       </c>
       <c r="R37" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4814,19 +4848,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4841,12 +4865,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4970,7 +4994,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124734081</v>
+        <v>124749040</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5004,19 +5028,23 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706490</v>
+        <v>706431</v>
       </c>
       <c r="R39" t="n">
         <v>7087362</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5043,19 +5071,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5064,28 +5087,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124739921</v>
+        <v>124749263</v>
       </c>
       <c r="B40" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5094,41 +5118,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706034</v>
+        <v>706282</v>
       </c>
       <c r="R40" t="n">
-        <v>7086918</v>
+        <v>7087215</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5155,19 +5183,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:57</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5176,28 +5199,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124732613</v>
+        <v>124749184</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5206,41 +5230,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706654</v>
+        <v>706340</v>
       </c>
       <c r="R41" t="n">
-        <v>7087408</v>
+        <v>7087178</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5267,19 +5295,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5288,25 +5311,26 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124734648</v>
+        <v>124749331</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5340,19 +5364,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706405</v>
+        <v>706228</v>
       </c>
       <c r="R42" t="n">
-        <v>7087320</v>
+        <v>7087165</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,19 +5407,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5400,28 +5423,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749246</v>
+        <v>124736627</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5430,45 +5454,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706288</v>
+        <v>706292</v>
       </c>
       <c r="R43" t="n">
-        <v>7087206</v>
+        <v>7087225</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5500,40 +5520,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749350</v>
+        <v>124734903</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5542,45 +5556,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706238</v>
+        <v>706371</v>
       </c>
       <c r="R44" t="n">
-        <v>7087154</v>
+        <v>7087353</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5607,14 +5617,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5623,26 +5638,25 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124734745</v>
+        <v>124749086</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5676,19 +5690,23 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706401</v>
+        <v>706447</v>
       </c>
       <c r="R45" t="n">
-        <v>7087323</v>
+        <v>7087337</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5715,24 +5733,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5741,25 +5749,26 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749133</v>
+        <v>124739096</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5793,23 +5802,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706364</v>
+        <v>706304</v>
       </c>
       <c r="R46" t="n">
-        <v>7087314</v>
+        <v>7087194</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5836,40 +5841,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124739661</v>
+        <v>124738318</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5878,38 +5892,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705952</v>
+        <v>706281</v>
       </c>
       <c r="R47" t="n">
-        <v>7086928</v>
+        <v>7087219</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5939,19 +5953,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5966,22 +5970,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124733886</v>
+        <v>124749539</v>
       </c>
       <c r="B48" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5990,41 +5994,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706495</v>
+        <v>706157</v>
       </c>
       <c r="R48" t="n">
-        <v>7087369</v>
+        <v>7087072</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6051,24 +6059,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6077,28 +6075,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124736627</v>
+        <v>124749070</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6107,41 +6106,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706292</v>
+        <v>706442</v>
       </c>
       <c r="R49" t="n">
-        <v>7087225</v>
+        <v>7087349</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6173,34 +6176,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749686</v>
+        <v>124739909</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6209,44 +6218,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>705962</v>
+        <v>706048</v>
       </c>
       <c r="R50" t="n">
-        <v>7086855</v>
+        <v>7086914</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6284,26 +6299,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749184</v>
+        <v>124734081</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6337,23 +6351,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706340</v>
+        <v>706490</v>
       </c>
       <c r="R51" t="n">
-        <v>7087178</v>
+        <v>7087362</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6380,14 +6390,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6396,29 +6411,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124734903</v>
+        <v>124749392</v>
       </c>
       <c r="B52" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6427,41 +6441,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706371</v>
+        <v>706191</v>
       </c>
       <c r="R52" t="n">
-        <v>7087353</v>
+        <v>7087129</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6488,19 +6506,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6509,28 +6522,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124732683</v>
+        <v>124749013</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6539,41 +6553,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706597</v>
+        <v>706446</v>
       </c>
       <c r="R53" t="n">
-        <v>7087402</v>
+        <v>7087375</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6600,19 +6618,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6621,25 +6634,26 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749070</v>
+        <v>124749460</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6683,10 +6697,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706442</v>
+        <v>706115</v>
       </c>
       <c r="R54" t="n">
-        <v>7087349</v>
+        <v>7087088</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6723,7 +6737,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6751,7 +6765,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749539</v>
+        <v>124733393</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6785,23 +6799,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706157</v>
+        <v>706533</v>
       </c>
       <c r="R55" t="n">
-        <v>7087072</v>
+        <v>7087362</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6828,14 +6838,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6844,26 +6859,25 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749086</v>
+        <v>124749167</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6907,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706447</v>
+        <v>706354</v>
       </c>
       <c r="R56" t="n">
-        <v>7087337</v>
+        <v>7087195</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6975,10 +6989,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749040</v>
+        <v>124732683</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6987,45 +7001,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706431</v>
+        <v>706597</v>
       </c>
       <c r="R57" t="n">
-        <v>7087362</v>
+        <v>7087402</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7052,14 +7062,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7068,29 +7083,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124733522</v>
+        <v>124749376</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7099,41 +7113,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706523</v>
+        <v>706224</v>
       </c>
       <c r="R58" t="n">
-        <v>7087364</v>
+        <v>7087139</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7160,19 +7178,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7181,28 +7194,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124749290</v>
+        <v>124734648</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7211,49 +7225,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706276</v>
+        <v>706405</v>
       </c>
       <c r="R59" t="n">
-        <v>7087213</v>
+        <v>7087320</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7280,9 +7286,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7297,19 +7313,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124734139</v>
+        <v>124749657</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7343,19 +7359,23 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706472</v>
+        <v>705966</v>
       </c>
       <c r="R60" t="n">
-        <v>7087356</v>
+        <v>7086987</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7382,24 +7402,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7408,28 +7418,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124737518</v>
+        <v>124749290</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7438,41 +7449,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706341</v>
+        <v>706276</v>
       </c>
       <c r="R61" t="n">
-        <v>7087207</v>
+        <v>7087213</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7499,19 +7518,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7526,22 +7535,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124732401</v>
+        <v>124739580</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7554,34 +7563,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706665</v>
+        <v>706048</v>
       </c>
       <c r="R62" t="n">
-        <v>7087406</v>
+        <v>7086914</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7611,19 +7620,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7638,22 +7637,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749167</v>
+        <v>124734381</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7662,45 +7661,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706354</v>
+        <v>706473</v>
       </c>
       <c r="R63" t="n">
-        <v>7087195</v>
+        <v>7087334</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7727,14 +7722,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7743,29 +7743,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124739909</v>
+        <v>124732613</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7774,47 +7773,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706048</v>
+        <v>706654</v>
       </c>
       <c r="R64" t="n">
-        <v>7086914</v>
+        <v>7087408</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7844,9 +7834,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7861,19 +7861,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749657</v>
+        <v>124749575</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705966</v>
+        <v>706133</v>
       </c>
       <c r="R65" t="n">
-        <v>7086987</v>
+        <v>7087057</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749500</v>
+        <v>124737518</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8019,23 +8019,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706145</v>
+        <v>706341</v>
       </c>
       <c r="R66" t="n">
-        <v>7087098</v>
+        <v>7087207</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8062,14 +8058,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,19 +8079,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124739921</v>
+        <v>124749539</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,41 +2664,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706034</v>
+        <v>706157</v>
       </c>
       <c r="R18" t="n">
-        <v>7086918</v>
+        <v>7087072</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2725,19 +2729,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:57</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2746,28 +2745,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124735169</v>
+        <v>124739585</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,38 +2776,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706394</v>
+        <v>705944</v>
       </c>
       <c r="R19" t="n">
-        <v>7087340</v>
+        <v>7086954</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2837,9 +2837,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,19 +2864,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124734745</v>
+        <v>124734417</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2906,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706401</v>
+        <v>706465</v>
       </c>
       <c r="R20" t="n">
-        <v>7087323</v>
+        <v>7087346</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2941,7 +2951,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2961,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2983,7 +2993,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749111</v>
+        <v>124749331</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3027,10 +3037,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706398</v>
+        <v>706228</v>
       </c>
       <c r="R21" t="n">
-        <v>7087345</v>
+        <v>7087165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3067,7 +3077,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,7 +3105,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124734139</v>
+        <v>124735830</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3135,10 +3145,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706472</v>
+        <v>706344</v>
       </c>
       <c r="R22" t="n">
-        <v>7087356</v>
+        <v>7087202</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3170,7 +3180,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3180,12 +3190,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3212,7 +3217,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124732401</v>
+        <v>124732613</v>
       </c>
       <c r="B23" t="n">
         <v>91012</v>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706665</v>
+        <v>706654</v>
       </c>
       <c r="R23" t="n">
-        <v>7087406</v>
+        <v>7087408</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3287,7 +3292,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3297,7 +3302,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124734940</v>
+        <v>124736627</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3336,25 +3341,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3364,10 +3369,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706418</v>
+        <v>706292</v>
       </c>
       <c r="R24" t="n">
-        <v>7087323</v>
+        <v>7087225</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3426,7 +3431,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124739585</v>
+        <v>124749414</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3460,19 +3465,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705944</v>
+        <v>706126</v>
       </c>
       <c r="R25" t="n">
-        <v>7086954</v>
+        <v>7087117</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3499,19 +3508,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,28 +3524,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124733522</v>
+        <v>124749111</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3550,41 +3555,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706523</v>
+        <v>706398</v>
       </c>
       <c r="R26" t="n">
-        <v>7087364</v>
+        <v>7087345</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3611,19 +3620,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3632,28 +3636,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124733886</v>
+        <v>124749460</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3662,41 +3667,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706495</v>
+        <v>706115</v>
       </c>
       <c r="R27" t="n">
-        <v>7087369</v>
+        <v>7087088</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3723,24 +3732,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3749,25 +3748,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749350</v>
+        <v>124749263</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706238</v>
+        <v>706282</v>
       </c>
       <c r="R28" t="n">
-        <v>7087154</v>
+        <v>7087215</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3879,7 +3879,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749500</v>
+        <v>124749013</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706145</v>
+        <v>706446</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087375</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3991,7 +3991,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124749246</v>
+        <v>124739909</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4024,24 +4024,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706288</v>
+        <v>706048</v>
       </c>
       <c r="R30" t="n">
-        <v>7087206</v>
+        <v>7086914</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4073,37 +4078,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124735830</v>
+        <v>124749133</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4137,19 +4136,23 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706344</v>
+        <v>706364</v>
       </c>
       <c r="R31" t="n">
-        <v>7087202</v>
+        <v>7087314</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4176,49 +4179,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749686</v>
+        <v>124734381</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4231,40 +4225,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705962</v>
+        <v>706473</v>
       </c>
       <c r="R32" t="n">
-        <v>7086855</v>
+        <v>7087334</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4291,40 +4282,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124744220</v>
+        <v>124732401</v>
       </c>
       <c r="B33" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4333,53 +4333,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706411</v>
+        <v>706665</v>
       </c>
       <c r="R33" t="n">
-        <v>7087322</v>
+        <v>7087406</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4406,9 +4394,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4423,19 +4421,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749414</v>
+        <v>124749040</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4479,10 +4477,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706126</v>
+        <v>706431</v>
       </c>
       <c r="R34" t="n">
-        <v>7087117</v>
+        <v>7087362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4519,7 +4517,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,7 +4545,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124739661</v>
+        <v>124737518</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4583,14 +4581,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>705952</v>
+        <v>706341</v>
       </c>
       <c r="R35" t="n">
-        <v>7086928</v>
+        <v>7087207</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4622,7 +4620,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4630,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,7 +4657,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124749133</v>
+        <v>124734081</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4693,23 +4691,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706364</v>
+        <v>706490</v>
       </c>
       <c r="R36" t="n">
-        <v>7087314</v>
+        <v>7087362</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4736,40 +4730,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124736752</v>
+        <v>124739921</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,47 +4781,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706281</v>
+        <v>706034</v>
       </c>
       <c r="R37" t="n">
-        <v>7087219</v>
+        <v>7086918</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4848,9 +4842,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4865,22 +4869,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124734417</v>
+        <v>124738318</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4889,25 +4893,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4917,10 +4921,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706465</v>
+        <v>706281</v>
       </c>
       <c r="R38" t="n">
-        <v>7087346</v>
+        <v>7087219</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4950,24 +4954,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4982,19 +4971,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749040</v>
+        <v>124749500</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -5038,10 +5027,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706431</v>
+        <v>706145</v>
       </c>
       <c r="R39" t="n">
-        <v>7087362</v>
+        <v>7087098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5078,7 +5067,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5106,7 +5095,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749263</v>
+        <v>124749184</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5150,10 +5139,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706282</v>
+        <v>706340</v>
       </c>
       <c r="R40" t="n">
-        <v>7087215</v>
+        <v>7087178</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5218,7 +5207,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749184</v>
+        <v>124749070</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -5262,10 +5251,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706340</v>
+        <v>706442</v>
       </c>
       <c r="R41" t="n">
-        <v>7087178</v>
+        <v>7087349</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5330,10 +5319,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749331</v>
+        <v>124735169</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5342,45 +5331,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706228</v>
+        <v>706394</v>
       </c>
       <c r="R42" t="n">
-        <v>7087165</v>
+        <v>7087340</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5412,40 +5397,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124736627</v>
+        <v>124732683</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5458,21 +5437,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5482,10 +5461,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706292</v>
+        <v>706597</v>
       </c>
       <c r="R43" t="n">
-        <v>7087225</v>
+        <v>7087402</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5515,9 +5494,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5532,22 +5521,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124734903</v>
+        <v>124749246</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5556,41 +5545,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706371</v>
+        <v>706288</v>
       </c>
       <c r="R44" t="n">
-        <v>7087353</v>
+        <v>7087206</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5617,19 +5610,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5638,25 +5626,26 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749086</v>
+        <v>124736752</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5689,24 +5678,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706447</v>
+        <v>706281</v>
       </c>
       <c r="R45" t="n">
-        <v>7087337</v>
+        <v>7087219</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5738,37 +5732,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124739096</v>
+        <v>124733393</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5808,10 +5796,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706304</v>
+        <v>706533</v>
       </c>
       <c r="R46" t="n">
-        <v>7087194</v>
+        <v>7087362</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5843,7 +5831,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,7 +5841,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5880,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124738318</v>
+        <v>124749376</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5892,41 +5880,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706281</v>
+        <v>706224</v>
       </c>
       <c r="R47" t="n">
-        <v>7087219</v>
+        <v>7087139</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5958,31 +5950,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749539</v>
+        <v>124749086</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6026,10 +6024,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706157</v>
+        <v>706447</v>
       </c>
       <c r="R48" t="n">
-        <v>7087072</v>
+        <v>7087337</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6094,7 +6092,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749070</v>
+        <v>124739661</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6128,23 +6126,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706442</v>
+        <v>705952</v>
       </c>
       <c r="R49" t="n">
-        <v>7087349</v>
+        <v>7086928</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6171,14 +6165,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6187,26 +6186,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124739909</v>
+        <v>124739096</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6239,26 +6237,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706048</v>
+        <v>706304</v>
       </c>
       <c r="R50" t="n">
-        <v>7086914</v>
+        <v>7087194</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6288,9 +6277,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6305,19 +6304,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124734081</v>
+        <v>124734745</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6357,10 +6356,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706490</v>
+        <v>706401</v>
       </c>
       <c r="R51" t="n">
-        <v>7087362</v>
+        <v>7087323</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6392,7 +6391,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6402,7 +6401,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6429,7 +6433,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749392</v>
+        <v>124749575</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6473,10 +6477,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706191</v>
+        <v>706133</v>
       </c>
       <c r="R52" t="n">
-        <v>7087129</v>
+        <v>7087057</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6541,7 +6545,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749013</v>
+        <v>124749392</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6585,10 +6589,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706446</v>
+        <v>706191</v>
       </c>
       <c r="R53" t="n">
-        <v>7087375</v>
+        <v>7087129</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6625,7 +6629,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>20+ bladrosetter</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6653,7 +6657,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749460</v>
+        <v>124749167</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6697,10 +6701,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706115</v>
+        <v>706354</v>
       </c>
       <c r="R54" t="n">
-        <v>7087088</v>
+        <v>7087195</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6737,7 +6741,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6765,10 +6769,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124733393</v>
+        <v>124749686</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6777,41 +6781,44 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706533</v>
+        <v>705962</v>
       </c>
       <c r="R55" t="n">
-        <v>7087362</v>
+        <v>7086855</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6838,46 +6845,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749167</v>
+        <v>124749350</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6921,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706354</v>
+        <v>706238</v>
       </c>
       <c r="R56" t="n">
-        <v>7087195</v>
+        <v>7087154</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6961,7 +6959,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6989,10 +6987,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124732683</v>
+        <v>124749290</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7001,41 +6999,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706597</v>
+        <v>706276</v>
       </c>
       <c r="R57" t="n">
-        <v>7087402</v>
+        <v>7087213</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7062,19 +7068,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7089,22 +7085,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749376</v>
+        <v>124744220</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7113,31 +7109,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7145,10 +7149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706224</v>
+        <v>706411</v>
       </c>
       <c r="R58" t="n">
-        <v>7087139</v>
+        <v>7087322</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7183,18 +7187,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7213,7 +7211,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124734648</v>
+        <v>124734940</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7253,10 +7251,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706405</v>
+        <v>706418</v>
       </c>
       <c r="R59" t="n">
-        <v>7087320</v>
+        <v>7087323</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7286,19 +7284,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7313,19 +7301,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749657</v>
+        <v>124734139</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7359,23 +7347,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705966</v>
+        <v>706472</v>
       </c>
       <c r="R60" t="n">
-        <v>7086987</v>
+        <v>7087356</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7402,14 +7386,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,29 +7412,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749290</v>
+        <v>124749657</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7449,35 +7442,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7485,10 +7474,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706276</v>
+        <v>705966</v>
       </c>
       <c r="R61" t="n">
-        <v>7087213</v>
+        <v>7086987</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7523,12 +7512,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7547,10 +7542,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124739580</v>
+        <v>124734903</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7559,38 +7554,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706048</v>
+        <v>706371</v>
       </c>
       <c r="R62" t="n">
-        <v>7086914</v>
+        <v>7087353</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7620,9 +7615,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7637,19 +7642,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124734381</v>
+        <v>124739580</v>
       </c>
       <c r="B63" t="n">
         <v>57529</v>
@@ -7685,14 +7690,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706473</v>
+        <v>706048</v>
       </c>
       <c r="R63" t="n">
-        <v>7087334</v>
+        <v>7086914</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7722,19 +7727,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7749,22 +7744,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124732613</v>
+        <v>124733886</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7773,25 +7768,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7801,10 +7796,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706654</v>
+        <v>706495</v>
       </c>
       <c r="R64" t="n">
-        <v>7087408</v>
+        <v>7087369</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7836,7 +7831,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7846,7 +7841,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7873,10 +7873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749575</v>
+        <v>124733522</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,45 +7885,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706133</v>
+        <v>706523</v>
       </c>
       <c r="R65" t="n">
-        <v>7087057</v>
+        <v>7087364</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7950,14 +7946,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,26 +7967,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124737518</v>
+        <v>124734648</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706341</v>
+        <v>706405</v>
       </c>
       <c r="R66" t="n">
-        <v>7087207</v>
+        <v>7087320</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -4769,10 +4769,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124739921</v>
+        <v>124738318</v>
       </c>
       <c r="B37" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4785,34 +4785,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706034</v>
+        <v>706281</v>
       </c>
       <c r="R37" t="n">
-        <v>7086918</v>
+        <v>7087219</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4842,19 +4842,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4869,22 +4859,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124738318</v>
+        <v>124739921</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4897,34 +4887,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706281</v>
+        <v>706034</v>
       </c>
       <c r="R38" t="n">
-        <v>7087219</v>
+        <v>7086918</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4954,9 +4944,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,12 +4971,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -7873,10 +7873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124733522</v>
+        <v>124734648</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7885,25 +7885,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706523</v>
+        <v>706405</v>
       </c>
       <c r="R65" t="n">
-        <v>7087364</v>
+        <v>7087320</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7985,10 +7985,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124734648</v>
+        <v>124733522</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,25 +7997,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706405</v>
+        <v>706523</v>
       </c>
       <c r="R66" t="n">
-        <v>7087320</v>
+        <v>7087364</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749539</v>
+        <v>124736627</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,45 +2664,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706157</v>
+        <v>706292</v>
       </c>
       <c r="R18" t="n">
-        <v>7087072</v>
+        <v>7087225</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2734,40 +2730,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124739585</v>
+        <v>124738318</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,38 +2766,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705944</v>
+        <v>706281</v>
       </c>
       <c r="R19" t="n">
-        <v>7086954</v>
+        <v>7087219</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2837,19 +2827,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2864,19 +2844,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124734417</v>
+        <v>124749331</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2910,19 +2890,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706465</v>
+        <v>706228</v>
       </c>
       <c r="R20" t="n">
-        <v>7087346</v>
+        <v>7087165</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2949,24 +2933,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2975,25 +2949,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749331</v>
+        <v>124739909</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3026,24 +3001,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706228</v>
+        <v>706048</v>
       </c>
       <c r="R21" t="n">
-        <v>7087165</v>
+        <v>7086914</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3075,37 +3055,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124735830</v>
+        <v>124739096</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3145,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706344</v>
+        <v>706304</v>
       </c>
       <c r="R22" t="n">
-        <v>7087202</v>
+        <v>7087194</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3180,7 +3154,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3190,7 +3164,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3217,10 +3191,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124732613</v>
+        <v>124733886</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3229,25 +3203,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3257,10 +3231,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706654</v>
+        <v>706495</v>
       </c>
       <c r="R23" t="n">
-        <v>7087408</v>
+        <v>7087369</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3292,7 +3266,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3302,7 +3276,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3329,10 +3308,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124736627</v>
+        <v>124749111</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3341,41 +3320,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706292</v>
+        <v>706398</v>
       </c>
       <c r="R24" t="n">
-        <v>7087225</v>
+        <v>7087345</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3407,31 +3390,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749414</v>
+        <v>124739661</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3465,23 +3454,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706126</v>
+        <v>705952</v>
       </c>
       <c r="R25" t="n">
-        <v>7087117</v>
+        <v>7086928</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3508,14 +3493,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,26 +3514,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124749111</v>
+        <v>124749263</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3587,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706398</v>
+        <v>706282</v>
       </c>
       <c r="R26" t="n">
-        <v>7087345</v>
+        <v>7087215</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3655,7 +3644,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749460</v>
+        <v>124749133</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3699,10 +3688,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706115</v>
+        <v>706364</v>
       </c>
       <c r="R27" t="n">
-        <v>7087088</v>
+        <v>7087314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,11 +3724,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3767,7 +3751,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749263</v>
+        <v>124734081</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3801,23 +3785,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706282</v>
+        <v>706490</v>
       </c>
       <c r="R28" t="n">
-        <v>7087215</v>
+        <v>7087362</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3844,14 +3824,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,29 +3845,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749013</v>
+        <v>124744220</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,31 +3875,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3923,10 +3915,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706446</v>
+        <v>706411</v>
       </c>
       <c r="R29" t="n">
-        <v>7087375</v>
+        <v>7087322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3961,18 +3953,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3991,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124739909</v>
+        <v>124732613</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,47 +3989,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706048</v>
+        <v>706654</v>
       </c>
       <c r="R30" t="n">
-        <v>7086914</v>
+        <v>7087408</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4073,9 +4050,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,22 +4077,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749133</v>
+        <v>124732683</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4114,45 +4101,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706364</v>
+        <v>706597</v>
       </c>
       <c r="R31" t="n">
-        <v>7087314</v>
+        <v>7087402</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4179,40 +4162,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124734381</v>
+        <v>124734139</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4221,25 +4213,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4249,10 +4241,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706473</v>
+        <v>706472</v>
       </c>
       <c r="R32" t="n">
-        <v>7087334</v>
+        <v>7087356</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4284,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,7 +4286,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4321,10 +4318,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124732401</v>
+        <v>124734745</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4333,25 +4330,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4361,10 +4358,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706665</v>
+        <v>706401</v>
       </c>
       <c r="R33" t="n">
-        <v>7087406</v>
+        <v>7087323</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4396,7 +4393,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4406,7 +4403,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4433,7 +4435,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749040</v>
+        <v>124749500</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4477,10 +4479,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706431</v>
+        <v>706145</v>
       </c>
       <c r="R34" t="n">
-        <v>7087362</v>
+        <v>7087098</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4517,7 +4519,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,10 +4547,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124737518</v>
+        <v>124735169</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4557,25 +4559,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4585,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706341</v>
+        <v>706394</v>
       </c>
       <c r="R35" t="n">
-        <v>7087207</v>
+        <v>7087340</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4618,19 +4620,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4645,22 +4637,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124734081</v>
+        <v>124732401</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4669,25 +4661,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4697,10 +4689,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706490</v>
+        <v>706665</v>
       </c>
       <c r="R36" t="n">
-        <v>7087362</v>
+        <v>7087406</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4732,7 +4724,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4742,7 +4734,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,10 +4761,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124738318</v>
+        <v>124734903</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4785,21 +4777,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4809,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706281</v>
+        <v>706371</v>
       </c>
       <c r="R37" t="n">
-        <v>7087219</v>
+        <v>7087353</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4842,9 +4834,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4859,22 +4861,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124739921</v>
+        <v>124749070</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4883,41 +4885,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706034</v>
+        <v>706442</v>
       </c>
       <c r="R38" t="n">
-        <v>7086918</v>
+        <v>7087349</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4944,19 +4950,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:57</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4965,28 +4966,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749500</v>
+        <v>124749686</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4995,31 +4997,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5027,10 +5028,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706145</v>
+        <v>705962</v>
       </c>
       <c r="R39" t="n">
-        <v>7087098</v>
+        <v>7086855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5063,11 +5064,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5095,7 +5091,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749184</v>
+        <v>124749414</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -5139,10 +5135,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706340</v>
+        <v>706126</v>
       </c>
       <c r="R40" t="n">
-        <v>7087178</v>
+        <v>7087117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5207,10 +5203,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749070</v>
+        <v>124739921</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5219,45 +5215,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706442</v>
+        <v>706034</v>
       </c>
       <c r="R41" t="n">
-        <v>7087349</v>
+        <v>7086918</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5284,14 +5276,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5300,29 +5297,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124735169</v>
+        <v>124737518</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5331,25 +5327,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5359,10 +5355,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706394</v>
+        <v>706341</v>
       </c>
       <c r="R42" t="n">
-        <v>7087340</v>
+        <v>7087207</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5392,9 +5388,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5409,22 +5415,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124732683</v>
+        <v>124736752</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5433,38 +5439,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706597</v>
+        <v>706281</v>
       </c>
       <c r="R43" t="n">
-        <v>7087402</v>
+        <v>7087219</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5494,19 +5509,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5521,19 +5526,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749246</v>
+        <v>124749575</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5577,10 +5582,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706288</v>
+        <v>706133</v>
       </c>
       <c r="R44" t="n">
-        <v>7087206</v>
+        <v>7087057</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5617,7 +5622,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5645,7 +5650,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124736752</v>
+        <v>124735830</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5678,26 +5683,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706281</v>
+        <v>706344</v>
       </c>
       <c r="R45" t="n">
-        <v>7087219</v>
+        <v>7087202</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5727,9 +5723,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5744,19 +5750,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124733393</v>
+        <v>124749539</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5790,19 +5796,23 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706533</v>
+        <v>706157</v>
       </c>
       <c r="R46" t="n">
-        <v>7087362</v>
+        <v>7087072</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5829,19 +5839,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,25 +5855,26 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749376</v>
+        <v>124734648</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5902,23 +5908,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706224</v>
+        <v>706405</v>
       </c>
       <c r="R47" t="n">
-        <v>7087139</v>
+        <v>7087320</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5945,14 +5947,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5961,26 +5968,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749086</v>
+        <v>124749184</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6024,10 +6030,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706447</v>
+        <v>706340</v>
       </c>
       <c r="R48" t="n">
-        <v>7087337</v>
+        <v>7087178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6092,7 +6098,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124739661</v>
+        <v>124749246</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6126,19 +6132,23 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>705952</v>
+        <v>706288</v>
       </c>
       <c r="R49" t="n">
-        <v>7086928</v>
+        <v>7087206</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6165,19 +6175,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6186,25 +6191,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124739096</v>
+        <v>124749040</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6238,19 +6244,23 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706304</v>
+        <v>706431</v>
       </c>
       <c r="R50" t="n">
-        <v>7087194</v>
+        <v>7087362</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,19 +6287,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,28 +6303,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124734745</v>
+        <v>124749290</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6328,41 +6334,49 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706401</v>
+        <v>706276</v>
       </c>
       <c r="R51" t="n">
-        <v>7087323</v>
+        <v>7087213</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6389,24 +6403,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6421,22 +6420,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749575</v>
+        <v>124739580</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6445,45 +6444,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706133</v>
+        <v>706048</v>
       </c>
       <c r="R52" t="n">
-        <v>7087057</v>
+        <v>7086914</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6515,37 +6510,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749392</v>
+        <v>124734940</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6579,23 +6568,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706191</v>
+        <v>706418</v>
       </c>
       <c r="R53" t="n">
-        <v>7087129</v>
+        <v>7087323</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6627,37 +6612,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124749167</v>
+        <v>124739585</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6691,23 +6670,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706354</v>
+        <v>705944</v>
       </c>
       <c r="R54" t="n">
-        <v>7087195</v>
+        <v>7086954</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6734,14 +6709,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6750,29 +6730,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749686</v>
+        <v>124749376</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6781,30 +6760,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6812,10 +6792,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>705962</v>
+        <v>706224</v>
       </c>
       <c r="R55" t="n">
-        <v>7086855</v>
+        <v>7087139</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6848,6 +6828,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6875,7 +6860,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749350</v>
+        <v>124749013</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706238</v>
+        <v>706446</v>
       </c>
       <c r="R56" t="n">
-        <v>7087154</v>
+        <v>7087375</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6959,7 +6944,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6987,10 +6972,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749290</v>
+        <v>124749460</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,35 +6984,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7035,10 +7016,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706276</v>
+        <v>706115</v>
       </c>
       <c r="R57" t="n">
-        <v>7087213</v>
+        <v>7087088</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7073,12 +7054,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7097,10 +7084,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124744220</v>
+        <v>124749167</v>
       </c>
       <c r="B58" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7109,39 +7096,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7149,10 +7128,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706411</v>
+        <v>706354</v>
       </c>
       <c r="R58" t="n">
-        <v>7087322</v>
+        <v>7087195</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,12 +7166,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7211,7 +7196,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124734940</v>
+        <v>124734417</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7251,10 +7236,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706418</v>
+        <v>706465</v>
       </c>
       <c r="R59" t="n">
-        <v>7087323</v>
+        <v>7087346</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7284,9 +7269,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7301,19 +7301,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124734139</v>
+        <v>124749657</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7347,19 +7347,23 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706472</v>
+        <v>705966</v>
       </c>
       <c r="R60" t="n">
-        <v>7087356</v>
+        <v>7086987</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7386,24 +7390,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7412,28 +7406,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749657</v>
+        <v>124734381</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7442,45 +7437,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705966</v>
+        <v>706473</v>
       </c>
       <c r="R61" t="n">
-        <v>7086987</v>
+        <v>7087334</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7507,14 +7498,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7523,29 +7519,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124734903</v>
+        <v>124733522</v>
       </c>
       <c r="B62" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7554,25 +7549,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7582,10 +7577,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706371</v>
+        <v>706523</v>
       </c>
       <c r="R62" t="n">
-        <v>7087353</v>
+        <v>7087364</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7617,7 +7612,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7627,7 +7622,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7654,10 +7649,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124739580</v>
+        <v>124733393</v>
       </c>
       <c r="B63" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7666,38 +7661,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706048</v>
+        <v>706533</v>
       </c>
       <c r="R63" t="n">
-        <v>7086914</v>
+        <v>7087362</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7727,9 +7722,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7744,22 +7749,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124733886</v>
+        <v>124749350</v>
       </c>
       <c r="B64" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7768,41 +7773,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706495</v>
+        <v>706238</v>
       </c>
       <c r="R64" t="n">
-        <v>7087369</v>
+        <v>7087154</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7829,24 +7838,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,25 +7854,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124734648</v>
+        <v>124749392</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7907,19 +7907,23 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706405</v>
+        <v>706191</v>
       </c>
       <c r="R65" t="n">
-        <v>7087320</v>
+        <v>7087129</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7946,19 +7950,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7967,28 +7966,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124733522</v>
+        <v>124749086</v>
       </c>
       <c r="B66" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7997,41 +7997,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706523</v>
+        <v>706447</v>
       </c>
       <c r="R66" t="n">
-        <v>7087364</v>
+        <v>7087337</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8058,19 +8062,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8079,18 +8078,19 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -5203,10 +5203,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124739921</v>
+        <v>124737518</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,38 +5215,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706034</v>
+        <v>706341</v>
       </c>
       <c r="R41" t="n">
-        <v>7086918</v>
+        <v>7087207</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,10 +5315,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124737518</v>
+        <v>124739921</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5327,38 +5327,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706341</v>
+        <v>706034</v>
       </c>
       <c r="R42" t="n">
-        <v>7087207</v>
+        <v>7086918</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749290</v>
+        <v>124739580</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6334,49 +6334,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706276</v>
+        <v>706048</v>
       </c>
       <c r="R51" t="n">
-        <v>7087213</v>
+        <v>7086914</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6420,22 +6412,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124739580</v>
+        <v>124749376</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,41 +6436,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706048</v>
+        <v>706224</v>
       </c>
       <c r="R52" t="n">
-        <v>7086914</v>
+        <v>7087139</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,24 +6506,30 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6748,10 +6750,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749376</v>
+        <v>124749290</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6760,31 +6762,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6792,10 +6798,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706224</v>
+        <v>706276</v>
       </c>
       <c r="R55" t="n">
-        <v>7087139</v>
+        <v>7087213</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6830,18 +6836,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124736627</v>
+        <v>124732613</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2668,21 +2668,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706292</v>
+        <v>706654</v>
       </c>
       <c r="R18" t="n">
-        <v>7087225</v>
+        <v>7087408</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2725,9 +2725,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2742,22 +2752,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124738318</v>
+        <v>124749070</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2766,41 +2776,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706281</v>
+        <v>706442</v>
       </c>
       <c r="R19" t="n">
-        <v>7087219</v>
+        <v>7087349</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2832,31 +2846,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749331</v>
+        <v>124749414</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2900,10 +2920,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706228</v>
+        <v>706126</v>
       </c>
       <c r="R20" t="n">
-        <v>7087165</v>
+        <v>7087117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2940,7 +2960,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,7 +2988,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124739909</v>
+        <v>124737966</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3003,7 +3023,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3013,14 +3033,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706048</v>
+        <v>706281</v>
       </c>
       <c r="R21" t="n">
-        <v>7086914</v>
+        <v>7087219</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3079,7 +3099,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124739096</v>
+        <v>124749575</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3113,19 +3133,23 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706304</v>
+        <v>706133</v>
       </c>
       <c r="R22" t="n">
-        <v>7087194</v>
+        <v>7087057</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3152,19 +3176,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,28 +3192,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124733886</v>
+        <v>124749013</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,41 +3223,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706495</v>
+        <v>706446</v>
       </c>
       <c r="R23" t="n">
-        <v>7087369</v>
+        <v>7087375</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3264,24 +3288,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,18 +3304,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3420,7 +3435,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124739661</v>
+        <v>124749500</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3454,19 +3469,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705952</v>
+        <v>706145</v>
       </c>
       <c r="R25" t="n">
-        <v>7086928</v>
+        <v>7087098</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3493,19 +3512,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,25 +3528,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124749263</v>
+        <v>124749331</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3576,10 +3591,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706282</v>
+        <v>706228</v>
       </c>
       <c r="R26" t="n">
-        <v>7087215</v>
+        <v>7087165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3616,7 +3631,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,10 +3659,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749133</v>
+        <v>124736627</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3656,45 +3671,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706364</v>
+        <v>706292</v>
       </c>
       <c r="R27" t="n">
-        <v>7087314</v>
+        <v>7087225</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3732,26 +3743,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124734081</v>
+        <v>124749539</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3785,19 +3795,23 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706490</v>
+        <v>706157</v>
       </c>
       <c r="R28" t="n">
-        <v>7087362</v>
+        <v>7087072</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,19 +3838,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3845,28 +3854,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124744220</v>
+        <v>124749392</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3875,39 +3885,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3915,10 +3917,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706411</v>
+        <v>706191</v>
       </c>
       <c r="R29" t="n">
-        <v>7087322</v>
+        <v>7087129</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3953,12 +3955,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3977,10 +3985,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732613</v>
+        <v>124739909</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3989,38 +3997,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706654</v>
+        <v>706048</v>
       </c>
       <c r="R30" t="n">
-        <v>7087408</v>
+        <v>7086914</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4050,19 +4067,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,22 +4084,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124732683</v>
+        <v>124749290</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4101,41 +4108,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706597</v>
+        <v>706276</v>
       </c>
       <c r="R31" t="n">
-        <v>7087402</v>
+        <v>7087213</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,19 +4177,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4189,19 +4194,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124734139</v>
+        <v>124734745</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4241,10 +4246,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706472</v>
+        <v>706401</v>
       </c>
       <c r="R32" t="n">
-        <v>7087356</v>
+        <v>7087323</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4276,7 +4281,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,12 +4291,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4318,7 +4323,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124734745</v>
+        <v>124749184</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4352,19 +4357,23 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706401</v>
+        <v>706340</v>
       </c>
       <c r="R33" t="n">
-        <v>7087323</v>
+        <v>7087178</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4391,24 +4400,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4417,25 +4416,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749500</v>
+        <v>124739585</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4469,23 +4469,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706145</v>
+        <v>705944</v>
       </c>
       <c r="R34" t="n">
-        <v>7087098</v>
+        <v>7086954</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4512,14 +4508,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4528,29 +4529,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124735169</v>
+        <v>124734903</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4559,25 +4559,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706394</v>
+        <v>706371</v>
       </c>
       <c r="R35" t="n">
-        <v>7087340</v>
+        <v>7087353</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4620,9 +4620,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4637,22 +4647,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124732401</v>
+        <v>124739096</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4661,25 +4671,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706665</v>
+        <v>706304</v>
       </c>
       <c r="R36" t="n">
-        <v>7087406</v>
+        <v>7087194</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4724,7 +4734,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4734,7 +4744,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,10 +4771,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124734903</v>
+        <v>124749460</v>
       </c>
       <c r="B37" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,41 +4783,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706371</v>
+        <v>706115</v>
       </c>
       <c r="R37" t="n">
-        <v>7087353</v>
+        <v>7087088</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4834,19 +4848,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,28 +4864,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124749070</v>
+        <v>124739921</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4885,45 +4895,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706442</v>
+        <v>706034</v>
       </c>
       <c r="R38" t="n">
-        <v>7087349</v>
+        <v>7086918</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4950,14 +4956,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4966,29 +4977,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124749686</v>
+        <v>124733522</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5001,40 +5011,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705962</v>
+        <v>706523</v>
       </c>
       <c r="R39" t="n">
-        <v>7086855</v>
+        <v>7087364</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5061,40 +5068,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749414</v>
+        <v>124739580</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,45 +5119,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706126</v>
+        <v>706048</v>
       </c>
       <c r="R40" t="n">
-        <v>7087117</v>
+        <v>7086914</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5173,40 +5185,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124737518</v>
+        <v>124749686</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,41 +5221,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706341</v>
+        <v>705962</v>
       </c>
       <c r="R41" t="n">
-        <v>7087207</v>
+        <v>7086855</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5276,49 +5285,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124739921</v>
+        <v>124749246</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5327,41 +5327,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706034</v>
+        <v>706288</v>
       </c>
       <c r="R42" t="n">
-        <v>7086918</v>
+        <v>7087206</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5388,19 +5392,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:57</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5409,25 +5408,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124736752</v>
+        <v>124749040</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5460,29 +5460,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706281</v>
+        <v>706431</v>
       </c>
       <c r="R43" t="n">
-        <v>7087219</v>
+        <v>7087362</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5514,34 +5509,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124749575</v>
+        <v>124738318</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5550,45 +5551,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706133</v>
+        <v>706281</v>
       </c>
       <c r="R44" t="n">
-        <v>7087057</v>
+        <v>7087219</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5620,37 +5617,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124735830</v>
+        <v>124734648</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5690,10 +5681,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706344</v>
+        <v>706405</v>
       </c>
       <c r="R45" t="n">
-        <v>7087202</v>
+        <v>7087320</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5725,7 +5716,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5735,7 +5726,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5762,7 +5753,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749539</v>
+        <v>124749350</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5806,10 +5797,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706157</v>
+        <v>706238</v>
       </c>
       <c r="R46" t="n">
-        <v>7087072</v>
+        <v>7087154</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5846,7 +5837,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5874,7 +5865,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124734648</v>
+        <v>124749086</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5908,19 +5899,23 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706405</v>
+        <v>706447</v>
       </c>
       <c r="R47" t="n">
-        <v>7087320</v>
+        <v>7087337</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5947,19 +5942,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5968,28 +5958,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124749184</v>
+        <v>124734381</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5998,45 +5989,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706340</v>
+        <v>706473</v>
       </c>
       <c r="R48" t="n">
-        <v>7087178</v>
+        <v>7087334</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6063,14 +6050,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,26 +6071,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124749246</v>
+        <v>124734940</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -6132,23 +6123,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706288</v>
+        <v>706418</v>
       </c>
       <c r="R49" t="n">
-        <v>7087206</v>
+        <v>7087323</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6180,37 +6167,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749040</v>
+        <v>124737518</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6244,23 +6225,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706431</v>
+        <v>706341</v>
       </c>
       <c r="R50" t="n">
-        <v>7087362</v>
+        <v>7087207</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6287,14 +6264,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6303,29 +6285,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124739580</v>
+        <v>124749376</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6334,41 +6315,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706048</v>
+        <v>706224</v>
       </c>
       <c r="R51" t="n">
-        <v>7086914</v>
+        <v>7087139</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6400,31 +6385,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749376</v>
+        <v>124733393</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6458,23 +6449,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706224</v>
+        <v>706533</v>
       </c>
       <c r="R52" t="n">
-        <v>7087139</v>
+        <v>7087362</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6501,14 +6488,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6517,29 +6509,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124734940</v>
+        <v>124735169</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6548,25 +6539,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6576,10 +6567,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706418</v>
+        <v>706394</v>
       </c>
       <c r="R53" t="n">
-        <v>7087323</v>
+        <v>7087340</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6638,10 +6629,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124739585</v>
+        <v>124744220</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6650,41 +6641,53 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705944</v>
+        <v>706411</v>
       </c>
       <c r="R54" t="n">
-        <v>7086954</v>
+        <v>7087322</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6711,19 +6714,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,22 +6731,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749290</v>
+        <v>124749133</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6762,35 +6755,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6798,10 +6787,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706276</v>
+        <v>706364</v>
       </c>
       <c r="R55" t="n">
-        <v>7087213</v>
+        <v>7087314</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6842,6 +6831,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6860,7 +6850,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749013</v>
+        <v>124735830</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6894,23 +6884,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706446</v>
+        <v>706344</v>
       </c>
       <c r="R56" t="n">
-        <v>7087375</v>
+        <v>7087202</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6937,14 +6923,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6953,26 +6944,25 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749460</v>
+        <v>124734139</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7006,23 +6996,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706115</v>
+        <v>706472</v>
       </c>
       <c r="R57" t="n">
-        <v>7087088</v>
+        <v>7087356</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7049,14 +7035,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7065,29 +7061,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749167</v>
+        <v>124732401</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7096,45 +7091,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706354</v>
+        <v>706665</v>
       </c>
       <c r="R58" t="n">
-        <v>7087195</v>
+        <v>7087406</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7161,14 +7152,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7177,29 +7173,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124734417</v>
+        <v>124733886</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7208,25 +7203,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7236,10 +7231,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706465</v>
+        <v>706495</v>
       </c>
       <c r="R59" t="n">
-        <v>7087346</v>
+        <v>7087369</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7271,7 +7266,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7281,12 +7276,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7313,7 +7308,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749657</v>
+        <v>124749167</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7357,10 +7352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705966</v>
+        <v>706354</v>
       </c>
       <c r="R60" t="n">
-        <v>7086987</v>
+        <v>7087195</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7425,10 +7420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124734381</v>
+        <v>124749263</v>
       </c>
       <c r="B61" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7437,41 +7432,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706473</v>
+        <v>706282</v>
       </c>
       <c r="R61" t="n">
-        <v>7087334</v>
+        <v>7087215</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7498,19 +7497,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7519,28 +7513,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124733522</v>
+        <v>124749657</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7549,41 +7544,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706523</v>
+        <v>705966</v>
       </c>
       <c r="R62" t="n">
-        <v>7087364</v>
+        <v>7086987</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7610,19 +7609,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7631,28 +7625,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124733393</v>
+        <v>124732683</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7661,25 +7656,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7689,10 +7684,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706533</v>
+        <v>706597</v>
       </c>
       <c r="R63" t="n">
-        <v>7087362</v>
+        <v>7087402</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7724,7 +7719,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7734,7 +7729,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,7 +7756,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124749350</v>
+        <v>124734417</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7795,23 +7790,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706238</v>
+        <v>706465</v>
       </c>
       <c r="R64" t="n">
-        <v>7087154</v>
+        <v>7087346</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7838,14 +7829,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7854,26 +7855,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749392</v>
+        <v>124734081</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7907,23 +7907,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706191</v>
+        <v>706490</v>
       </c>
       <c r="R65" t="n">
-        <v>7087129</v>
+        <v>7087362</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7950,14 +7946,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,26 +7967,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749086</v>
+        <v>124739661</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -8019,23 +8019,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706447</v>
+        <v>705952</v>
       </c>
       <c r="R66" t="n">
-        <v>7087337</v>
+        <v>7086928</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8062,14 +8058,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,19 +8079,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124732613</v>
+        <v>124749246</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,41 +2664,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706654</v>
+        <v>706288</v>
       </c>
       <c r="R18" t="n">
-        <v>7087408</v>
+        <v>7087206</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2725,19 +2729,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2746,28 +2745,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124749070</v>
+        <v>124749414</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706442</v>
+        <v>706126</v>
       </c>
       <c r="R19" t="n">
-        <v>7087349</v>
+        <v>7087117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2876,10 +2876,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749414</v>
+        <v>124749111</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706126</v>
+        <v>706398</v>
       </c>
       <c r="R20" t="n">
-        <v>7087117</v>
+        <v>7087345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124737966</v>
+        <v>124739585</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3021,26 +3021,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706281</v>
+        <v>705944</v>
       </c>
       <c r="R21" t="n">
-        <v>7087219</v>
+        <v>7086954</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3070,9 +3061,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,22 +3088,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749575</v>
+        <v>124749460</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,10 +3144,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706133</v>
+        <v>706115</v>
       </c>
       <c r="R22" t="n">
-        <v>7087057</v>
+        <v>7087088</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3183,7 +3184,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3211,10 +3212,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749013</v>
+        <v>124734081</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3245,23 +3246,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706446</v>
+        <v>706490</v>
       </c>
       <c r="R23" t="n">
-        <v>7087375</v>
+        <v>7087362</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3288,14 +3285,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3304,29 +3306,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124749111</v>
+        <v>124733522</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3335,45 +3336,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706398</v>
+        <v>706523</v>
       </c>
       <c r="R24" t="n">
-        <v>7087345</v>
+        <v>7087364</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3400,14 +3397,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3416,29 +3418,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749500</v>
+        <v>124734417</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3469,23 +3470,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706145</v>
+        <v>706465</v>
       </c>
       <c r="R25" t="n">
-        <v>7087098</v>
+        <v>7087346</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3512,14 +3509,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,19 +3535,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3550,7 +3556,7 @@
         <v>124749331</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3659,10 +3665,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124736627</v>
+        <v>124749500</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3671,41 +3677,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706292</v>
+        <v>706145</v>
       </c>
       <c r="R27" t="n">
-        <v>7087225</v>
+        <v>7087098</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3737,34 +3747,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749539</v>
+        <v>124734940</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3795,23 +3811,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706157</v>
+        <v>706418</v>
       </c>
       <c r="R28" t="n">
-        <v>7087072</v>
+        <v>7087323</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3843,40 +3855,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749392</v>
+        <v>124749575</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3917,10 +3923,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706191</v>
+        <v>706133</v>
       </c>
       <c r="R29" t="n">
-        <v>7087129</v>
+        <v>7087057</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3985,10 +3991,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124739909</v>
+        <v>124732613</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3997,47 +4003,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706048</v>
+        <v>706654</v>
       </c>
       <c r="R30" t="n">
-        <v>7086914</v>
+        <v>7087408</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4067,9 +4064,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,22 +4091,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749290</v>
+        <v>124734381</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4108,49 +4115,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706276</v>
+        <v>706473</v>
       </c>
       <c r="R31" t="n">
-        <v>7087213</v>
+        <v>7087334</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4177,9 +4176,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4194,22 +4203,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124734745</v>
+        <v>124749376</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4240,19 +4249,23 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706401</v>
+        <v>706224</v>
       </c>
       <c r="R32" t="n">
-        <v>7087323</v>
+        <v>7087139</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,24 +4292,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4305,28 +4308,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749184</v>
+        <v>124749657</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706340</v>
+        <v>705966</v>
       </c>
       <c r="R33" t="n">
-        <v>7087178</v>
+        <v>7086987</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4435,10 +4439,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124739585</v>
+        <v>124739096</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4471,14 +4475,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>705944</v>
+        <v>706304</v>
       </c>
       <c r="R34" t="n">
-        <v>7086954</v>
+        <v>7087194</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4510,7 +4514,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4520,7 +4524,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,10 +4551,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124734903</v>
+        <v>124732683</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4559,25 +4563,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4591,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706371</v>
+        <v>706597</v>
       </c>
       <c r="R35" t="n">
-        <v>7087353</v>
+        <v>7087402</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4622,7 +4626,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,10 +4663,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124739096</v>
+        <v>124749290</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,41 +4675,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706304</v>
+        <v>706276</v>
       </c>
       <c r="R36" t="n">
-        <v>7087194</v>
+        <v>7087213</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4732,19 +4744,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,22 +4761,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124749460</v>
+        <v>124744220</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4783,31 +4785,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4815,10 +4825,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706115</v>
+        <v>706411</v>
       </c>
       <c r="R37" t="n">
-        <v>7087088</v>
+        <v>7087322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4853,18 +4863,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4883,10 +4887,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124739921</v>
+        <v>124739580</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>57632</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4895,25 +4899,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4923,10 +4927,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706034</v>
+        <v>706048</v>
       </c>
       <c r="R38" t="n">
-        <v>7086918</v>
+        <v>7086914</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4956,19 +4960,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4983,22 +4977,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124733522</v>
+        <v>124736627</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5035,10 +5029,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706523</v>
+        <v>706292</v>
       </c>
       <c r="R39" t="n">
-        <v>7087364</v>
+        <v>7087225</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5068,19 +5062,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5095,22 +5079,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124739580</v>
+        <v>124749350</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5119,41 +5103,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706048</v>
+        <v>706238</v>
       </c>
       <c r="R40" t="n">
-        <v>7086914</v>
+        <v>7087154</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5185,34 +5173,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749686</v>
+        <v>124735830</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,44 +5215,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705962</v>
+        <v>706344</v>
       </c>
       <c r="R41" t="n">
-        <v>7086855</v>
+        <v>7087202</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5285,40 +5276,49 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749246</v>
+        <v>124749263</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706288</v>
+        <v>706282</v>
       </c>
       <c r="R42" t="n">
-        <v>7087206</v>
+        <v>7087215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749040</v>
+        <v>124749184</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706431</v>
+        <v>706340</v>
       </c>
       <c r="R43" t="n">
-        <v>7087362</v>
+        <v>7087178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5539,10 +5539,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124738318</v>
+        <v>124737518</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,25 +5551,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706281</v>
+        <v>706341</v>
       </c>
       <c r="R44" t="n">
-        <v>7087219</v>
+        <v>7087207</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5612,9 +5612,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5629,22 +5639,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124734648</v>
+        <v>124739909</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5674,17 +5684,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706405</v>
+        <v>706048</v>
       </c>
       <c r="R45" t="n">
-        <v>7087320</v>
+        <v>7086914</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5714,19 +5733,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5741,22 +5750,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124749350</v>
+        <v>124734903</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5765,45 +5774,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706238</v>
+        <v>706371</v>
       </c>
       <c r="R46" t="n">
-        <v>7087154</v>
+        <v>7087353</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5830,14 +5835,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5846,29 +5856,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124749086</v>
+        <v>124737966</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5898,24 +5907,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706447</v>
+        <v>706281</v>
       </c>
       <c r="R47" t="n">
-        <v>7087337</v>
+        <v>7087219</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5947,40 +5961,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124734381</v>
+        <v>124732401</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>91166</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5993,21 +6001,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6017,10 +6025,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706473</v>
+        <v>706665</v>
       </c>
       <c r="R48" t="n">
-        <v>7087334</v>
+        <v>7087406</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6052,7 +6060,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6062,7 +6070,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6089,10 +6097,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124734940</v>
+        <v>124739921</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6101,38 +6109,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706418</v>
+        <v>706034</v>
       </c>
       <c r="R49" t="n">
-        <v>7087323</v>
+        <v>7086918</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6162,9 +6170,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,22 +6197,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124737518</v>
+        <v>124749040</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6225,19 +6243,23 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706341</v>
+        <v>706431</v>
       </c>
       <c r="R50" t="n">
-        <v>7087207</v>
+        <v>7087362</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6264,19 +6286,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6285,28 +6302,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749376</v>
+        <v>124735169</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6315,45 +6333,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706224</v>
+        <v>706394</v>
       </c>
       <c r="R51" t="n">
-        <v>7087139</v>
+        <v>7087340</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6385,40 +6399,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124733393</v>
+        <v>124738318</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6427,25 +6435,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6455,10 +6463,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706533</v>
+        <v>706281</v>
       </c>
       <c r="R52" t="n">
-        <v>7087362</v>
+        <v>7087219</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6488,19 +6496,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6515,22 +6513,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124735169</v>
+        <v>124734648</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6539,25 +6537,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6567,10 +6565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706394</v>
+        <v>706405</v>
       </c>
       <c r="R53" t="n">
-        <v>7087340</v>
+        <v>7087320</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6600,9 +6598,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6617,22 +6625,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124744220</v>
+        <v>124734745</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6641,53 +6649,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706411</v>
+        <v>706401</v>
       </c>
       <c r="R54" t="n">
-        <v>7087322</v>
+        <v>7087323</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6714,9 +6710,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6731,22 +6742,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124749133</v>
+        <v>124734139</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6777,23 +6788,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706364</v>
+        <v>706472</v>
       </c>
       <c r="R55" t="n">
-        <v>7087314</v>
+        <v>7087356</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6820,40 +6827,54 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124735830</v>
+        <v>124749167</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6884,19 +6905,23 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706344</v>
+        <v>706354</v>
       </c>
       <c r="R56" t="n">
-        <v>7087202</v>
+        <v>7087195</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6923,19 +6948,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6944,28 +6964,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124734139</v>
+        <v>124749070</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6996,19 +7017,23 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706472</v>
+        <v>706442</v>
       </c>
       <c r="R57" t="n">
-        <v>7087356</v>
+        <v>7087349</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7035,24 +7060,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Mer än 30</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7061,28 +7076,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124732401</v>
+        <v>124749686</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7113,19 +7129,22 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706665</v>
+        <v>705962</v>
       </c>
       <c r="R58" t="n">
-        <v>7087406</v>
+        <v>7086855</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7152,49 +7171,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124733886</v>
+        <v>124739661</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7203,38 +7213,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706495</v>
+        <v>705952</v>
       </c>
       <c r="R59" t="n">
-        <v>7087369</v>
+        <v>7086928</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7266,7 +7276,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7276,12 +7286,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7308,10 +7313,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124749167</v>
+        <v>124733886</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7320,45 +7325,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706354</v>
+        <v>706495</v>
       </c>
       <c r="R60" t="n">
-        <v>7087195</v>
+        <v>7087369</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7385,14 +7386,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7401,29 +7412,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749263</v>
+        <v>124749539</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7464,10 +7474,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706282</v>
+        <v>706157</v>
       </c>
       <c r="R61" t="n">
-        <v>7087215</v>
+        <v>7087072</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7532,10 +7542,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749657</v>
+        <v>124733393</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7566,23 +7576,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705966</v>
+        <v>706533</v>
       </c>
       <c r="R62" t="n">
-        <v>7086987</v>
+        <v>7087362</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7609,14 +7615,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7625,29 +7636,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124732683</v>
+        <v>124749392</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7656,41 +7666,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706597</v>
+        <v>706191</v>
       </c>
       <c r="R63" t="n">
-        <v>7087402</v>
+        <v>7087129</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7717,19 +7731,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7738,28 +7747,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124734417</v>
+        <v>124749013</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7790,19 +7800,23 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706465</v>
+        <v>706446</v>
       </c>
       <c r="R64" t="n">
-        <v>7087346</v>
+        <v>7087375</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7829,24 +7843,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,28 +7859,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124734081</v>
+        <v>124749086</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7907,19 +7912,23 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706490</v>
+        <v>706447</v>
       </c>
       <c r="R65" t="n">
-        <v>7087362</v>
+        <v>7087337</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7946,19 +7955,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7967,28 +7971,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124739661</v>
+        <v>124749133</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8019,19 +8024,23 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705952</v>
+        <v>706364</v>
       </c>
       <c r="R66" t="n">
-        <v>7086928</v>
+        <v>7087314</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8058,39 +8067,30 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -6525,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124734648</v>
+        <v>124749686</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6537,41 +6537,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706405</v>
+        <v>705962</v>
       </c>
       <c r="R53" t="n">
-        <v>7087320</v>
+        <v>7086855</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6598,39 +6601,30 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7095,10 +7089,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749686</v>
+        <v>124734648</v>
       </c>
       <c r="B58" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7107,44 +7101,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705962</v>
+        <v>706405</v>
       </c>
       <c r="R58" t="n">
-        <v>7086855</v>
+        <v>7087320</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7171,30 +7162,39 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -2652,7 +2652,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749246</v>
+        <v>124749184</v>
       </c>
       <c r="B18" t="n">
         <v>98269</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706288</v>
+        <v>706340</v>
       </c>
       <c r="R18" t="n">
-        <v>7087206</v>
+        <v>7087178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10+ bladrosetter.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,7 +2764,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124749414</v>
+        <v>124734940</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2798,23 +2798,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706126</v>
+        <v>706418</v>
       </c>
       <c r="R19" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,37 +2842,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124749111</v>
+        <v>124733393</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
@@ -2910,23 +2900,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706398</v>
+        <v>706533</v>
       </c>
       <c r="R20" t="n">
-        <v>7087345</v>
+        <v>7087362</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,14 +2939,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,26 +2960,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124739585</v>
+        <v>124749539</v>
       </c>
       <c r="B21" t="n">
         <v>98269</v>
@@ -3022,19 +3012,23 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705944</v>
+        <v>706157</v>
       </c>
       <c r="R21" t="n">
-        <v>7086954</v>
+        <v>7087072</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3061,19 +3055,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:48</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,25 +3071,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124749460</v>
+        <v>124734417</v>
       </c>
       <c r="B22" t="n">
         <v>98269</v>
@@ -3134,23 +3124,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706115</v>
+        <v>706465</v>
       </c>
       <c r="R22" t="n">
-        <v>7087088</v>
+        <v>7087346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3177,14 +3163,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3193,26 +3189,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124734081</v>
+        <v>124749133</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -3246,19 +3241,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706490</v>
+        <v>706364</v>
       </c>
       <c r="R23" t="n">
-        <v>7087362</v>
+        <v>7087314</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3285,49 +3284,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124733522</v>
+        <v>124749246</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3336,41 +3326,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706523</v>
+        <v>706288</v>
       </c>
       <c r="R24" t="n">
-        <v>7087364</v>
+        <v>7087206</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3397,19 +3391,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3418,25 +3407,26 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124734417</v>
+        <v>124749414</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3470,19 +3460,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706465</v>
+        <v>706126</v>
       </c>
       <c r="R25" t="n">
-        <v>7087346</v>
+        <v>7087117</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3509,24 +3503,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mer än 20</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3535,28 +3519,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124749331</v>
+        <v>124733522</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,45 +3550,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706228</v>
+        <v>706523</v>
       </c>
       <c r="R26" t="n">
-        <v>7087165</v>
+        <v>7087364</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3630,14 +3611,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3646,26 +3632,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749500</v>
+        <v>124749376</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3709,10 +3694,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706145</v>
+        <v>706224</v>
       </c>
       <c r="R27" t="n">
-        <v>7087098</v>
+        <v>7087139</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3777,7 +3762,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124734940</v>
+        <v>124749070</v>
       </c>
       <c r="B28" t="n">
         <v>98269</v>
@@ -3811,19 +3796,23 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706418</v>
+        <v>706442</v>
       </c>
       <c r="R28" t="n">
-        <v>7087323</v>
+        <v>7087349</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3855,31 +3844,37 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124749575</v>
+        <v>124739585</v>
       </c>
       <c r="B29" t="n">
         <v>98269</v>
@@ -3913,23 +3908,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706133</v>
+        <v>705944</v>
       </c>
       <c r="R29" t="n">
-        <v>7087057</v>
+        <v>7086954</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3956,14 +3947,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,29 +3968,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124732613</v>
+        <v>124749111</v>
       </c>
       <c r="B30" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,41 +3998,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706654</v>
+        <v>706398</v>
       </c>
       <c r="R30" t="n">
-        <v>7087408</v>
+        <v>7087345</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4064,19 +4063,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4085,28 +4079,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124734381</v>
+        <v>124749040</v>
       </c>
       <c r="B31" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4115,41 +4110,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706473</v>
+        <v>706431</v>
       </c>
       <c r="R31" t="n">
-        <v>7087334</v>
+        <v>7087362</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4176,19 +4175,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,25 +4191,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124749376</v>
+        <v>124739909</v>
       </c>
       <c r="B32" t="n">
         <v>98269</v>
@@ -4248,24 +4243,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706224</v>
+        <v>706048</v>
       </c>
       <c r="R32" t="n">
-        <v>7087139</v>
+        <v>7086914</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4297,37 +4297,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749657</v>
+        <v>124749500</v>
       </c>
       <c r="B33" t="n">
         <v>98269</v>
@@ -4371,10 +4365,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705966</v>
+        <v>706145</v>
       </c>
       <c r="R33" t="n">
-        <v>7086987</v>
+        <v>7087098</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4439,7 +4433,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124739096</v>
+        <v>124749350</v>
       </c>
       <c r="B34" t="n">
         <v>98269</v>
@@ -4473,19 +4467,23 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706304</v>
+        <v>706238</v>
       </c>
       <c r="R34" t="n">
-        <v>7087194</v>
+        <v>7087154</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4512,19 +4510,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:32</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4533,28 +4526,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124732683</v>
+        <v>124749460</v>
       </c>
       <c r="B35" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4563,41 +4557,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706597</v>
+        <v>706115</v>
       </c>
       <c r="R35" t="n">
-        <v>7087402</v>
+        <v>7087088</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4624,19 +4622,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4645,28 +4638,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124749290</v>
+        <v>124734648</v>
       </c>
       <c r="B36" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4675,49 +4669,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706276</v>
+        <v>706405</v>
       </c>
       <c r="R36" t="n">
-        <v>7087213</v>
+        <v>7087320</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4744,9 +4730,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,22 +4757,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124744220</v>
+        <v>124734745</v>
       </c>
       <c r="B37" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4785,53 +4781,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706411</v>
+        <v>706401</v>
       </c>
       <c r="R37" t="n">
-        <v>7087322</v>
+        <v>7087323</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4858,9 +4842,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4875,22 +4874,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124739580</v>
+        <v>124732613</v>
       </c>
       <c r="B38" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4903,34 +4902,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706048</v>
+        <v>706654</v>
       </c>
       <c r="R38" t="n">
-        <v>7086914</v>
+        <v>7087408</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4960,9 +4959,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4977,22 +4986,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124736627</v>
+        <v>124734139</v>
       </c>
       <c r="B39" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5001,25 +5010,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5029,10 +5038,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706292</v>
+        <v>706472</v>
       </c>
       <c r="R39" t="n">
-        <v>7087225</v>
+        <v>7087356</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5062,9 +5071,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5079,19 +5103,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124749350</v>
+        <v>124737518</v>
       </c>
       <c r="B40" t="n">
         <v>98269</v>
@@ -5125,23 +5149,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706238</v>
+        <v>706341</v>
       </c>
       <c r="R40" t="n">
-        <v>7087154</v>
+        <v>7087207</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5168,14 +5188,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ett fåtal.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,26 +5209,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124735830</v>
+        <v>124749657</v>
       </c>
       <c r="B41" t="n">
         <v>98269</v>
@@ -5237,19 +5261,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706344</v>
+        <v>705966</v>
       </c>
       <c r="R41" t="n">
-        <v>7087202</v>
+        <v>7086987</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5276,19 +5304,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5297,28 +5320,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124749263</v>
+        <v>124734903</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5327,45 +5351,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706282</v>
+        <v>706371</v>
       </c>
       <c r="R42" t="n">
-        <v>7087215</v>
+        <v>7087353</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5392,14 +5412,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5408,26 +5433,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124749184</v>
+        <v>124739096</v>
       </c>
       <c r="B43" t="n">
         <v>98269</v>
@@ -5461,23 +5485,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706340</v>
+        <v>706304</v>
       </c>
       <c r="R43" t="n">
-        <v>7087178</v>
+        <v>7087194</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5504,14 +5524,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5520,26 +5545,25 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124737518</v>
+        <v>124737966</v>
       </c>
       <c r="B44" t="n">
         <v>98269</v>
@@ -5572,17 +5596,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706341</v>
+        <v>706281</v>
       </c>
       <c r="R44" t="n">
-        <v>7087207</v>
+        <v>7087219</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5612,19 +5645,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5639,19 +5662,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124739909</v>
+        <v>124749013</v>
       </c>
       <c r="B45" t="n">
         <v>98269</v>
@@ -5684,29 +5707,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706048</v>
+        <v>706446</v>
       </c>
       <c r="R45" t="n">
-        <v>7086914</v>
+        <v>7087375</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5738,34 +5756,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124734903</v>
+        <v>124732401</v>
       </c>
       <c r="B46" t="n">
-        <v>80057</v>
+        <v>91166</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5774,25 +5798,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5802,10 +5826,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706371</v>
+        <v>706665</v>
       </c>
       <c r="R46" t="n">
-        <v>7087353</v>
+        <v>7087406</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5837,7 +5861,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5847,7 +5871,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5874,10 +5898,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124737966</v>
+        <v>124744220</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5886,50 +5910,53 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706281</v>
+        <v>706411</v>
       </c>
       <c r="R47" t="n">
-        <v>7087219</v>
+        <v>7087322</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5973,22 +6000,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124732401</v>
+        <v>124734381</v>
       </c>
       <c r="B48" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6001,21 +6028,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6025,10 +6052,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706665</v>
+        <v>706473</v>
       </c>
       <c r="R48" t="n">
-        <v>7087406</v>
+        <v>7087334</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6060,7 +6087,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6070,7 +6097,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6097,10 +6124,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124739921</v>
+        <v>124739661</v>
       </c>
       <c r="B49" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6109,25 +6136,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6137,10 +6164,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706034</v>
+        <v>705952</v>
       </c>
       <c r="R49" t="n">
-        <v>7086918</v>
+        <v>7086928</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6172,7 +6199,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6182,7 +6209,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6209,10 +6236,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124749040</v>
+        <v>124739580</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6221,45 +6248,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706431</v>
+        <v>706048</v>
       </c>
       <c r="R50" t="n">
-        <v>7087362</v>
+        <v>7086914</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6291,40 +6314,34 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124735169</v>
+        <v>124749575</v>
       </c>
       <c r="B51" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6333,41 +6350,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706394</v>
+        <v>706133</v>
       </c>
       <c r="R51" t="n">
-        <v>7087340</v>
+        <v>7087057</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6399,34 +6420,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124738318</v>
+        <v>124749392</v>
       </c>
       <c r="B52" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6435,41 +6462,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706281</v>
+        <v>706191</v>
       </c>
       <c r="R52" t="n">
-        <v>7087219</v>
+        <v>7087129</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6501,34 +6532,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749686</v>
+        <v>124749331</v>
       </c>
       <c r="B53" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6537,30 +6574,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6568,10 +6606,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705962</v>
+        <v>706228</v>
       </c>
       <c r="R53" t="n">
-        <v>7086855</v>
+        <v>7087165</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6604,6 +6642,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6631,7 +6674,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124734745</v>
+        <v>124735830</v>
       </c>
       <c r="B54" t="n">
         <v>98269</v>
@@ -6671,10 +6714,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706401</v>
+        <v>706344</v>
       </c>
       <c r="R54" t="n">
-        <v>7087323</v>
+        <v>7087202</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6706,7 +6749,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6716,12 +6759,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6748,10 +6786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124734139</v>
+        <v>124738318</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6760,25 +6798,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6826,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706472</v>
+        <v>706281</v>
       </c>
       <c r="R55" t="n">
-        <v>7087356</v>
+        <v>7087219</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6821,24 +6859,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6853,22 +6876,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124749167</v>
+        <v>124732683</v>
       </c>
       <c r="B56" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6877,45 +6900,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706354</v>
+        <v>706597</v>
       </c>
       <c r="R56" t="n">
-        <v>7087195</v>
+        <v>7087402</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6942,14 +6961,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6958,29 +6982,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124749070</v>
+        <v>124739921</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6989,45 +7012,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706442</v>
+        <v>706034</v>
       </c>
       <c r="R57" t="n">
-        <v>7087349</v>
+        <v>7086918</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7054,14 +7073,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7070,29 +7094,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124734648</v>
+        <v>124749290</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,41 +7124,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706405</v>
+        <v>706276</v>
       </c>
       <c r="R58" t="n">
-        <v>7087320</v>
+        <v>7087213</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,19 +7193,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7189,22 +7210,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124739661</v>
+        <v>124733886</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7213,38 +7234,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705952</v>
+        <v>706495</v>
       </c>
       <c r="R59" t="n">
-        <v>7086928</v>
+        <v>7087369</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7276,7 +7297,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7286,7 +7307,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7313,10 +7339,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124733886</v>
+        <v>124735169</v>
       </c>
       <c r="B60" t="n">
-        <v>56836</v>
+        <v>91166</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7325,25 +7351,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7353,10 +7379,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706495</v>
+        <v>706394</v>
       </c>
       <c r="R60" t="n">
-        <v>7087369</v>
+        <v>7087340</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7386,24 +7412,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,22 +7429,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124749539</v>
+        <v>124736627</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7442,45 +7453,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706157</v>
+        <v>706292</v>
       </c>
       <c r="R61" t="n">
-        <v>7087072</v>
+        <v>7087225</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7512,37 +7519,31 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124733393</v>
+        <v>124749167</v>
       </c>
       <c r="B62" t="n">
         <v>98269</v>
@@ -7576,19 +7577,23 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706533</v>
+        <v>706354</v>
       </c>
       <c r="R62" t="n">
-        <v>7087362</v>
+        <v>7087195</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7615,19 +7620,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7636,25 +7636,26 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749392</v>
+        <v>124749263</v>
       </c>
       <c r="B63" t="n">
         <v>98269</v>
@@ -7698,10 +7699,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706191</v>
+        <v>706282</v>
       </c>
       <c r="R63" t="n">
-        <v>7087129</v>
+        <v>7087215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7766,7 +7767,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124749013</v>
+        <v>124734081</v>
       </c>
       <c r="B64" t="n">
         <v>98269</v>
@@ -7800,23 +7801,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706446</v>
+        <v>706490</v>
       </c>
       <c r="R64" t="n">
-        <v>7087375</v>
+        <v>7087362</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7843,14 +7840,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7859,29 +7861,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749086</v>
+        <v>124749686</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7890,31 +7891,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706447</v>
+        <v>705962</v>
       </c>
       <c r="R65" t="n">
-        <v>7087337</v>
+        <v>7086855</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7958,11 +7958,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7990,7 +7985,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749133</v>
+        <v>124749086</v>
       </c>
       <c r="B66" t="n">
         <v>98269</v>
@@ -8034,10 +8029,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706364</v>
+        <v>706447</v>
       </c>
       <c r="R66" t="n">
-        <v>7087314</v>
+        <v>7087337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8070,6 +8065,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55683697</v>
+        <v>55683694</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706444.0679929107</v>
+        <v>706303</v>
       </c>
       <c r="R2" t="n">
-        <v>7087384.025965689</v>
+        <v>7087168</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -802,15 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55683688</v>
+        <v>101826339</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,37 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>706040.8528305558</v>
+        <v>706208</v>
       </c>
       <c r="R3" t="n">
-        <v>7086935.920887038</v>
+        <v>7087155</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,27 +897,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55683699</v>
+        <v>101826347</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,37 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>706470.0142891905</v>
+        <v>705952</v>
       </c>
       <c r="R4" t="n">
-        <v>7087406.967672462</v>
+        <v>7086918</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,49 +1013,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55683691</v>
+        <v>55683690</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>705963.0888215249</v>
+        <v>705972</v>
       </c>
       <c r="R5" t="n">
-        <v>7086906.032976821</v>
+        <v>7086890</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,6 +1120,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1168,35 +1151,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55683685</v>
+        <v>55683697</v>
       </c>
       <c r="B6" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>706042.0572907617</v>
+        <v>706444</v>
       </c>
       <c r="R6" t="n">
-        <v>7086904.149731286</v>
+        <v>7087384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,6 +1242,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1276,37 +1273,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55683693</v>
+        <v>55683699</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1316,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>706247.9963763404</v>
+        <v>706470</v>
       </c>
       <c r="R7" t="n">
-        <v>7087187.098730648</v>
+        <v>7087407</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,6 +1364,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1388,15 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55683694</v>
+        <v>101826336</v>
       </c>
       <c r="B8" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,37 +1406,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>706302.8371525727</v>
+        <v>706525</v>
       </c>
       <c r="R8" t="n">
-        <v>7087168.152271462</v>
+        <v>7087398</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,22 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,27 +1495,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55683696</v>
+        <v>124732192</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,37 +1522,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706438.0905193186</v>
+        <v>706679</v>
       </c>
       <c r="R9" t="n">
-        <v>7087300.034105423</v>
+        <v>7087409</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,22 +1576,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,46 +1602,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55683690</v>
+        <v>124732401</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,17 +1649,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705972.1283636615</v>
+        <v>706665</v>
       </c>
       <c r="R10" t="n">
-        <v>7086889.8175129</v>
+        <v>7087406</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,22 +1683,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-08-07</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,46 +1709,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101826339</v>
+        <v>124732613</v>
       </c>
       <c r="B11" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,37 +1736,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brattfällan, Bjurholm, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706208.0446453462</v>
+        <v>706654</v>
       </c>
       <c r="R11" t="n">
-        <v>7087154.831022538</v>
+        <v>7087408</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,22 +1790,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,50 +1816,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101826347</v>
+        <v>124732683</v>
       </c>
       <c r="B12" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,37 +1843,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brattfällan, Bjurholm, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705952.1338574963</v>
+        <v>706597</v>
       </c>
       <c r="R12" t="n">
-        <v>7086917.698751946</v>
+        <v>7087402</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1970,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,50 +1923,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101826336</v>
+        <v>124735169</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,17 +1970,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brattfällan, Bjurholm, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>706525.095865685</v>
+        <v>706394</v>
       </c>
       <c r="R13" t="n">
-        <v>7087397.773463283</v>
+        <v>7087340</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2101,22 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,50 +2020,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Jonas Eilertsen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101825170</v>
+        <v>124739147</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,37 +2047,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brattfällsberget nedre del, mot Öreälven, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706636.2393680817</v>
+        <v>705981</v>
       </c>
       <c r="R14" t="n">
-        <v>7087391.39487978</v>
+        <v>7087062</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2232,22 +2101,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,62 +2131,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101826346</v>
+        <v>124749686</v>
       </c>
       <c r="B15" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brattfällan, Bjurholm, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705922.7819120236</v>
+        <v>705962</v>
       </c>
       <c r="R15" t="n">
-        <v>7086966.640094223</v>
+        <v>7086855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,22 +2211,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,75 +2225,67 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101826348</v>
+        <v>124739921</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brattfällan, Bjurholm, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705954.4838782533</v>
+        <v>706034</v>
       </c>
       <c r="R16" t="n">
-        <v>7086915.641476237</v>
+        <v>7086918</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2460,22 +2309,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,54 +2335,30 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>101826338</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2561,10 +2386,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>706214.9846896862</v>
+        <v>706215</v>
       </c>
       <c r="R17" t="n">
-        <v>7087157.057404533</v>
+        <v>7087157</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2594,19 +2419,9 @@
           <t>2022-06-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-06-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,15 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124749184</v>
+        <v>101826348</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,38 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706340</v>
+        <v>705954</v>
       </c>
       <c r="R18" t="n">
-        <v>7087178</v>
+        <v>7086916</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2726,17 +2532,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2745,72 +2546,85 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124734940</v>
+        <v>101825170</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällsberget nedre del, mot Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706418</v>
+        <v>706636</v>
       </c>
       <c r="R19" t="n">
-        <v>7087323</v>
+        <v>7087392</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2834,12 +2648,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,49 +2668,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124733393</v>
+        <v>124734903</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2906,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706533</v>
+        <v>706371</v>
       </c>
       <c r="R20" t="n">
-        <v>7087362</v>
+        <v>7087353</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2941,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,14 +2760,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2978,57 +2787,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124749539</v>
+        <v>124733522</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706157</v>
+        <v>706523</v>
       </c>
       <c r="R21" t="n">
-        <v>7087072</v>
+        <v>7087364</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3055,14 +2855,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3071,56 +2876,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124734417</v>
+        <v>124734381</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3130,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706465</v>
+        <v>706473</v>
       </c>
       <c r="R22" t="n">
-        <v>7087346</v>
+        <v>7087334</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3165,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3175,12 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mer än 20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3207,57 +3001,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124749133</v>
+        <v>124736627</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706364</v>
+        <v>706292</v>
       </c>
       <c r="R23" t="n">
-        <v>7087314</v>
+        <v>7087225</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3295,76 +3080,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124749246</v>
+        <v>124739580</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706288</v>
+        <v>706048</v>
       </c>
       <c r="R24" t="n">
-        <v>7087206</v>
+        <v>7086914</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3396,87 +3171,72 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>10+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124749414</v>
+        <v>124733886</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706126</v>
+        <v>706495</v>
       </c>
       <c r="R25" t="n">
-        <v>7087117</v>
+        <v>7087369</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3503,72 +3263,76 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>20+ bladrosetter.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124733522</v>
+        <v>124738318</v>
       </c>
       <c r="B26" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3578,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706523</v>
+        <v>706281</v>
       </c>
       <c r="R26" t="n">
-        <v>7087364</v>
+        <v>7087219</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3611,26 +3375,16 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3638,55 +3392,58 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124749376</v>
+        <v>124744220</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3694,10 +3451,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706224</v>
+        <v>706411</v>
       </c>
       <c r="R27" t="n">
-        <v>7087139</v>
+        <v>7087322</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3732,18 +3489,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3762,43 +3513,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124749070</v>
+        <v>124749290</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3806,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706442</v>
+        <v>706276</v>
       </c>
       <c r="R28" t="n">
-        <v>7087349</v>
+        <v>7087213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3844,18 +3594,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3874,53 +3618,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124739585</v>
+        <v>101826346</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705944</v>
+        <v>705923</v>
       </c>
       <c r="R29" t="n">
-        <v>7086954</v>
+        <v>7086966</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3944,22 +3683,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3974,27 +3703,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124749111</v>
+        <v>55683691</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4020,23 +3748,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706398</v>
+        <v>705963</v>
       </c>
       <c r="R30" t="n">
-        <v>7087345</v>
+        <v>7086906</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4060,17 +3784,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,34 +3808,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124749040</v>
+        <v>55683693</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,23 +3855,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706431</v>
+        <v>706248</v>
       </c>
       <c r="R31" t="n">
-        <v>7087362</v>
+        <v>7087187</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4172,17 +3891,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,34 +3915,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124739909</v>
+        <v>124733393</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4243,26 +3961,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706048</v>
+        <v>706533</v>
       </c>
       <c r="R32" t="n">
-        <v>7086914</v>
+        <v>7087362</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4292,9 +4001,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4309,27 +4028,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124749500</v>
+        <v>124734081</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4355,23 +4069,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706145</v>
+        <v>706490</v>
       </c>
       <c r="R33" t="n">
-        <v>7087098</v>
+        <v>7087362</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4398,14 +4108,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4414,34 +4129,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124749350</v>
+        <v>124734139</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4467,23 +4176,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706238</v>
+        <v>706472</v>
       </c>
       <c r="R34" t="n">
-        <v>7087154</v>
+        <v>7087356</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4510,14 +4215,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>Mer än 30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4526,34 +4241,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124749460</v>
+        <v>124734417</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4579,23 +4288,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706115</v>
+        <v>706465</v>
       </c>
       <c r="R35" t="n">
-        <v>7087088</v>
+        <v>7087346</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4622,14 +4327,24 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+          <t>Mer än 20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,19 +4353,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4660,12 +4374,7 @@
         <v>124734648</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4772,12 +4481,7 @@
         <v>124734745</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4886,37 +4590,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124732613</v>
+        <v>124734940</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4926,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706654</v>
+        <v>706418</v>
       </c>
       <c r="R38" t="n">
-        <v>7087408</v>
+        <v>7087323</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4959,19 +4658,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,27 +4675,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124734139</v>
+        <v>124735830</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5038,10 +4722,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706472</v>
+        <v>706344</v>
       </c>
       <c r="R39" t="n">
-        <v>7087356</v>
+        <v>7087202</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5073,7 +4757,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5083,12 +4767,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mer än 30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5115,15 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124737518</v>
+        <v>124736752</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5148,17 +4822,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706341</v>
+        <v>706281</v>
       </c>
       <c r="R40" t="n">
-        <v>7087207</v>
+        <v>7087219</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5188,19 +4871,9 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5215,27 +4888,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124749657</v>
+        <v>124737518</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5261,23 +4929,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Brattfällan, Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705966</v>
+        <v>706341</v>
       </c>
       <c r="R41" t="n">
-        <v>7086987</v>
+        <v>7087207</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5304,14 +4968,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5320,56 +4989,50 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124734903</v>
+        <v>124739096</v>
       </c>
       <c r="B42" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5379,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706371</v>
+        <v>706304</v>
       </c>
       <c r="R42" t="n">
-        <v>7087353</v>
+        <v>7087194</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5414,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5424,14 +5087,14 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -5451,15 +5114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124739096</v>
+        <v>124739585</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,14 +5145,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706304</v>
+        <v>705944</v>
       </c>
       <c r="R43" t="n">
-        <v>7087194</v>
+        <v>7086954</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5526,7 +5184,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5536,7 +5194,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5563,15 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124737966</v>
+        <v>124739661</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5596,26 +5249,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706281</v>
+        <v>705952</v>
       </c>
       <c r="R44" t="n">
-        <v>7087219</v>
+        <v>7086928</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5645,9 +5289,19 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5662,27 +5316,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124749013</v>
+        <v>124739909</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5707,24 +5356,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattfällan, Ång</t>
+          <t>Fagernäs, Fagernäs, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706446</v>
+        <v>706048</v>
       </c>
       <c r="R45" t="n">
-        <v>7087375</v>
+        <v>7086914</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5756,83 +5410,76 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124732401</v>
+        <v>124749013</v>
       </c>
       <c r="B46" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706665</v>
+        <v>706446</v>
       </c>
       <c r="R46" t="n">
-        <v>7087406</v>
+        <v>7087375</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5859,19 +5506,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>08:49</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5880,69 +5522,57 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124744220</v>
+        <v>124749040</v>
       </c>
       <c r="B47" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5950,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706411</v>
+        <v>706431</v>
       </c>
       <c r="R47" t="n">
-        <v>7087322</v>
+        <v>7087362</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5988,12 +5618,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter. Mycket rikligt på tuva.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6012,53 +5648,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124734381</v>
+        <v>124749070</v>
       </c>
       <c r="B48" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706473</v>
+        <v>706442</v>
       </c>
       <c r="R48" t="n">
-        <v>7087334</v>
+        <v>7087349</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6085,19 +5720,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6106,33 +5736,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124739661</v>
+        <v>124749086</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,19 +5784,23 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>705952</v>
+        <v>706447</v>
       </c>
       <c r="R49" t="n">
-        <v>7086928</v>
+        <v>7087337</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6197,19 +5827,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:50</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,71 +5843,71 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124739580</v>
+        <v>124749111</v>
       </c>
       <c r="B50" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706048</v>
+        <v>706398</v>
       </c>
       <c r="R50" t="n">
-        <v>7086914</v>
+        <v>7087345</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6314,39 +5939,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124749575</v>
+        <v>124749133</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6382,10 +6008,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706133</v>
+        <v>706364</v>
       </c>
       <c r="R51" t="n">
-        <v>7087057</v>
+        <v>7087314</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6418,11 +6044,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6450,15 +6071,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124749392</v>
+        <v>124749167</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6494,10 +6110,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706191</v>
+        <v>706354</v>
       </c>
       <c r="R52" t="n">
-        <v>7087129</v>
+        <v>7087195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6562,15 +6178,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124749331</v>
+        <v>124749184</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6606,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706228</v>
+        <v>706340</v>
       </c>
       <c r="R53" t="n">
-        <v>7087165</v>
+        <v>7087178</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6646,7 +6257,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ett fåtal.</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6674,15 +6285,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124735830</v>
+        <v>124749246</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6708,19 +6314,23 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706344</v>
+        <v>706288</v>
       </c>
       <c r="R54" t="n">
-        <v>7087202</v>
+        <v>7087206</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6747,19 +6357,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:24</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6768,71 +6373,71 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124738318</v>
+        <v>124749263</v>
       </c>
       <c r="B55" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706281</v>
+        <v>706282</v>
       </c>
       <c r="R55" t="n">
-        <v>7087219</v>
+        <v>7087215</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6864,77 +6469,82 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124732683</v>
+        <v>124749331</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706597</v>
+        <v>706228</v>
       </c>
       <c r="R56" t="n">
-        <v>7087402</v>
+        <v>7087165</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6961,19 +6571,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:03</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6982,71 +6587,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124739921</v>
+        <v>124749350</v>
       </c>
       <c r="B57" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fagernäs, Fagernäs, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706034</v>
+        <v>706238</v>
       </c>
       <c r="R57" t="n">
-        <v>7086918</v>
+        <v>7087154</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7073,19 +6678,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:57</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ett fåtal.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7094,65 +6694,57 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124749290</v>
+        <v>124749376</v>
       </c>
       <c r="B58" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7160,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706276</v>
+        <v>706224</v>
       </c>
       <c r="R58" t="n">
-        <v>7087213</v>
+        <v>7087139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7198,12 +6790,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7222,53 +6820,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124733886</v>
+        <v>124749392</v>
       </c>
       <c r="B59" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706495</v>
+        <v>706191</v>
       </c>
       <c r="R59" t="n">
-        <v>7087369</v>
+        <v>7087129</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7295,97 +6892,87 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124735169</v>
+        <v>124749414</v>
       </c>
       <c r="B60" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706394</v>
+        <v>706126</v>
       </c>
       <c r="R60" t="n">
-        <v>7087340</v>
+        <v>7087117</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7417,77 +7004,82 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124736627</v>
+        <v>124749460</v>
       </c>
       <c r="B61" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706292</v>
+        <v>706115</v>
       </c>
       <c r="R61" t="n">
-        <v>7087225</v>
+        <v>7087088</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7519,39 +7111,40 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fläckvis mycket rikligt över flera kvadratmeter.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124749167</v>
+        <v>124749500</v>
       </c>
       <c r="B62" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7587,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706354</v>
+        <v>706145</v>
       </c>
       <c r="R62" t="n">
-        <v>7087195</v>
+        <v>7087098</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7655,15 +7248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124749263</v>
+        <v>124749539</v>
       </c>
       <c r="B63" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7699,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706282</v>
+        <v>706157</v>
       </c>
       <c r="R63" t="n">
-        <v>7087215</v>
+        <v>7087072</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7767,15 +7355,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124734081</v>
+        <v>124749575</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7801,19 +7384,23 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brattfällan, Brattfällan, Ång</t>
+          <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706490</v>
+        <v>706133</v>
       </c>
       <c r="R64" t="n">
-        <v>7087362</v>
+        <v>7087057</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7840,19 +7427,14 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7861,60 +7443,57 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124749686</v>
+        <v>124749657</v>
       </c>
       <c r="B65" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7922,10 +7501,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705962</v>
+        <v>705966</v>
       </c>
       <c r="R65" t="n">
-        <v>7086855</v>
+        <v>7086987</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7958,6 +7537,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>20+ bladrosetter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7985,57 +7569,44 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124749086</v>
+        <v>55683685</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Brattfällan, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706447</v>
+        <v>706042</v>
       </c>
       <c r="R66" t="n">
-        <v>7087337</v>
+        <v>7086904</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8059,17 +7630,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20+ bladrosetter.</t>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,19 +7654,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 14646-2025 artfynd.xlsx
+++ b/artfynd/A 14646-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826339</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683699</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1508,6 +1543,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124732192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1722,6 +1767,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124732401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1829,6 +1879,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124732613</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124732683</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124735169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2140,6 +2205,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739147</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2241,6 +2311,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749686</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2348,6 +2423,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739921</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2464,6 +2544,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826338</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2580,6 +2665,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2677,6 +2767,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101825170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2784,6 +2879,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734903</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2891,6 +2991,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124733522</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2998,6 +3103,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734381</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3095,6 +3205,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124736627</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3192,6 +3307,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739580</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3304,6 +3424,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124733886</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3401,6 +3526,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124738318</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3510,6 +3640,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744220</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3615,6 +3750,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749290</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3716,6 +3856,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101826346</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3823,6 +3968,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683691</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3930,6 +4080,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683693</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4037,6 +4192,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124733393</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4144,6 +4304,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734081</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4256,6 +4421,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734139</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4368,6 +4538,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734417</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4475,6 +4650,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734648</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4587,6 +4767,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734745</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4684,6 +4869,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734940</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4791,6 +4981,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124735830</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4897,6 +5092,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124736752</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5004,6 +5204,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124737518</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5111,6 +5316,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739096</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5218,6 +5428,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739585</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5325,6 +5540,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739661</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5431,6 +5651,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739909</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5538,6 +5763,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749013</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5645,6 +5875,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749040</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5752,6 +5987,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749070</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5859,6 +6099,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749086</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5966,6 +6211,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749111</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6068,6 +6318,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749133</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6175,6 +6430,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749167</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6282,6 +6542,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749184</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6389,6 +6654,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749246</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6496,6 +6766,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749263</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6603,6 +6878,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749331</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6710,6 +6990,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749350</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6817,6 +7102,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749376</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6924,6 +7214,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749392</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7031,6 +7326,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749414</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7138,6 +7438,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749460</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7245,6 +7550,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749500</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7352,6 +7662,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749539</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7459,6 +7774,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749575</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7566,6 +7886,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124749657</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7669,8 +7994,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683685</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>